--- a/resources/outputs_schema_data_analytics_nutrition_template.xlsx
+++ b/resources/outputs_schema_data_analytics_nutrition_template.xlsx
@@ -1,34 +1,141 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB4B3CEE-1FFF-422D-9F96-87C5FCE2B6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+  <si>
+    <t>output_name</t>
+  </si>
+  <si>
+    <t>output_title</t>
+  </si>
+  <si>
+    <t>output_subtitle</t>
+  </si>
+  <si>
+    <t>variables</t>
+  </si>
+  <si>
+    <t>disaggregation</t>
+  </si>
+  <si>
+    <t>output_func_name</t>
+  </si>
+  <si>
+    <t>test_params</t>
+  </si>
+  <si>
+    <t>output_type</t>
+  </si>
+  <si>
+    <t>outputs_group</t>
+  </si>
+  <si>
+    <t>outputs_per_group</t>
+  </si>
+  <si>
+    <t>dataset_type</t>
+  </si>
+  <si>
+    <t>muac_cat_overall_unweighted</t>
+  </si>
+  <si>
+    <t>muac_cat_overall</t>
+  </si>
+  <si>
+    <t>nut_muac_cat</t>
+  </si>
+  <si>
+    <t>plot_stacked_bar</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_muac_cat,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat,title_name="Nutritional Status by MUAC, Overall",show_labels=TRUE</t>
+  </si>
+  <si>
+    <t>visualization</t>
+  </si>
+  <si>
+    <t>base</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>mfaz_cat_overall_unweighted</t>
+  </si>
+  <si>
+    <t>mfaz_cat_overall</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_mfaz_cat,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat,title_name="Nutritional Status by MFAZ, Overall",show_labels=TRUE</t>
+  </si>
+  <si>
+    <t>mfaz_boxplot_overall_unweighted</t>
+  </si>
+  <si>
+    <t>mfaz_boxplot_overall</t>
+  </si>
+  <si>
+    <t>plot_boxplot</t>
+  </si>
+  <si>
+    <t>nut_mfaz</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name="MUAC-for-Age Z-Score Boxplot, Overall",y_label=@variable_label$nut_mfaz</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F2328"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -43,84 +150,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,72 +460,142 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>output_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>output_title</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>output_subtitle</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>variables</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>disaggregation</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>output_func_name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>test_params</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>output_type</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>outputs_group</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>outputs_per_group</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>dataset_type</t>
-        </is>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{3EE8CCD2-69EC-4278-AE21-D65D369CECAD}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{76FCC99B-F1FC-4090-95AB-A31441781683}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{A27A6072-8D0B-4EC8-A0C7-3EA6D6ABD9F4}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/resources/outputs_schema_data_analytics_nutrition_template.xlsx
+++ b/resources/outputs_schema_data_analytics_nutrition_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB4B3CEE-1FFF-422D-9F96-87C5FCE2B6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96981816-77CE-4B35-A44E-A392AB861D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="475">
   <si>
     <t>output_name</t>
   </si>
@@ -55,9 +55,6 @@
     <t>dataset_type</t>
   </si>
   <si>
-    <t>muac_cat_overall_unweighted</t>
-  </si>
-  <si>
     <t>muac_cat_overall</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
     <t>plot_stacked_bar</t>
   </si>
   <si>
-    <t>category_var=@variable_map$nut_muac_cat,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat,title_name="Nutritional Status by MUAC, Overall",show_labels=TRUE</t>
-  </si>
-  <si>
     <t>visualization</t>
   </si>
   <si>
@@ -79,21 +73,12 @@
     <t>data</t>
   </si>
   <si>
-    <t>mfaz_cat_overall_unweighted</t>
-  </si>
-  <si>
     <t>mfaz_cat_overall</t>
   </si>
   <si>
     <t>nut_mfaz_cat</t>
   </si>
   <si>
-    <t>category_var=@variable_map$nut_mfaz_cat,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat,title_name="Nutritional Status by MFAZ, Overall",show_labels=TRUE</t>
-  </si>
-  <si>
-    <t>mfaz_boxplot_overall_unweighted</t>
-  </si>
-  <si>
     <t>mfaz_boxplot_overall</t>
   </si>
   <si>
@@ -103,7 +88,1363 @@
     <t>nut_mfaz</t>
   </si>
   <si>
-    <t>numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name="MUAC-for-Age Z-Score Boxplot, Overall",y_label=@variable_label$nut_mfaz</t>
+    <t>muac_cat_overall_noflag</t>
+  </si>
+  <si>
+    <t>gam_muac_overall</t>
+  </si>
+  <si>
+    <t>gam_muac_overall_noflag</t>
+  </si>
+  <si>
+    <t>gam_muac</t>
+  </si>
+  <si>
+    <t>gam_muac_noflag</t>
+  </si>
+  <si>
+    <t>nut_muac_cat_noflag</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC, Overall</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$gam_muac_noflag,color_palette="traffic_light",legend_label=@variable_label$gam_muac_noflag,show_labels=TRUE</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$gam_muac,color_palette="traffic_light",legend_label=@variable_label$gam_muac,show_labels=TRUE</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_muac_cat_noflag,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat_noflag,show_labels=TRUE</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_muac_cat,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat,show_labels=TRUE</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_mfaz_cat,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE</t>
+  </si>
+  <si>
+    <t>nut_muac_cm</t>
+  </si>
+  <si>
+    <t>nut_muac_cm_noflag</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat_noflag</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_mfaz_cat_noflag,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat_noflag,show_labels=TRUE</t>
+  </si>
+  <si>
+    <t>mfaz_boxplot_overall_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_cat_overall_noflag</t>
+  </si>
+  <si>
+    <t>nut_mfaz_noflag</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>plot_cumulative_distribution</t>
+  </si>
+  <si>
+    <t>data_var=@variable_map$nut_muac_cm,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm</t>
+  </si>
+  <si>
+    <t>data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag</t>
+  </si>
+  <si>
+    <t>muac_cumdist_overall</t>
+  </si>
+  <si>
+    <t>muac_cumdist_overall_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_zscore_dist_overall</t>
+  </si>
+  <si>
+    <t>mfaz_zscore_dist_overall_noflag</t>
+  </si>
+  <si>
+    <t>plot_zscore_distribution</t>
+  </si>
+  <si>
+    <t>zscore_var=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz</t>
+  </si>
+  <si>
+    <t>zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag</t>
+  </si>
+  <si>
+    <t>plot_date_runnner</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_sd_overall</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_sd_overall_noflag</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_mean_overall</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_mean_overall_noflag</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean"</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean"</t>
+  </si>
+  <si>
+    <t>muac_cumrunner_mean_overall</t>
+  </si>
+  <si>
+    <t>muac_cumrunner_mean_overall_noflag</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean"</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean"</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2</t>
+  </si>
+  <si>
+    <t>ecfies_vars_stacked_bar_overall</t>
+  </si>
+  <si>
+    <t>ecfies_s01,ecfies_s02,ecfies_s03,ecfies_s04,ecfies_s05,ecfies_s06,ecfies_s07,ecfies_s08</t>
+  </si>
+  <si>
+    <t>plot_stacked_bar_multiple_vars</t>
+  </si>
+  <si>
+    <t>ecfies_overall</t>
+  </si>
+  <si>
+    <t>nut_ecfies_cat</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_ecfies_cat,color_palette="traffic_light",legend_label=@variable_label$nut_ecfies_cat,show_labels=TRUE</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_muac_cm,show_labels=TRUE,y_label=@variable_label$nut_muac_cm,show_mean=TRUE</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_muac_cm_noflag,show_labels=TRUE,y_label=@variable_label$nut_muac_cm_noflag,show_mean=TRUE</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name="MUAC-for-Age Z-Score Boxplot, Overall",y_label=@variable_label$nut_mfaz,show_mean=TRUE</t>
+  </si>
+  <si>
+    <t>ecfies_boxplot_overall</t>
+  </si>
+  <si>
+    <t>nut_ecfies_score</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_ecfies_score,show_labels=TRUE,y_label=@variable_label$nut_ecfies_score,show_mean=TRUE</t>
+  </si>
+  <si>
+    <t>bf_yesterday_overall</t>
+  </si>
+  <si>
+    <t>nut_bf_yesterday</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_bf_yesterday,legend_label=@variable_label$nut_bf_yesterday,show_labels=TRUE</t>
+  </si>
+  <si>
+    <t>bf_lack_reasons_overall</t>
+  </si>
+  <si>
+    <t>nut_bf_lack_reasons</t>
+  </si>
+  <si>
+    <t>plot_grouped_bar_multiple</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_muac_cat,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat,show_labels=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_muac_cat_noflag,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$gam_muac,color_palette="traffic_light",legend_label=@variable_label$gam_muac,show_labels=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$gam_muac_noflag,color_palette="traffic_light",legend_label=@variable_label$gam_muac_noflag,show_labels=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_muac_cm,show_labels=TRUE,y_label=@variable_label$nut_muac_cm,show_mean=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_muac_cm_noflag,show_labels=TRUE,y_label=@variable_label$nut_muac_cm_noflag,show_mean=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>data_var=@variable_map$nut_muac_cm,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_mfaz_cat,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_mfaz_cat_noflag,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name="MUAC-for-Age Z-Score Boxplot, Overall",y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>zscore_var=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,grouping=@variable_map$sex,grouping_label=@variable_label$sex</t>
+  </si>
+  <si>
+    <t>zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$sex,grouping_label=@variable_label$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>catecory_vars=c(@variable_map$ecfies_s01,@variable_map$ecfies_s02,@variable_map$ecfies_s03,@variable_map$ecfies_s04,@variable_map$ecfies_s05,@variable_map$ecfies_s06,@variable_map$ecfies_s07,@variable_map$ecfies_s08),category_labels=c(@variable_label$ecfies_s01,@variable_label$ecfies_s02,@variable_label$ecfies_s03,@variable_label$ecfies_s04,@variable_label$ecfies_s05,@variable_label$ecfies_s06,@variable_label$ecfies_s07,@variable_label$ecfies_s08),show_labels=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_ecfies_cat,color_palette="traffic_light",legend_label=@variable_label$nut_ecfies_cat,show_labels=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_ecfies_score,show_labels=TRUE,y_label=@variable_label$nut_ecfies_score,show_mean=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_bf_yesterday,legend_label=@variable_label$nut_bf_yesterday,show_labels=TRUE,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC, by Sex</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC, Overall</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC (flags excluded), Overall</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC (flags excluded), Overall</t>
+  </si>
+  <si>
+    <t>MUAC Boxplot, Overall</t>
+  </si>
+  <si>
+    <t>MUAC Boxplot (flags excluded), Overall</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Distribution, Overall</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Distribution (flags excluded), Overall</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Mean Runner Plot, Overall</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Mean Runner Plot (flags excluded), Overall</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative SD Runner Plot, Overall</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative SD Runner Plot (flags excluded), Overall</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score, Overall</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score (flags excluded), Overall</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Boxplot, Overall</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Boxplot (flags excluded), Overall</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Distribution, Overall</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Distribution (flags excluded), Overall</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative Mean Runner Plot, Overall</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative Mean Runner Plot (flags excluded), Overall</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative SD Runner Plot, Overall</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative SD Runner Plot (flags excluded), Overall</t>
+  </si>
+  <si>
+    <t>ECFIES Questions Stacked Bar, Overall</t>
+  </si>
+  <si>
+    <t>ECFIES Severity Stacked Bar, Overall</t>
+  </si>
+  <si>
+    <t>ECFIES Score Boxplot, Overall</t>
+  </si>
+  <si>
+    <t>Breastfed Previous Day, Overall</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC (flags excluded), by Sex</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC (flags excluded), by Sex</t>
+  </si>
+  <si>
+    <t>MUAC Boxplot, by Sex</t>
+  </si>
+  <si>
+    <t>MUAC Boxplot (flags excluded), by Sex</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Distribution, by Sex</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Distribution (flags excluded), by Sex</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Mean Runner Plot, by Sex</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Mean Runner Plot (flags excluded), by Sex</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative SD Runner Plot, by Sex</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative SD Runner Plot (flags excluded), by Sex</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score, by Sex</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score (flags excluded), by Sex</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Boxplot, by Sex</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Boxplot (flags excluded), by Sex</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Distribution, by Sex</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Distribution (flags excluded), by Sex</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative Mean Runner Plot, by Sex</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative Mean Runner Plot (flags excluded), by Sex</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative SD Runner Plot, by Sex</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative SD Runner Plot (flags excluded), by Sex</t>
+  </si>
+  <si>
+    <t>ECFIES Questions Stacked Bar, by Sex</t>
+  </si>
+  <si>
+    <t>ECFIES Severity Stacked Bar, by Sex</t>
+  </si>
+  <si>
+    <t>ECFIES Score Boxplot, by Sex</t>
+  </si>
+  <si>
+    <t>Breastfed Previous Day, by Sex</t>
+  </si>
+  <si>
+    <t>muac_cat_sex_noflag</t>
+  </si>
+  <si>
+    <t>gam_muac_sex</t>
+  </si>
+  <si>
+    <t>gam_muac_sex_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_boxplot_sex</t>
+  </si>
+  <si>
+    <t>mfaz_boxplot_sex_noflag</t>
+  </si>
+  <si>
+    <t>muac_cumdist_sex</t>
+  </si>
+  <si>
+    <t>muac_cumdist_sex_noflag</t>
+  </si>
+  <si>
+    <t>muac_cumrunner_mean_sex</t>
+  </si>
+  <si>
+    <t>muac_cumrunner_mean_sex_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_sd_sex</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_sd_sex_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_cat_sex</t>
+  </si>
+  <si>
+    <t>mfaz_cat_sex_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_zscore_dist_sex</t>
+  </si>
+  <si>
+    <t>mfaz_zscore_dist_sex_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_mean_sex</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_mean_sex_noflag</t>
+  </si>
+  <si>
+    <t>ecfies_vars_stacked_bar_sex</t>
+  </si>
+  <si>
+    <t>ecfies_sex</t>
+  </si>
+  <si>
+    <t>ecfies_boxplot_sex</t>
+  </si>
+  <si>
+    <t>bf_yesterday_sex</t>
+  </si>
+  <si>
+    <t>muac_cat_sex</t>
+  </si>
+  <si>
+    <t>age_months_cat</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_muac_cat,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat,show_labels=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_muac_cat_noflag,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat_noflag,show_labels=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$gam_muac,color_palette="traffic_light",legend_label=@variable_label$gam_muac,show_labels=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$gam_muac_noflag,color_palette="traffic_light",legend_label=@variable_label$gam_muac_noflag,show_labels=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_muac_cm,show_labels=TRUE,y_label=@variable_label$nut_muac_cm,show_mean=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_muac_cm_noflag,show_labels=TRUE,y_label=@variable_label$nut_muac_cm_noflag,show_mean=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>data_var=@variable_map$nut_muac_cm,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_mfaz_cat,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_mfaz_cat_noflag,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat_noflag,show_labels=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name="MUAC-for-Age Z-Score Boxplot, Overall",y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>zscore_var=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,grouping=@variable_map$age_months_cat,grouping_label=@variable_label$age_months_cat</t>
+  </si>
+  <si>
+    <t>zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$age_months_cat,grouping_label=@variable_label$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>catecory_vars=c(@variable_map$ecfies_s01,@variable_map$ecfies_s02,@variable_map$ecfies_s03,@variable_map$ecfies_s04,@variable_map$ecfies_s05,@variable_map$ecfies_s06,@variable_map$ecfies_s07,@variable_map$ecfies_s08),category_labels=c(@variable_label$ecfies_s01,@variable_label$ecfies_s02,@variable_label$ecfies_s03,@variable_label$ecfies_s04,@variable_label$ecfies_s05,@variable_label$ecfies_s06,@variable_label$ecfies_s07,@variable_label$ecfies_s08),show_labels=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_ecfies_cat,color_palette="traffic_light",legend_label=@variable_label$nut_ecfies_cat,show_labels=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_ecfies_score,show_labels=TRUE,y_label=@variable_label$nut_ecfies_score,show_mean=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_bf_yesterday,legend_label=@variable_label$nut_bf_yesterday,show_labels=TRUE,grouping=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>muac_cat_age_months</t>
+  </si>
+  <si>
+    <t>muac_cat_age_months_noflag</t>
+  </si>
+  <si>
+    <t>gam_muac_age_months</t>
+  </si>
+  <si>
+    <t>gam_muac_age_months_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_boxplot_age_months</t>
+  </si>
+  <si>
+    <t>mfaz_boxplot_age_months_noflag</t>
+  </si>
+  <si>
+    <t>muac_cumdist_age_months</t>
+  </si>
+  <si>
+    <t>muac_cumdist_age_months_noflag</t>
+  </si>
+  <si>
+    <t>muac_cumrunner_mean_age_months</t>
+  </si>
+  <si>
+    <t>muac_cumrunner_mean_age_months_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_sd_age_months</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_sd_age_months_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_cat_age_months</t>
+  </si>
+  <si>
+    <t>mfaz_cat_age_months_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_zscore_dist_age_months</t>
+  </si>
+  <si>
+    <t>mfaz_zscore_dist_age_months_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_mean_age_months</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_mean_age_months_noflag</t>
+  </si>
+  <si>
+    <t>ecfies_vars_stacked_bar_age_months</t>
+  </si>
+  <si>
+    <t>ecfies_age_months</t>
+  </si>
+  <si>
+    <t>ecfies_boxplot_age_months</t>
+  </si>
+  <si>
+    <t>bf_yesterday_age_months</t>
+  </si>
+  <si>
+    <t>Reasons Not Breastfeeding, Overall</t>
+  </si>
+  <si>
+    <t>Complementary Feeding Challenges, Overall</t>
+  </si>
+  <si>
+    <t>Food Groups Consumed, Overall</t>
+  </si>
+  <si>
+    <t>nut_food_child_consumptions</t>
+  </si>
+  <si>
+    <t>nut_complementary_feeding_challenges</t>
+  </si>
+  <si>
+    <t>food_child_consumptions_overall</t>
+  </si>
+  <si>
+    <t>complementary_feeding_challenges_overall</t>
+  </si>
+  <si>
+    <t>var_name=@variable_map$nut_bf_lack_reasons,variable_label=@variable_label$nut_bf_lack_reasons</t>
+  </si>
+  <si>
+    <t>var_name=@variable_map$nut_food_child_consumptions,variable_label=@variable_label$nut_food_child_consumptions</t>
+  </si>
+  <si>
+    <t>var_name=@variable_map$nut_complementary_feeding_challenges,variable_label=@variable_label$nut_complementary_feeding_challenges</t>
+  </si>
+  <si>
+    <t>category_vars=c(@variable_map$ecfies_s01,@variable_map$ecfies_s02,@variable_map$ecfies_s03,@variable_map$ecfies_s04,@variable_map$ecfies_s05,@variable_map$ecfies_s06,@variable_map$ecfies_s07,@variable_map$ecfies_s08),category_labels=c(@variable_label$ecfies_s01,@variable_label$ecfies_s02,@variable_label$ecfies_s03,@variable_label$ecfies_s04,@variable_label$ecfies_s05,@variable_label$ecfies_s06,@variable_label$ecfies_s07,@variable_label$ecfies_s08),show_labels=TRUE</t>
+  </si>
+  <si>
+    <t>var_name=@variable_map$nut_bf_lack_reasons,variable_label=@variable_label$nut_bf_lack_reasons,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>var_name=@variable_map$nut_food_child_consumptions,variable_label=@variable_label$nut_food_child_consumptions,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>var_name=@variable_map$nut_complementary_feeding_challenges,variable_label=@variable_label$nut_complementary_feeding_challenges,grouping=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>nut_muac_cat,sex</t>
+  </si>
+  <si>
+    <t>nut_muac_cat_noflag,sex</t>
+  </si>
+  <si>
+    <t>gam_muac,sex</t>
+  </si>
+  <si>
+    <t>gam_muac_noflag,sex</t>
+  </si>
+  <si>
+    <t>nut_muac_cm,sex</t>
+  </si>
+  <si>
+    <t>nut_muac_cm_noflag,sex</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat,sex</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat_noflag,sex</t>
+  </si>
+  <si>
+    <t>nut_mfaz,sex</t>
+  </si>
+  <si>
+    <t>nut_mfaz_noflag,sex</t>
+  </si>
+  <si>
+    <t>ecfies_s01,ecfies_s02,ecfies_s03,ecfies_s04,ecfies_s05,ecfies_s06,ecfies_s07,ecfies_s08,sex</t>
+  </si>
+  <si>
+    <t>nut_ecfies_cat,sex</t>
+  </si>
+  <si>
+    <t>nut_ecfies_score,sex</t>
+  </si>
+  <si>
+    <t>nut_bf_yesterday,sex</t>
+  </si>
+  <si>
+    <t>nut_bf_lack_reasons,sex</t>
+  </si>
+  <si>
+    <t>nut_food_child_consumptions,sex</t>
+  </si>
+  <si>
+    <t>nut_complementary_feeding_challenges,sex</t>
+  </si>
+  <si>
+    <t>nut_muac_cat,age_months_cat</t>
+  </si>
+  <si>
+    <t>nut_muac_cat_noflag,age_months_cat</t>
+  </si>
+  <si>
+    <t>gam_muac,age_months_cat</t>
+  </si>
+  <si>
+    <t>gam_muac_noflag,age_months_cat</t>
+  </si>
+  <si>
+    <t>nut_muac_cm,age_months_cat</t>
+  </si>
+  <si>
+    <t>nut_muac_cm_noflag,age_months_cat</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat,age_months_cat</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat_noflag,age_months_cat</t>
+  </si>
+  <si>
+    <t>nut_mfaz,age_months_cat</t>
+  </si>
+  <si>
+    <t>nut_mfaz_noflag,age_months_cat</t>
+  </si>
+  <si>
+    <t>ecfies_s01,ecfies_s02,ecfies_s03,ecfies_s04,ecfies_s05,ecfies_s06,ecfies_s07,ecfies_s08,age_months_cat</t>
+  </si>
+  <si>
+    <t>nut_ecfies_cat,age_months_cat</t>
+  </si>
+  <si>
+    <t>nut_ecfies_score,age_months_cat</t>
+  </si>
+  <si>
+    <t>nut_bf_yesterday,age_months_cat</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC, by Age Months Category</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC (flags excluded), by Age Months Category</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC (flags excluded), by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC Boxplot, by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC Boxplot (flags excluded), by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Distribution, by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Distribution (flags excluded), by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Mean Runner Plot, by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Mean Runner Plot (flags excluded), by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative SD Runner Plot, by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative SD Runner Plot (flags excluded), by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score, by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score (flags excluded), by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Boxplot, by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Boxplot (flags excluded), by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Distribution, by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Distribution (flags excluded), by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative Mean Runner Plot, by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative Mean Runner Plot (flags excluded), by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative SD Runner Plot, by Age Months Category</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative SD Runner Plot (flags excluded), by Age Months Category</t>
+  </si>
+  <si>
+    <t>ECFIES Questions Stacked Bar, by Age Months Category</t>
+  </si>
+  <si>
+    <t>ECFIES Severity Stacked Bar, by Age Months Category</t>
+  </si>
+  <si>
+    <t>ECFIES Score Boxplot, by Age Months Category</t>
+  </si>
+  <si>
+    <t>Breastfed Previous Day, by Age Months Category</t>
+  </si>
+  <si>
+    <t>nut_muac_cat,stratum</t>
+  </si>
+  <si>
+    <t>stratum</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_muac_cat,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat,show_labels=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>nut_muac_cat_noflag,stratum</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_muac_cat_noflag,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat_noflag,show_labels=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>gam_muac,stratum</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$gam_muac,color_palette="traffic_light",legend_label=@variable_label$gam_muac,show_labels=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>gam_muac_noflag,stratum</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$gam_muac_noflag,color_palette="traffic_light",legend_label=@variable_label$gam_muac_noflag,show_labels=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>nut_muac_cm,stratum</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_muac_cm,show_labels=TRUE,y_label=@variable_label$nut_muac_cm,show_mean=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>nut_muac_cm_noflag,stratum</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_muac_cm_noflag,show_labels=TRUE,y_label=@variable_label$nut_muac_cm_noflag,show_mean=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>data_var=@variable_map$nut_muac_cm,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat,stratum</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_mfaz_cat,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat_noflag,stratum</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_mfaz_cat_noflag,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat_noflag,show_labels=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>nut_mfaz,stratum</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name="MUAC-for-Age Z-Score Boxplot, Overall",y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>nut_mfaz_noflag,stratum</t>
+  </si>
+  <si>
+    <t>zscore_var=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,grouping=@variable_map$stratum,grouping_label=@variable_label$stratum</t>
+  </si>
+  <si>
+    <t>zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$stratum,grouping_label=@variable_label$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>ecfies_s01,ecfies_s02,ecfies_s03,ecfies_s04,ecfies_s05,ecfies_s06,ecfies_s07,ecfies_s08,stratum</t>
+  </si>
+  <si>
+    <t>catecory_vars=c(@variable_map$ecfies_s01,@variable_map$ecfies_s02,@variable_map$ecfies_s03,@variable_map$ecfies_s04,@variable_map$ecfies_s05,@variable_map$ecfies_s06,@variable_map$ecfies_s07,@variable_map$ecfies_s08),category_labels=c(@variable_label$ecfies_s01,@variable_label$ecfies_s02,@variable_label$ecfies_s03,@variable_label$ecfies_s04,@variable_label$ecfies_s05,@variable_label$ecfies_s06,@variable_label$ecfies_s07,@variable_label$ecfies_s08),show_labels=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>nut_ecfies_cat,stratum</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_ecfies_cat,color_palette="traffic_light",legend_label=@variable_label$nut_ecfies_cat,show_labels=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>nut_ecfies_score,stratum</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_ecfies_score,show_labels=TRUE,y_label=@variable_label$nut_ecfies_score,show_mean=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>nut_bf_yesterday,stratum</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_bf_yesterday,legend_label=@variable_label$nut_bf_yesterday,show_labels=TRUE,grouping=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC, by Strata</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC (flags excluded), by Strata</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC (flags excluded), by Strata</t>
+  </si>
+  <si>
+    <t>MUAC Boxplot, by Strata</t>
+  </si>
+  <si>
+    <t>MUAC Boxplot (flags excluded), by Strata</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Distribution, by Strata</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Distribution (flags excluded), by Strata</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Mean Runner Plot, by Strata</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Mean Runner Plot (flags excluded), by Strata</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative SD Runner Plot, by Strata</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative SD Runner Plot (flags excluded), by Strata</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score, by Strata</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score (flags excluded), by Strata</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Boxplot, by Strata</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Boxplot (flags excluded), by Strata</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Distribution, by Strata</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Distribution (flags excluded), by Strata</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative Mean Runner Plot, by Strata</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative Mean Runner Plot (flags excluded), by Strata</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative SD Runner Plot, by Strata</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative SD Runner Plot (flags excluded), by Strata</t>
+  </si>
+  <si>
+    <t>ECFIES Questions Stacked Bar, by Strata</t>
+  </si>
+  <si>
+    <t>ECFIES Severity Stacked Bar, by Strata</t>
+  </si>
+  <si>
+    <t>ECFIES Score Boxplot, by Strata</t>
+  </si>
+  <si>
+    <t>Breastfed Previous Day, by Strata</t>
+  </si>
+  <si>
+    <t>muac_cat_stratum</t>
+  </si>
+  <si>
+    <t>muac_cat__stratum_noflag</t>
+  </si>
+  <si>
+    <t>gam_muac_stratum</t>
+  </si>
+  <si>
+    <t>mfaz_boxplot_stratum</t>
+  </si>
+  <si>
+    <t>mfaz_boxplot_stratum_noflag</t>
+  </si>
+  <si>
+    <t>muac_cumdist_stratum</t>
+  </si>
+  <si>
+    <t>muac_cumdist_stratum_noflag</t>
+  </si>
+  <si>
+    <t>muac_cumrunner_mean_stratum</t>
+  </si>
+  <si>
+    <t>muac_cumrunner_mean_stratum_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_sd_stratum</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_sd_stratum_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_cat_stratum</t>
+  </si>
+  <si>
+    <t>mfaz_cat_stratum_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_zscore_dist_stratum</t>
+  </si>
+  <si>
+    <t>mfaz_zscore_dist_stratum_noflag</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_mean_stratum</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_mean_stratum_noflag</t>
+  </si>
+  <si>
+    <t>ecfies_vars_stacked_bar_stratum</t>
+  </si>
+  <si>
+    <t>ecfies_stratum</t>
+  </si>
+  <si>
+    <t>ecfies_boxplot_stratum</t>
+  </si>
+  <si>
+    <t>bf_yesterday_stratum</t>
+  </si>
+  <si>
+    <t>muac_cat_enum_id</t>
+  </si>
+  <si>
+    <t>nut_muac_cat,enum_id</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_muac_cat,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat,show_labels=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>muac_cat__enum_id_noflag</t>
+  </si>
+  <si>
+    <t>nut_muac_cat_noflag,enum_id</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_muac_cat_noflag,color_palette="traffic_light",legend_label=@variable_label$nut_muac_cat_noflag,show_labels=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>gam_muac_enum_id</t>
+  </si>
+  <si>
+    <t>gam_muac,enum_id</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$gam_muac,color_palette="traffic_light",legend_label=@variable_label$gam_muac,show_labels=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>gam_muac_noflag,enum_id</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$gam_muac_noflag,color_palette="traffic_light",legend_label=@variable_label$gam_muac_noflag,show_labels=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>mfaz_boxplot_enum_id</t>
+  </si>
+  <si>
+    <t>nut_muac_cm,enum_id</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_muac_cm,show_labels=TRUE,y_label=@variable_label$nut_muac_cm,show_mean=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>mfaz_boxplot_enum_id_noflag</t>
+  </si>
+  <si>
+    <t>nut_muac_cm_noflag,enum_id</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_muac_cm_noflag,show_labels=TRUE,y_label=@variable_label$nut_muac_cm_noflag,show_mean=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>muac_cumdist_enum_id</t>
+  </si>
+  <si>
+    <t>data_var=@variable_map$nut_muac_cm,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>muac_cumdist_enum_id_noflag</t>
+  </si>
+  <si>
+    <t>data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>muac_cumrunner_mean_enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>muac_cumrunner_mean_enum_id_noflag</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_sd_enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_sd_enum_id_noflag</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>mfaz_cat_enum_id</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat,enum_id</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_mfaz_cat,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>mfaz_cat_enum_id_noflag</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat_noflag,enum_id</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_mfaz_cat_noflag,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat_noflag,show_labels=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>nut_mfaz,enum_id</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name="MUAC-for-Age Z-Score Boxplot, Overall",y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>nut_mfaz_noflag,enum_id</t>
+  </si>
+  <si>
+    <t>mfaz_zscore_dist_enum_id</t>
+  </si>
+  <si>
+    <t>zscore_var=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,grouping=@variable_map$enum_id,grouping_label=@variable_label$enum_id</t>
+  </si>
+  <si>
+    <t>mfaz_zscore_dist_enum_id_noflag</t>
+  </si>
+  <si>
+    <t>zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$enum_id,grouping_label=@variable_label$enum_id</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_mean_enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>mfaz_cumrunner_mean_enum_id_noflag</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>ecfies_vars_stacked_bar_enum_id</t>
+  </si>
+  <si>
+    <t>ecfies_s01,ecfies_s02,ecfies_s03,ecfies_s04,ecfies_s05,ecfies_s06,ecfies_s07,ecfies_s08,enum_id</t>
+  </si>
+  <si>
+    <t>catecory_vars=c(@variable_map$ecfies_s01,@variable_map$ecfies_s02,@variable_map$ecfies_s03,@variable_map$ecfies_s04,@variable_map$ecfies_s05,@variable_map$ecfies_s06,@variable_map$ecfies_s07,@variable_map$ecfies_s08),category_labels=c(@variable_label$ecfies_s01,@variable_label$ecfies_s02,@variable_label$ecfies_s03,@variable_label$ecfies_s04,@variable_label$ecfies_s05,@variable_label$ecfies_s06,@variable_label$ecfies_s07,@variable_label$ecfies_s08),show_labels=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>ecfies_enum_id</t>
+  </si>
+  <si>
+    <t>nut_ecfies_cat,enum_id</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_ecfies_cat,color_palette="traffic_light",legend_label=@variable_label$nut_ecfies_cat,show_labels=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>ecfies_boxplot_enum_id</t>
+  </si>
+  <si>
+    <t>nut_ecfies_score,enum_id</t>
+  </si>
+  <si>
+    <t>numeric_var=@variable_map$nut_ecfies_score,show_labels=TRUE,y_label=@variable_label$nut_ecfies_score,show_mean=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>bf_yesterday_enum_id</t>
+  </si>
+  <si>
+    <t>nut_bf_yesterday,enum_id</t>
+  </si>
+  <si>
+    <t>category_var=@variable_map$nut_bf_yesterday,legend_label=@variable_label$nut_bf_yesterday,show_labels=TRUE,grouping=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>Nutritional Status by MUAC (flags excluded), by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC (flags excluded), by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC Boxplot, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC Boxplot (flags excluded), by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Distribution, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Distribution (flags excluded), by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Mean Runner Plot, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative Mean Runner Plot (flags excluded), by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative SD Runner Plot, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC Cumulative SD Runner Plot (flags excluded), by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score (flags excluded), by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Boxplot, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Boxplot (flags excluded), by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Distribution, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Distribution (flags excluded), by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative Mean Runner Plot, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative Mean Runner Plot (flags excluded), by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative SD Runner Plot, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-score Cumulative SD Runner Plot (flags excluded), by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>ECFIES Questions Stacked Bar, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>ECFIES Severity Stacked Bar, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>ECFIES Score Boxplot, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>Breastfed Previous Day, by Enumerator/Team</t>
+  </si>
+  <si>
+    <t>survey_design</t>
+  </si>
+  <si>
+    <t>enumerator</t>
   </si>
 </sst>
 </file>
@@ -461,15 +1802,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K247"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.85546875" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.140625" customWidth="1"/>
     <col min="7" max="7" width="44.42578125" customWidth="1"/>
     <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
@@ -514,87 +1855,7527 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" t="s">
+        <v>15</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" t="s">
+        <v>241</v>
+      </c>
+      <c r="H24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H26" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H27" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>231</v>
+      </c>
+      <c r="B28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" t="s">
+        <v>84</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H28" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>233</v>
+      </c>
+      <c r="B29" t="s">
+        <v>236</v>
+      </c>
+      <c r="D29" t="s">
+        <v>234</v>
+      </c>
+      <c r="F29" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H29" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>232</v>
+      </c>
+      <c r="B30" t="s">
+        <v>237</v>
+      </c>
+      <c r="D30" t="s">
+        <v>235</v>
+      </c>
+      <c r="F30" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H30" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" t="s">
+        <v>245</v>
+      </c>
+      <c r="E31" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H31" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" t="s">
+        <v>246</v>
+      </c>
+      <c r="E32" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H32" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" t="s">
+        <v>15</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" t="s">
+        <v>247</v>
+      </c>
+      <c r="E33" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" t="s">
+        <v>15</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B34" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" t="s">
+        <v>248</v>
+      </c>
+      <c r="E34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H34" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" t="s">
+        <v>15</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>139</v>
+      </c>
+      <c r="B35" t="s">
+        <v>164</v>
+      </c>
+      <c r="C35" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" t="s">
+        <v>249</v>
+      </c>
+      <c r="E35" t="s">
+        <v>85</v>
+      </c>
+      <c r="F35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H35" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" t="s">
+        <v>15</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" t="s">
+        <v>165</v>
+      </c>
+      <c r="C36" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" t="s">
+        <v>250</v>
+      </c>
+      <c r="E36" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" t="s">
+        <v>15</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" t="s">
+        <v>249</v>
+      </c>
+      <c r="E37" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" t="s">
+        <v>42</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" t="s">
+        <v>15</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>142</v>
+      </c>
+      <c r="B38" t="s">
+        <v>167</v>
+      </c>
+      <c r="C38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" t="s">
+        <v>250</v>
+      </c>
+      <c r="E38" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38" t="s">
+        <v>42</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H38" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" t="s">
+        <v>15</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" t="s">
+        <v>168</v>
+      </c>
+      <c r="C39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E39" t="s">
+        <v>85</v>
+      </c>
+      <c r="F39" t="s">
+        <v>52</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H39" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" t="s">
+        <v>169</v>
+      </c>
+      <c r="C40" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" t="s">
+        <v>250</v>
+      </c>
+      <c r="E40" t="s">
+        <v>85</v>
+      </c>
+      <c r="F40" t="s">
+        <v>52</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H40" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" t="s">
+        <v>15</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>145</v>
+      </c>
+      <c r="B41" t="s">
+        <v>170</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" t="s">
+        <v>249</v>
+      </c>
+      <c r="E41" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H41" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>146</v>
+      </c>
+      <c r="B42" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" t="s">
+        <v>250</v>
+      </c>
+      <c r="E42" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" t="s">
+        <v>172</v>
+      </c>
+      <c r="D43" t="s">
+        <v>251</v>
+      </c>
+      <c r="E43" t="s">
+        <v>85</v>
+      </c>
+      <c r="F43" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H43" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" t="s">
+        <v>15</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" t="s">
+        <v>173</v>
+      </c>
+      <c r="D44" t="s">
+        <v>252</v>
+      </c>
+      <c r="E44" t="s">
+        <v>85</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H44" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" t="s">
+        <v>15</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" t="s">
+        <v>164</v>
+      </c>
+      <c r="D45" t="s">
+        <v>253</v>
+      </c>
+      <c r="E45" t="s">
+        <v>85</v>
+      </c>
+      <c r="F45" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" t="s">
+        <v>15</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>150</v>
+      </c>
+      <c r="B46" t="s">
+        <v>165</v>
+      </c>
+      <c r="D46" t="s">
+        <v>254</v>
+      </c>
+      <c r="E46" t="s">
+        <v>85</v>
+      </c>
+      <c r="F46" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H46" t="s">
+        <v>14</v>
+      </c>
+      <c r="I46" t="s">
+        <v>15</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>151</v>
+      </c>
+      <c r="B47" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" t="s">
+        <v>85</v>
+      </c>
+      <c r="F47" t="s">
+        <v>49</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H47" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" t="s">
+        <v>15</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" t="s">
+        <v>175</v>
+      </c>
+      <c r="D48" t="s">
+        <v>254</v>
+      </c>
+      <c r="E48" t="s">
+        <v>85</v>
+      </c>
+      <c r="F48" t="s">
+        <v>49</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H48" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" t="s">
+        <v>15</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" t="s">
+        <v>253</v>
+      </c>
+      <c r="E49" t="s">
+        <v>85</v>
+      </c>
+      <c r="F49" t="s">
+        <v>52</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H49" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" t="s">
+        <v>15</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>154</v>
+      </c>
+      <c r="B50" t="s">
+        <v>177</v>
+      </c>
+      <c r="D50" t="s">
+        <v>254</v>
+      </c>
+      <c r="E50" t="s">
+        <v>85</v>
+      </c>
+      <c r="F50" t="s">
+        <v>52</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H50" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" t="s">
+        <v>15</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>155</v>
+      </c>
+      <c r="B51" t="s">
+        <v>170</v>
+      </c>
+      <c r="D51" t="s">
+        <v>253</v>
+      </c>
+      <c r="E51" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H51" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" t="s">
+        <v>15</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>156</v>
+      </c>
+      <c r="B52" t="s">
+        <v>171</v>
+      </c>
+      <c r="D52" t="s">
+        <v>254</v>
+      </c>
+      <c r="E52" t="s">
+        <v>85</v>
+      </c>
+      <c r="F52" t="s">
+        <v>52</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H52" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" t="s">
+        <v>15</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>157</v>
+      </c>
+      <c r="B53" t="s">
+        <v>178</v>
+      </c>
+      <c r="D53" t="s">
+        <v>255</v>
+      </c>
+      <c r="E53" t="s">
+        <v>85</v>
+      </c>
+      <c r="F53" t="s">
+        <v>69</v>
+      </c>
+      <c r="G53" t="s">
+        <v>107</v>
+      </c>
+      <c r="H53" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" t="s">
+        <v>15</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>158</v>
+      </c>
+      <c r="B54" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" t="s">
+        <v>256</v>
+      </c>
+      <c r="E54" t="s">
+        <v>85</v>
+      </c>
+      <c r="F54" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" t="s">
+        <v>15</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" t="s">
+        <v>180</v>
+      </c>
+      <c r="D55" t="s">
+        <v>257</v>
+      </c>
+      <c r="E55" t="s">
+        <v>85</v>
+      </c>
+      <c r="F55" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H55" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" t="s">
+        <v>15</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" t="s">
+        <v>181</v>
+      </c>
+      <c r="D56" t="s">
+        <v>258</v>
+      </c>
+      <c r="E56" t="s">
+        <v>85</v>
+      </c>
+      <c r="F56" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H56" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" t="s">
+        <v>15</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>231</v>
+      </c>
+      <c r="B57" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" t="s">
+        <v>259</v>
+      </c>
+      <c r="E57" t="s">
+        <v>85</v>
+      </c>
+      <c r="F57" t="s">
+        <v>84</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H57" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" t="s">
+        <v>15</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>233</v>
+      </c>
+      <c r="B58" t="s">
+        <v>236</v>
+      </c>
+      <c r="D58" t="s">
+        <v>260</v>
+      </c>
+      <c r="E58" t="s">
+        <v>85</v>
+      </c>
+      <c r="F58" t="s">
+        <v>84</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H58" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>232</v>
+      </c>
+      <c r="B59" t="s">
+        <v>237</v>
+      </c>
+      <c r="D59" t="s">
+        <v>261</v>
+      </c>
+      <c r="E59" t="s">
+        <v>85</v>
+      </c>
+      <c r="F59" t="s">
+        <v>84</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="H59" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>276</v>
+      </c>
+      <c r="B60" t="s">
+        <v>209</v>
+      </c>
+      <c r="C60" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" t="s">
+        <v>262</v>
+      </c>
+      <c r="E60" t="s">
+        <v>183</v>
+      </c>
+      <c r="F60" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H60" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>277</v>
+      </c>
+      <c r="B61" t="s">
+        <v>210</v>
+      </c>
+      <c r="C61" t="s">
+        <v>41</v>
+      </c>
+      <c r="D61" t="s">
+        <v>263</v>
+      </c>
+      <c r="E61" t="s">
+        <v>183</v>
+      </c>
+      <c r="F61" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H61" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>28</v>
+      </c>
+      <c r="B62" t="s">
+        <v>211</v>
+      </c>
+      <c r="C62" t="s">
+        <v>41</v>
+      </c>
+      <c r="D62" t="s">
+        <v>264</v>
+      </c>
+      <c r="E62" t="s">
+        <v>183</v>
+      </c>
+      <c r="F62" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H62" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" t="s">
+        <v>15</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>278</v>
+      </c>
+      <c r="B63" t="s">
+        <v>212</v>
+      </c>
+      <c r="C63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D63" t="s">
+        <v>265</v>
+      </c>
+      <c r="E63" t="s">
+        <v>183</v>
+      </c>
+      <c r="F63" t="s">
+        <v>13</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H63" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" t="s">
+        <v>15</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>279</v>
+      </c>
+      <c r="B64" t="s">
+        <v>213</v>
+      </c>
+      <c r="C64" t="s">
+        <v>41</v>
+      </c>
+      <c r="D64" t="s">
+        <v>266</v>
+      </c>
+      <c r="E64" t="s">
+        <v>183</v>
+      </c>
+      <c r="F64" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H64" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" t="s">
+        <v>15</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>280</v>
+      </c>
+      <c r="B65" t="s">
+        <v>214</v>
+      </c>
+      <c r="C65" t="s">
+        <v>41</v>
+      </c>
+      <c r="D65" t="s">
+        <v>267</v>
+      </c>
+      <c r="E65" t="s">
+        <v>183</v>
+      </c>
+      <c r="F65" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H65" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>281</v>
+      </c>
+      <c r="B66" t="s">
+        <v>215</v>
+      </c>
+      <c r="C66" t="s">
+        <v>41</v>
+      </c>
+      <c r="D66" t="s">
+        <v>266</v>
+      </c>
+      <c r="E66" t="s">
+        <v>183</v>
+      </c>
+      <c r="F66" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" t="s">
+        <v>15</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>282</v>
+      </c>
+      <c r="B67" t="s">
+        <v>216</v>
+      </c>
+      <c r="C67" t="s">
+        <v>41</v>
+      </c>
+      <c r="D67" t="s">
+        <v>267</v>
+      </c>
+      <c r="E67" t="s">
+        <v>183</v>
+      </c>
+      <c r="F67" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H67" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" t="s">
+        <v>15</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>283</v>
+      </c>
+      <c r="B68" t="s">
+        <v>217</v>
+      </c>
+      <c r="C68" t="s">
+        <v>41</v>
+      </c>
+      <c r="D68" t="s">
+        <v>266</v>
+      </c>
+      <c r="E68" t="s">
+        <v>183</v>
+      </c>
+      <c r="F68" t="s">
+        <v>52</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H68" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" t="s">
+        <v>15</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>284</v>
+      </c>
+      <c r="B69" t="s">
+        <v>218</v>
+      </c>
+      <c r="C69" t="s">
+        <v>41</v>
+      </c>
+      <c r="D69" t="s">
+        <v>267</v>
+      </c>
+      <c r="E69" t="s">
+        <v>183</v>
+      </c>
+      <c r="F69" t="s">
+        <v>52</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H69" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" t="s">
+        <v>15</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>285</v>
+      </c>
+      <c r="B70" t="s">
+        <v>219</v>
+      </c>
+      <c r="C70" t="s">
+        <v>41</v>
+      </c>
+      <c r="D70" t="s">
+        <v>266</v>
+      </c>
+      <c r="E70" t="s">
+        <v>183</v>
+      </c>
+      <c r="F70" t="s">
+        <v>52</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H70" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" t="s">
+        <v>15</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>286</v>
+      </c>
+      <c r="B71" t="s">
+        <v>220</v>
+      </c>
+      <c r="C71" t="s">
+        <v>41</v>
+      </c>
+      <c r="D71" t="s">
+        <v>267</v>
+      </c>
+      <c r="E71" t="s">
+        <v>183</v>
+      </c>
+      <c r="F71" t="s">
+        <v>52</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H71" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" t="s">
+        <v>15</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>287</v>
+      </c>
+      <c r="B72" t="s">
+        <v>221</v>
+      </c>
+      <c r="D72" t="s">
+        <v>268</v>
+      </c>
+      <c r="E72" t="s">
+        <v>183</v>
+      </c>
+      <c r="F72" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H72" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" t="s">
+        <v>15</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>288</v>
+      </c>
+      <c r="B73" t="s">
+        <v>222</v>
+      </c>
+      <c r="D73" t="s">
+        <v>269</v>
+      </c>
+      <c r="E73" t="s">
+        <v>183</v>
+      </c>
+      <c r="F73" t="s">
+        <v>13</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H73" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" t="s">
+        <v>15</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>289</v>
+      </c>
+      <c r="B74" t="s">
+        <v>213</v>
+      </c>
+      <c r="D74" t="s">
+        <v>270</v>
+      </c>
+      <c r="E74" t="s">
+        <v>183</v>
+      </c>
+      <c r="F74" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H74" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>290</v>
+      </c>
+      <c r="B75" t="s">
+        <v>214</v>
+      </c>
+      <c r="D75" t="s">
+        <v>271</v>
+      </c>
+      <c r="E75" t="s">
+        <v>183</v>
+      </c>
+      <c r="F75" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H75" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" t="s">
+        <v>15</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>291</v>
+      </c>
+      <c r="B76" t="s">
+        <v>223</v>
+      </c>
+      <c r="D76" t="s">
+        <v>270</v>
+      </c>
+      <c r="E76" t="s">
+        <v>183</v>
+      </c>
+      <c r="F76" t="s">
+        <v>49</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H76" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76" t="s">
+        <v>15</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>292</v>
+      </c>
+      <c r="B77" t="s">
+        <v>224</v>
+      </c>
+      <c r="D77" t="s">
+        <v>271</v>
+      </c>
+      <c r="E77" t="s">
+        <v>183</v>
+      </c>
+      <c r="F77" t="s">
+        <v>49</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H77" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>293</v>
+      </c>
+      <c r="B78" t="s">
+        <v>225</v>
+      </c>
+      <c r="D78" t="s">
+        <v>270</v>
+      </c>
+      <c r="E78" t="s">
+        <v>183</v>
+      </c>
+      <c r="F78" t="s">
+        <v>52</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H78" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>294</v>
+      </c>
+      <c r="B79" t="s">
+        <v>226</v>
+      </c>
+      <c r="D79" t="s">
+        <v>271</v>
+      </c>
+      <c r="E79" t="s">
+        <v>183</v>
+      </c>
+      <c r="F79" t="s">
+        <v>52</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H79" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" t="s">
+        <v>15</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>295</v>
+      </c>
+      <c r="B80" t="s">
+        <v>219</v>
+      </c>
+      <c r="D80" t="s">
+        <v>270</v>
+      </c>
+      <c r="E80" t="s">
+        <v>183</v>
+      </c>
+      <c r="F80" t="s">
+        <v>52</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H80" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80" t="s">
+        <v>15</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>296</v>
+      </c>
+      <c r="B81" t="s">
+        <v>220</v>
+      </c>
+      <c r="D81" t="s">
+        <v>271</v>
+      </c>
+      <c r="E81" t="s">
+        <v>183</v>
+      </c>
+      <c r="F81" t="s">
+        <v>52</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H81" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>297</v>
+      </c>
+      <c r="B82" t="s">
+        <v>227</v>
+      </c>
+      <c r="D82" t="s">
+        <v>272</v>
+      </c>
+      <c r="E82" t="s">
+        <v>183</v>
+      </c>
+      <c r="F82" t="s">
+        <v>69</v>
+      </c>
+      <c r="G82" t="s">
+        <v>205</v>
+      </c>
+      <c r="H82" t="s">
+        <v>14</v>
+      </c>
+      <c r="I82" t="s">
+        <v>15</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>298</v>
+      </c>
+      <c r="B83" t="s">
+        <v>228</v>
+      </c>
+      <c r="D83" t="s">
+        <v>273</v>
+      </c>
+      <c r="E83" t="s">
+        <v>183</v>
+      </c>
+      <c r="F83" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H83" t="s">
+        <v>14</v>
+      </c>
+      <c r="I83" t="s">
+        <v>15</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>299</v>
+      </c>
+      <c r="B84" t="s">
+        <v>229</v>
+      </c>
+      <c r="D84" t="s">
+        <v>274</v>
+      </c>
+      <c r="E84" t="s">
+        <v>183</v>
+      </c>
+      <c r="F84" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H84" t="s">
+        <v>14</v>
+      </c>
+      <c r="I84" t="s">
+        <v>15</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>300</v>
+      </c>
+      <c r="B85" t="s">
+        <v>230</v>
+      </c>
+      <c r="D85" t="s">
+        <v>275</v>
+      </c>
+      <c r="E85" t="s">
+        <v>183</v>
+      </c>
+      <c r="F85" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H85" t="s">
+        <v>14</v>
+      </c>
+      <c r="I85" t="s">
+        <v>15</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>341</v>
+      </c>
+      <c r="B86" t="s">
+        <v>366</v>
+      </c>
+      <c r="C86" t="s">
+        <v>41</v>
+      </c>
+      <c r="D86" t="s">
+        <v>301</v>
+      </c>
+      <c r="E86" t="s">
+        <v>302</v>
+      </c>
+      <c r="F86" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="H86" t="s">
+        <v>14</v>
+      </c>
+      <c r="I86" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>342</v>
+      </c>
+      <c r="B87" t="s">
+        <v>367</v>
+      </c>
+      <c r="C87" t="s">
+        <v>41</v>
+      </c>
+      <c r="D87" t="s">
+        <v>304</v>
+      </c>
+      <c r="E87" t="s">
+        <v>302</v>
+      </c>
+      <c r="F87" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="H87" t="s">
+        <v>14</v>
+      </c>
+      <c r="I87" t="s">
+        <v>15</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>28</v>
+      </c>
+      <c r="B88" t="s">
+        <v>368</v>
+      </c>
+      <c r="C88" t="s">
+        <v>41</v>
+      </c>
+      <c r="D88" t="s">
+        <v>306</v>
+      </c>
+      <c r="E88" t="s">
+        <v>302</v>
+      </c>
+      <c r="F88" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H88" t="s">
+        <v>14</v>
+      </c>
+      <c r="I88" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>343</v>
+      </c>
+      <c r="B89" t="s">
+        <v>212</v>
+      </c>
+      <c r="C89" t="s">
+        <v>41</v>
+      </c>
+      <c r="D89" t="s">
+        <v>308</v>
+      </c>
+      <c r="E89" t="s">
+        <v>302</v>
+      </c>
+      <c r="F89" t="s">
+        <v>13</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H89" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>344</v>
+      </c>
+      <c r="B90" t="s">
+        <v>369</v>
+      </c>
+      <c r="C90" t="s">
+        <v>41</v>
+      </c>
+      <c r="D90" t="s">
+        <v>310</v>
+      </c>
+      <c r="E90" t="s">
+        <v>302</v>
+      </c>
+      <c r="F90" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="H90" t="s">
+        <v>14</v>
+      </c>
+      <c r="I90" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>345</v>
+      </c>
+      <c r="B91" t="s">
+        <v>370</v>
+      </c>
+      <c r="C91" t="s">
+        <v>41</v>
+      </c>
+      <c r="D91" t="s">
+        <v>312</v>
+      </c>
+      <c r="E91" t="s">
+        <v>302</v>
+      </c>
+      <c r="F91" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H91" t="s">
+        <v>14</v>
+      </c>
+      <c r="I91" t="s">
+        <v>15</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>346</v>
+      </c>
+      <c r="B92" t="s">
+        <v>371</v>
+      </c>
+      <c r="C92" t="s">
+        <v>41</v>
+      </c>
+      <c r="D92" t="s">
+        <v>310</v>
+      </c>
+      <c r="E92" t="s">
+        <v>302</v>
+      </c>
+      <c r="F92" t="s">
+        <v>42</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="H92" t="s">
+        <v>14</v>
+      </c>
+      <c r="I92" t="s">
+        <v>15</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>347</v>
+      </c>
+      <c r="B93" t="s">
+        <v>372</v>
+      </c>
+      <c r="C93" t="s">
+        <v>41</v>
+      </c>
+      <c r="D93" t="s">
+        <v>312</v>
+      </c>
+      <c r="E93" t="s">
+        <v>302</v>
+      </c>
+      <c r="F93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="H93" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" t="s">
+        <v>15</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>348</v>
+      </c>
+      <c r="B94" t="s">
+        <v>373</v>
+      </c>
+      <c r="C94" t="s">
+        <v>41</v>
+      </c>
+      <c r="D94" t="s">
+        <v>310</v>
+      </c>
+      <c r="E94" t="s">
+        <v>302</v>
+      </c>
+      <c r="F94" t="s">
+        <v>52</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="H94" t="s">
+        <v>14</v>
+      </c>
+      <c r="I94" t="s">
+        <v>15</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>349</v>
+      </c>
+      <c r="B95" t="s">
+        <v>374</v>
+      </c>
+      <c r="C95" t="s">
+        <v>41</v>
+      </c>
+      <c r="D95" t="s">
+        <v>312</v>
+      </c>
+      <c r="E95" t="s">
+        <v>302</v>
+      </c>
+      <c r="F95" t="s">
+        <v>52</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H95" t="s">
+        <v>14</v>
+      </c>
+      <c r="I95" t="s">
+        <v>15</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>350</v>
+      </c>
+      <c r="B96" t="s">
+        <v>375</v>
+      </c>
+      <c r="C96" t="s">
+        <v>41</v>
+      </c>
+      <c r="D96" t="s">
+        <v>310</v>
+      </c>
+      <c r="E96" t="s">
+        <v>302</v>
+      </c>
+      <c r="F96" t="s">
+        <v>52</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="H96" t="s">
+        <v>14</v>
+      </c>
+      <c r="I96" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>351</v>
+      </c>
+      <c r="B97" t="s">
+        <v>376</v>
+      </c>
+      <c r="C97" t="s">
+        <v>41</v>
+      </c>
+      <c r="D97" t="s">
+        <v>312</v>
+      </c>
+      <c r="E97" t="s">
+        <v>302</v>
+      </c>
+      <c r="F97" t="s">
+        <v>52</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="H97" t="s">
+        <v>14</v>
+      </c>
+      <c r="I97" t="s">
+        <v>15</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>352</v>
+      </c>
+      <c r="B98" t="s">
+        <v>377</v>
+      </c>
+      <c r="D98" t="s">
+        <v>320</v>
+      </c>
+      <c r="E98" t="s">
+        <v>302</v>
+      </c>
+      <c r="F98" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="H98" t="s">
+        <v>14</v>
+      </c>
+      <c r="I98" t="s">
+        <v>15</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>353</v>
+      </c>
+      <c r="B99" t="s">
+        <v>378</v>
+      </c>
+      <c r="D99" t="s">
+        <v>322</v>
+      </c>
+      <c r="E99" t="s">
+        <v>302</v>
+      </c>
+      <c r="F99" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H99" t="s">
+        <v>14</v>
+      </c>
+      <c r="I99" t="s">
+        <v>15</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>354</v>
+      </c>
+      <c r="B100" t="s">
+        <v>369</v>
+      </c>
+      <c r="D100" t="s">
+        <v>324</v>
+      </c>
+      <c r="E100" t="s">
+        <v>302</v>
+      </c>
+      <c r="F100" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H100" t="s">
+        <v>14</v>
+      </c>
+      <c r="I100" t="s">
+        <v>15</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>355</v>
+      </c>
+      <c r="B101" t="s">
+        <v>370</v>
+      </c>
+      <c r="D101" t="s">
+        <v>326</v>
+      </c>
+      <c r="E101" t="s">
+        <v>302</v>
+      </c>
+      <c r="F101" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H101" t="s">
+        <v>14</v>
+      </c>
+      <c r="I101" t="s">
+        <v>15</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>356</v>
+      </c>
+      <c r="B102" t="s">
+        <v>379</v>
+      </c>
+      <c r="D102" t="s">
+        <v>324</v>
+      </c>
+      <c r="E102" t="s">
+        <v>302</v>
+      </c>
+      <c r="F102" t="s">
+        <v>49</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H102" t="s">
+        <v>14</v>
+      </c>
+      <c r="I102" t="s">
+        <v>15</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>357</v>
+      </c>
+      <c r="B103" t="s">
+        <v>380</v>
+      </c>
+      <c r="D103" t="s">
+        <v>326</v>
+      </c>
+      <c r="E103" t="s">
+        <v>302</v>
+      </c>
+      <c r="F103" t="s">
+        <v>49</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H103" t="s">
+        <v>14</v>
+      </c>
+      <c r="I103" t="s">
+        <v>15</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>358</v>
+      </c>
+      <c r="B104" t="s">
+        <v>381</v>
+      </c>
+      <c r="D104" t="s">
+        <v>324</v>
+      </c>
+      <c r="E104" t="s">
+        <v>302</v>
+      </c>
+      <c r="F104" t="s">
+        <v>52</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="H104" t="s">
+        <v>14</v>
+      </c>
+      <c r="I104" t="s">
+        <v>15</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>359</v>
+      </c>
+      <c r="B105" t="s">
+        <v>382</v>
+      </c>
+      <c r="D105" t="s">
+        <v>326</v>
+      </c>
+      <c r="E105" t="s">
+        <v>302</v>
+      </c>
+      <c r="F105" t="s">
+        <v>52</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="H105" t="s">
+        <v>14</v>
+      </c>
+      <c r="I105" t="s">
+        <v>15</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>360</v>
+      </c>
+      <c r="B106" t="s">
+        <v>375</v>
+      </c>
+      <c r="D106" t="s">
+        <v>324</v>
+      </c>
+      <c r="E106" t="s">
+        <v>302</v>
+      </c>
+      <c r="F106" t="s">
+        <v>52</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H106" t="s">
+        <v>14</v>
+      </c>
+      <c r="I106" t="s">
+        <v>15</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>361</v>
+      </c>
+      <c r="B107" t="s">
+        <v>376</v>
+      </c>
+      <c r="D107" t="s">
+        <v>326</v>
+      </c>
+      <c r="E107" t="s">
+        <v>302</v>
+      </c>
+      <c r="F107" t="s">
+        <v>52</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="H107" t="s">
+        <v>14</v>
+      </c>
+      <c r="I107" t="s">
+        <v>15</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>362</v>
+      </c>
+      <c r="B108" t="s">
+        <v>383</v>
+      </c>
+      <c r="D108" t="s">
+        <v>333</v>
+      </c>
+      <c r="E108" t="s">
+        <v>302</v>
+      </c>
+      <c r="F108" t="s">
+        <v>69</v>
+      </c>
+      <c r="G108" t="s">
+        <v>334</v>
+      </c>
+      <c r="H108" t="s">
+        <v>14</v>
+      </c>
+      <c r="I108" t="s">
+        <v>15</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>363</v>
+      </c>
+      <c r="B109" t="s">
+        <v>384</v>
+      </c>
+      <c r="D109" t="s">
+        <v>335</v>
+      </c>
+      <c r="E109" t="s">
+        <v>302</v>
+      </c>
+      <c r="F109" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="H109" t="s">
+        <v>14</v>
+      </c>
+      <c r="I109" t="s">
+        <v>15</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>364</v>
+      </c>
+      <c r="B110" t="s">
+        <v>385</v>
+      </c>
+      <c r="D110" t="s">
+        <v>337</v>
+      </c>
+      <c r="E110" t="s">
+        <v>302</v>
+      </c>
+      <c r="F110" t="s">
+        <v>20</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H110" t="s">
+        <v>14</v>
+      </c>
+      <c r="I110" t="s">
+        <v>15</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>365</v>
+      </c>
+      <c r="B111" t="s">
+        <v>386</v>
+      </c>
+      <c r="D111" t="s">
+        <v>339</v>
+      </c>
+      <c r="E111" t="s">
+        <v>302</v>
+      </c>
+      <c r="F111" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H111" t="s">
+        <v>14</v>
+      </c>
+      <c r="I111" t="s">
+        <v>15</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>448</v>
+      </c>
+      <c r="B112" t="s">
+        <v>387</v>
+      </c>
+      <c r="C112" t="s">
+        <v>41</v>
+      </c>
+      <c r="D112" t="s">
+        <v>388</v>
+      </c>
+      <c r="E112" t="s">
+        <v>389</v>
+      </c>
+      <c r="F112" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="H112" t="s">
+        <v>14</v>
+      </c>
+      <c r="I112" t="s">
+        <v>474</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>449</v>
+      </c>
+      <c r="B113" t="s">
+        <v>391</v>
+      </c>
+      <c r="C113" t="s">
+        <v>41</v>
+      </c>
+      <c r="D113" t="s">
+        <v>392</v>
+      </c>
+      <c r="E113" t="s">
+        <v>389</v>
+      </c>
+      <c r="F113" t="s">
+        <v>13</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="H113" t="s">
+        <v>14</v>
+      </c>
+      <c r="I113" t="s">
+        <v>474</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>28</v>
+      </c>
+      <c r="B114" t="s">
+        <v>394</v>
+      </c>
+      <c r="C114" t="s">
+        <v>41</v>
+      </c>
+      <c r="D114" t="s">
+        <v>395</v>
+      </c>
+      <c r="E114" t="s">
+        <v>389</v>
+      </c>
+      <c r="F114" t="s">
+        <v>13</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H114" t="s">
+        <v>14</v>
+      </c>
+      <c r="I114" t="s">
+        <v>474</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>450</v>
+      </c>
+      <c r="B115" t="s">
+        <v>212</v>
+      </c>
+      <c r="C115" t="s">
+        <v>41</v>
+      </c>
+      <c r="D115" t="s">
+        <v>397</v>
+      </c>
+      <c r="E115" t="s">
+        <v>389</v>
+      </c>
+      <c r="F115" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="H115" t="s">
+        <v>14</v>
+      </c>
+      <c r="I115" t="s">
+        <v>474</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>451</v>
+      </c>
+      <c r="B116" t="s">
+        <v>399</v>
+      </c>
+      <c r="C116" t="s">
+        <v>41</v>
+      </c>
+      <c r="D116" t="s">
+        <v>400</v>
+      </c>
+      <c r="E116" t="s">
+        <v>389</v>
+      </c>
+      <c r="F116" t="s">
+        <v>20</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="H116" t="s">
+        <v>14</v>
+      </c>
+      <c r="I116" t="s">
+        <v>474</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>452</v>
+      </c>
+      <c r="B117" t="s">
+        <v>402</v>
+      </c>
+      <c r="C117" t="s">
+        <v>41</v>
+      </c>
+      <c r="D117" t="s">
+        <v>403</v>
+      </c>
+      <c r="E117" t="s">
+        <v>389</v>
+      </c>
+      <c r="F117" t="s">
+        <v>20</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H117" t="s">
+        <v>14</v>
+      </c>
+      <c r="I117" t="s">
+        <v>474</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>453</v>
+      </c>
+      <c r="B118" t="s">
+        <v>405</v>
+      </c>
+      <c r="C118" t="s">
+        <v>41</v>
+      </c>
+      <c r="D118" t="s">
+        <v>400</v>
+      </c>
+      <c r="E118" t="s">
+        <v>389</v>
+      </c>
+      <c r="F118" t="s">
+        <v>42</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="H118" t="s">
+        <v>14</v>
+      </c>
+      <c r="I118" t="s">
+        <v>474</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>454</v>
+      </c>
+      <c r="B119" t="s">
+        <v>407</v>
+      </c>
+      <c r="C119" t="s">
+        <v>41</v>
+      </c>
+      <c r="D119" t="s">
+        <v>403</v>
+      </c>
+      <c r="E119" t="s">
+        <v>389</v>
+      </c>
+      <c r="F119" t="s">
+        <v>42</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="H119" t="s">
+        <v>14</v>
+      </c>
+      <c r="I119" t="s">
+        <v>474</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>455</v>
+      </c>
+      <c r="B120" t="s">
+        <v>409</v>
+      </c>
+      <c r="C120" t="s">
+        <v>41</v>
+      </c>
+      <c r="D120" t="s">
+        <v>400</v>
+      </c>
+      <c r="E120" t="s">
+        <v>389</v>
+      </c>
+      <c r="F120" t="s">
+        <v>52</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="H120" t="s">
+        <v>14</v>
+      </c>
+      <c r="I120" t="s">
+        <v>474</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>456</v>
+      </c>
+      <c r="B121" t="s">
+        <v>411</v>
+      </c>
+      <c r="C121" t="s">
+        <v>41</v>
+      </c>
+      <c r="D121" t="s">
+        <v>403</v>
+      </c>
+      <c r="E121" t="s">
+        <v>389</v>
+      </c>
+      <c r="F121" t="s">
+        <v>52</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="H121" t="s">
+        <v>14</v>
+      </c>
+      <c r="I121" t="s">
+        <v>474</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>457</v>
+      </c>
+      <c r="B122" t="s">
+        <v>413</v>
+      </c>
+      <c r="C122" t="s">
+        <v>41</v>
+      </c>
+      <c r="D122" t="s">
+        <v>400</v>
+      </c>
+      <c r="E122" t="s">
+        <v>389</v>
+      </c>
+      <c r="F122" t="s">
+        <v>52</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H122" t="s">
+        <v>14</v>
+      </c>
+      <c r="I122" t="s">
+        <v>474</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>458</v>
+      </c>
+      <c r="B123" t="s">
+        <v>415</v>
+      </c>
+      <c r="C123" t="s">
+        <v>41</v>
+      </c>
+      <c r="D123" t="s">
+        <v>403</v>
+      </c>
+      <c r="E123" t="s">
+        <v>389</v>
+      </c>
+      <c r="F123" t="s">
+        <v>52</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="H123" t="s">
+        <v>14</v>
+      </c>
+      <c r="I123" t="s">
+        <v>474</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>459</v>
+      </c>
+      <c r="B124" t="s">
+        <v>417</v>
+      </c>
+      <c r="D124" t="s">
+        <v>418</v>
+      </c>
+      <c r="E124" t="s">
+        <v>389</v>
+      </c>
+      <c r="F124" t="s">
+        <v>13</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="H124" t="s">
+        <v>14</v>
+      </c>
+      <c r="I124" t="s">
+        <v>474</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>460</v>
+      </c>
+      <c r="B125" t="s">
+        <v>420</v>
+      </c>
+      <c r="D125" t="s">
+        <v>421</v>
+      </c>
+      <c r="E125" t="s">
+        <v>389</v>
+      </c>
+      <c r="F125" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H125" t="s">
+        <v>14</v>
+      </c>
+      <c r="I125" t="s">
+        <v>474</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>461</v>
+      </c>
+      <c r="B126" t="s">
+        <v>399</v>
+      </c>
+      <c r="D126" t="s">
+        <v>423</v>
+      </c>
+      <c r="E126" t="s">
+        <v>389</v>
+      </c>
+      <c r="F126" t="s">
+        <v>20</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H126" t="s">
+        <v>14</v>
+      </c>
+      <c r="I126" t="s">
+        <v>474</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>462</v>
+      </c>
+      <c r="B127" t="s">
+        <v>402</v>
+      </c>
+      <c r="D127" t="s">
+        <v>425</v>
+      </c>
+      <c r="E127" t="s">
+        <v>389</v>
+      </c>
+      <c r="F127" t="s">
+        <v>20</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H127" t="s">
+        <v>14</v>
+      </c>
+      <c r="I127" t="s">
+        <v>474</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>463</v>
+      </c>
+      <c r="B128" t="s">
+        <v>426</v>
+      </c>
+      <c r="D128" t="s">
+        <v>423</v>
+      </c>
+      <c r="E128" t="s">
+        <v>389</v>
+      </c>
+      <c r="F128" t="s">
+        <v>49</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H128" t="s">
+        <v>14</v>
+      </c>
+      <c r="I128" t="s">
+        <v>474</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>464</v>
+      </c>
+      <c r="B129" t="s">
+        <v>428</v>
+      </c>
+      <c r="D129" t="s">
+        <v>425</v>
+      </c>
+      <c r="E129" t="s">
+        <v>389</v>
+      </c>
+      <c r="F129" t="s">
+        <v>49</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="H129" t="s">
+        <v>14</v>
+      </c>
+      <c r="I129" t="s">
+        <v>474</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>465</v>
+      </c>
+      <c r="B130" t="s">
+        <v>430</v>
+      </c>
+      <c r="D130" t="s">
+        <v>423</v>
+      </c>
+      <c r="E130" t="s">
+        <v>389</v>
+      </c>
+      <c r="F130" t="s">
+        <v>52</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="H130" t="s">
+        <v>14</v>
+      </c>
+      <c r="I130" t="s">
+        <v>474</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>466</v>
+      </c>
+      <c r="B131" t="s">
+        <v>432</v>
+      </c>
+      <c r="D131" t="s">
+        <v>425</v>
+      </c>
+      <c r="E131" t="s">
+        <v>389</v>
+      </c>
+      <c r="F131" t="s">
+        <v>52</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="H131" t="s">
+        <v>14</v>
+      </c>
+      <c r="I131" t="s">
+        <v>474</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>467</v>
+      </c>
+      <c r="B132" t="s">
+        <v>413</v>
+      </c>
+      <c r="D132" t="s">
+        <v>423</v>
+      </c>
+      <c r="E132" t="s">
+        <v>389</v>
+      </c>
+      <c r="F132" t="s">
+        <v>52</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="H132" t="s">
+        <v>14</v>
+      </c>
+      <c r="I132" t="s">
+        <v>474</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>468</v>
+      </c>
+      <c r="B133" t="s">
+        <v>415</v>
+      </c>
+      <c r="D133" t="s">
+        <v>425</v>
+      </c>
+      <c r="E133" t="s">
+        <v>389</v>
+      </c>
+      <c r="F133" t="s">
+        <v>52</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="H133" t="s">
+        <v>14</v>
+      </c>
+      <c r="I133" t="s">
+        <v>474</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>469</v>
+      </c>
+      <c r="B134" t="s">
+        <v>436</v>
+      </c>
+      <c r="D134" t="s">
+        <v>437</v>
+      </c>
+      <c r="E134" t="s">
+        <v>389</v>
+      </c>
+      <c r="F134" t="s">
+        <v>69</v>
+      </c>
+      <c r="G134" t="s">
+        <v>438</v>
+      </c>
+      <c r="H134" t="s">
+        <v>14</v>
+      </c>
+      <c r="I134" t="s">
+        <v>474</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>470</v>
+      </c>
+      <c r="B135" t="s">
+        <v>439</v>
+      </c>
+      <c r="D135" t="s">
+        <v>440</v>
+      </c>
+      <c r="E135" t="s">
+        <v>389</v>
+      </c>
+      <c r="F135" t="s">
+        <v>13</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="H135" t="s">
+        <v>14</v>
+      </c>
+      <c r="I135" t="s">
+        <v>474</v>
+      </c>
+      <c r="K135" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>471</v>
+      </c>
+      <c r="B136" t="s">
+        <v>442</v>
+      </c>
+      <c r="D136" t="s">
+        <v>443</v>
+      </c>
+      <c r="E136" t="s">
+        <v>389</v>
+      </c>
+      <c r="F136" t="s">
+        <v>20</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="H136" t="s">
+        <v>14</v>
+      </c>
+      <c r="I136" t="s">
+        <v>474</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>472</v>
+      </c>
+      <c r="B137" t="s">
+        <v>445</v>
+      </c>
+      <c r="D137" t="s">
+        <v>446</v>
+      </c>
+      <c r="E137" t="s">
+        <v>389</v>
+      </c>
+      <c r="F137" t="s">
+        <v>13</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="H137" t="s">
+        <v>14</v>
+      </c>
+      <c r="I137" t="s">
+        <v>474</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>112</v>
+      </c>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" t="s">
+        <v>41</v>
+      </c>
+      <c r="D138" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" t="s">
+        <v>13</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H138" t="s">
+        <v>14</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K138" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>113</v>
+      </c>
+      <c r="B139" t="s">
+        <v>22</v>
+      </c>
+      <c r="C139" t="s">
+        <v>41</v>
+      </c>
+      <c r="D139" t="s">
+        <v>27</v>
+      </c>
+      <c r="F139" t="s">
+        <v>13</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H139" t="s">
+        <v>14</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K139" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>28</v>
+      </c>
+      <c r="B140" t="s">
+        <v>23</v>
+      </c>
+      <c r="C140" t="s">
+        <v>41</v>
+      </c>
+      <c r="D140" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="F140" t="s">
+        <v>13</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H140" t="s">
+        <v>14</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K140" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>114</v>
+      </c>
+      <c r="B141" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141" t="s">
+        <v>41</v>
+      </c>
+      <c r="D141" t="s">
+        <v>26</v>
+      </c>
+      <c r="F141" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H141" t="s">
+        <v>14</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K141" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>115</v>
+      </c>
+      <c r="B142" t="s">
+        <v>19</v>
+      </c>
+      <c r="C142" t="s">
+        <v>41</v>
+      </c>
+      <c r="D142" t="s">
+        <v>34</v>
+      </c>
+      <c r="F142" t="s">
+        <v>20</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H142" t="s">
+        <v>14</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K142" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>116</v>
+      </c>
+      <c r="B143" t="s">
+        <v>38</v>
+      </c>
+      <c r="C143" t="s">
+        <v>41</v>
+      </c>
+      <c r="D143" t="s">
+        <v>35</v>
+      </c>
+      <c r="F143" t="s">
+        <v>20</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H143" t="s">
+        <v>14</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>117</v>
+      </c>
+      <c r="B144" t="s">
+        <v>45</v>
+      </c>
+      <c r="C144" t="s">
+        <v>41</v>
+      </c>
+      <c r="D144" t="s">
+        <v>34</v>
+      </c>
+      <c r="F144" t="s">
+        <v>42</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H144" t="s">
+        <v>14</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>118</v>
+      </c>
+      <c r="B145" t="s">
+        <v>46</v>
+      </c>
+      <c r="C145" t="s">
+        <v>41</v>
+      </c>
+      <c r="D145" t="s">
+        <v>35</v>
+      </c>
+      <c r="F145" t="s">
+        <v>42</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H145" t="s">
+        <v>14</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K145" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>119</v>
+      </c>
+      <c r="B146" t="s">
+        <v>61</v>
+      </c>
+      <c r="C146" t="s">
+        <v>41</v>
+      </c>
+      <c r="D146" t="s">
+        <v>34</v>
+      </c>
+      <c r="F146" t="s">
+        <v>52</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H146" t="s">
+        <v>14</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>120</v>
+      </c>
+      <c r="B147" t="s">
+        <v>62</v>
+      </c>
+      <c r="C147" t="s">
+        <v>41</v>
+      </c>
+      <c r="D147" t="s">
+        <v>35</v>
+      </c>
+      <c r="F147" t="s">
+        <v>52</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H147" t="s">
+        <v>14</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>121</v>
+      </c>
+      <c r="B148" t="s">
+        <v>53</v>
+      </c>
+      <c r="C148" t="s">
+        <v>41</v>
+      </c>
+      <c r="D148" t="s">
+        <v>34</v>
+      </c>
+      <c r="F148" t="s">
+        <v>52</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H148" t="s">
+        <v>14</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>122</v>
+      </c>
+      <c r="B149" t="s">
+        <v>54</v>
+      </c>
+      <c r="C149" t="s">
+        <v>41</v>
+      </c>
+      <c r="D149" t="s">
+        <v>35</v>
+      </c>
+      <c r="F149" t="s">
+        <v>52</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H149" t="s">
+        <v>14</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>123</v>
+      </c>
+      <c r="B150" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="D150" t="s">
         <v>18</v>
+      </c>
+      <c r="F150" t="s">
+        <v>13</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H150" t="s">
+        <v>14</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>124</v>
+      </c>
+      <c r="B151" t="s">
+        <v>39</v>
+      </c>
+      <c r="D151" t="s">
+        <v>36</v>
+      </c>
+      <c r="F151" t="s">
+        <v>13</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H151" t="s">
+        <v>14</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K151" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>125</v>
+      </c>
+      <c r="B152" t="s">
+        <v>19</v>
+      </c>
+      <c r="D152" t="s">
+        <v>21</v>
+      </c>
+      <c r="F152" t="s">
+        <v>20</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H152" t="s">
+        <v>14</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>126</v>
+      </c>
+      <c r="B153" t="s">
+        <v>38</v>
+      </c>
+      <c r="D153" t="s">
+        <v>40</v>
+      </c>
+      <c r="F153" t="s">
+        <v>20</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H153" t="s">
+        <v>14</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>127</v>
+      </c>
+      <c r="B154" t="s">
+        <v>47</v>
+      </c>
+      <c r="D154" t="s">
+        <v>21</v>
+      </c>
+      <c r="F154" t="s">
+        <v>49</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H154" t="s">
+        <v>14</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>128</v>
+      </c>
+      <c r="B155" t="s">
+        <v>48</v>
+      </c>
+      <c r="D155" t="s">
+        <v>40</v>
+      </c>
+      <c r="F155" t="s">
+        <v>49</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H155" t="s">
+        <v>14</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>129</v>
+      </c>
+      <c r="B156" t="s">
+        <v>57</v>
+      </c>
+      <c r="D156" t="s">
+        <v>21</v>
+      </c>
+      <c r="F156" t="s">
+        <v>52</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H156" t="s">
+        <v>14</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>130</v>
+      </c>
+      <c r="B157" t="s">
+        <v>58</v>
+      </c>
+      <c r="D157" t="s">
+        <v>40</v>
+      </c>
+      <c r="F157" t="s">
+        <v>52</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H157" t="s">
+        <v>14</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K157" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>131</v>
+      </c>
+      <c r="B158" t="s">
+        <v>53</v>
+      </c>
+      <c r="D158" t="s">
+        <v>21</v>
+      </c>
+      <c r="F158" t="s">
+        <v>52</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H158" t="s">
+        <v>14</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K158" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>132</v>
+      </c>
+      <c r="B159" t="s">
+        <v>54</v>
+      </c>
+      <c r="D159" t="s">
+        <v>40</v>
+      </c>
+      <c r="F159" t="s">
+        <v>52</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H159" t="s">
+        <v>14</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>133</v>
+      </c>
+      <c r="B160" t="s">
+        <v>67</v>
+      </c>
+      <c r="D160" t="s">
+        <v>68</v>
+      </c>
+      <c r="F160" t="s">
+        <v>69</v>
+      </c>
+      <c r="G160" t="s">
+        <v>241</v>
+      </c>
+      <c r="H160" t="s">
+        <v>14</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>134</v>
+      </c>
+      <c r="B161" t="s">
+        <v>70</v>
+      </c>
+      <c r="D161" t="s">
+        <v>71</v>
+      </c>
+      <c r="F161" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H161" t="s">
+        <v>14</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K161" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>135</v>
+      </c>
+      <c r="B162" t="s">
+        <v>76</v>
+      </c>
+      <c r="D162" t="s">
+        <v>77</v>
+      </c>
+      <c r="F162" t="s">
+        <v>20</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H162" t="s">
+        <v>14</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>136</v>
+      </c>
+      <c r="B163" t="s">
+        <v>79</v>
+      </c>
+      <c r="D163" t="s">
+        <v>80</v>
+      </c>
+      <c r="F163" t="s">
+        <v>13</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H163" t="s">
+        <v>14</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K163" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>231</v>
+      </c>
+      <c r="B164" t="s">
+        <v>82</v>
+      </c>
+      <c r="D164" t="s">
+        <v>83</v>
+      </c>
+      <c r="F164" t="s">
+        <v>84</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H164" t="s">
+        <v>14</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K164" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>233</v>
+      </c>
+      <c r="B165" t="s">
+        <v>236</v>
+      </c>
+      <c r="D165" t="s">
+        <v>234</v>
+      </c>
+      <c r="F165" t="s">
+        <v>84</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H165" t="s">
+        <v>14</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>232</v>
+      </c>
+      <c r="B166" t="s">
+        <v>237</v>
+      </c>
+      <c r="D166" t="s">
+        <v>235</v>
+      </c>
+      <c r="F166" t="s">
+        <v>84</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H166" t="s">
+        <v>14</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K166" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>111</v>
+      </c>
+      <c r="B167" t="s">
+        <v>182</v>
+      </c>
+      <c r="C167" t="s">
+        <v>41</v>
+      </c>
+      <c r="D167" t="s">
+        <v>245</v>
+      </c>
+      <c r="E167" t="s">
+        <v>85</v>
+      </c>
+      <c r="F167" t="s">
+        <v>13</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H167" t="s">
+        <v>14</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K167" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>137</v>
+      </c>
+      <c r="B168" t="s">
+        <v>161</v>
+      </c>
+      <c r="C168" t="s">
+        <v>41</v>
+      </c>
+      <c r="D168" t="s">
+        <v>246</v>
+      </c>
+      <c r="E168" t="s">
+        <v>85</v>
+      </c>
+      <c r="F168" t="s">
+        <v>13</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H168" t="s">
+        <v>14</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K168" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>28</v>
+      </c>
+      <c r="B169" t="s">
+        <v>162</v>
+      </c>
+      <c r="C169" t="s">
+        <v>41</v>
+      </c>
+      <c r="D169" t="s">
+        <v>247</v>
+      </c>
+      <c r="E169" t="s">
+        <v>85</v>
+      </c>
+      <c r="F169" t="s">
+        <v>13</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H169" t="s">
+        <v>14</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K169" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>138</v>
+      </c>
+      <c r="B170" t="s">
+        <v>163</v>
+      </c>
+      <c r="C170" t="s">
+        <v>41</v>
+      </c>
+      <c r="D170" t="s">
+        <v>248</v>
+      </c>
+      <c r="E170" t="s">
+        <v>85</v>
+      </c>
+      <c r="F170" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H170" t="s">
+        <v>14</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K170" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>139</v>
+      </c>
+      <c r="B171" t="s">
+        <v>164</v>
+      </c>
+      <c r="C171" t="s">
+        <v>41</v>
+      </c>
+      <c r="D171" t="s">
+        <v>249</v>
+      </c>
+      <c r="E171" t="s">
+        <v>85</v>
+      </c>
+      <c r="F171" t="s">
+        <v>20</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H171" t="s">
+        <v>14</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K171" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>140</v>
+      </c>
+      <c r="B172" t="s">
+        <v>165</v>
+      </c>
+      <c r="C172" t="s">
+        <v>41</v>
+      </c>
+      <c r="D172" t="s">
+        <v>250</v>
+      </c>
+      <c r="E172" t="s">
+        <v>85</v>
+      </c>
+      <c r="F172" t="s">
+        <v>20</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H172" t="s">
+        <v>14</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K172" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>141</v>
+      </c>
+      <c r="B173" t="s">
+        <v>166</v>
+      </c>
+      <c r="C173" t="s">
+        <v>41</v>
+      </c>
+      <c r="D173" t="s">
+        <v>249</v>
+      </c>
+      <c r="E173" t="s">
+        <v>85</v>
+      </c>
+      <c r="F173" t="s">
+        <v>42</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H173" t="s">
+        <v>14</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>142</v>
+      </c>
+      <c r="B174" t="s">
+        <v>167</v>
+      </c>
+      <c r="C174" t="s">
+        <v>41</v>
+      </c>
+      <c r="D174" t="s">
+        <v>250</v>
+      </c>
+      <c r="E174" t="s">
+        <v>85</v>
+      </c>
+      <c r="F174" t="s">
+        <v>42</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H174" t="s">
+        <v>14</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>143</v>
+      </c>
+      <c r="B175" t="s">
+        <v>168</v>
+      </c>
+      <c r="C175" t="s">
+        <v>41</v>
+      </c>
+      <c r="D175" t="s">
+        <v>249</v>
+      </c>
+      <c r="E175" t="s">
+        <v>85</v>
+      </c>
+      <c r="F175" t="s">
+        <v>52</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H175" t="s">
+        <v>14</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K175" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>144</v>
+      </c>
+      <c r="B176" t="s">
+        <v>169</v>
+      </c>
+      <c r="C176" t="s">
+        <v>41</v>
+      </c>
+      <c r="D176" t="s">
+        <v>250</v>
+      </c>
+      <c r="E176" t="s">
+        <v>85</v>
+      </c>
+      <c r="F176" t="s">
+        <v>52</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H176" t="s">
+        <v>14</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K176" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>145</v>
+      </c>
+      <c r="B177" t="s">
+        <v>170</v>
+      </c>
+      <c r="C177" t="s">
+        <v>41</v>
+      </c>
+      <c r="D177" t="s">
+        <v>249</v>
+      </c>
+      <c r="E177" t="s">
+        <v>85</v>
+      </c>
+      <c r="F177" t="s">
+        <v>52</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H177" t="s">
+        <v>14</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K177" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>146</v>
+      </c>
+      <c r="B178" t="s">
+        <v>171</v>
+      </c>
+      <c r="C178" t="s">
+        <v>41</v>
+      </c>
+      <c r="D178" t="s">
+        <v>250</v>
+      </c>
+      <c r="E178" t="s">
+        <v>85</v>
+      </c>
+      <c r="F178" t="s">
+        <v>52</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H178" t="s">
+        <v>14</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K178" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>147</v>
+      </c>
+      <c r="B179" t="s">
+        <v>172</v>
+      </c>
+      <c r="D179" t="s">
+        <v>251</v>
+      </c>
+      <c r="E179" t="s">
+        <v>85</v>
+      </c>
+      <c r="F179" t="s">
+        <v>13</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H179" t="s">
+        <v>14</v>
+      </c>
+      <c r="I179" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K179" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>148</v>
+      </c>
+      <c r="B180" t="s">
+        <v>173</v>
+      </c>
+      <c r="D180" t="s">
+        <v>252</v>
+      </c>
+      <c r="E180" t="s">
+        <v>85</v>
+      </c>
+      <c r="F180" t="s">
+        <v>13</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H180" t="s">
+        <v>14</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K180" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>149</v>
+      </c>
+      <c r="B181" t="s">
+        <v>164</v>
+      </c>
+      <c r="D181" t="s">
+        <v>253</v>
+      </c>
+      <c r="E181" t="s">
+        <v>85</v>
+      </c>
+      <c r="F181" t="s">
+        <v>20</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H181" t="s">
+        <v>14</v>
+      </c>
+      <c r="I181" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K181" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>150</v>
+      </c>
+      <c r="B182" t="s">
+        <v>165</v>
+      </c>
+      <c r="D182" t="s">
+        <v>254</v>
+      </c>
+      <c r="E182" t="s">
+        <v>85</v>
+      </c>
+      <c r="F182" t="s">
+        <v>20</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H182" t="s">
+        <v>14</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K182" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>151</v>
+      </c>
+      <c r="B183" t="s">
+        <v>174</v>
+      </c>
+      <c r="D183" t="s">
+        <v>253</v>
+      </c>
+      <c r="E183" t="s">
+        <v>85</v>
+      </c>
+      <c r="F183" t="s">
+        <v>49</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H183" t="s">
+        <v>14</v>
+      </c>
+      <c r="I183" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K183" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>152</v>
+      </c>
+      <c r="B184" t="s">
+        <v>175</v>
+      </c>
+      <c r="D184" t="s">
+        <v>254</v>
+      </c>
+      <c r="E184" t="s">
+        <v>85</v>
+      </c>
+      <c r="F184" t="s">
+        <v>49</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H184" t="s">
+        <v>14</v>
+      </c>
+      <c r="I184" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K184" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>153</v>
+      </c>
+      <c r="B185" t="s">
+        <v>176</v>
+      </c>
+      <c r="D185" t="s">
+        <v>253</v>
+      </c>
+      <c r="E185" t="s">
+        <v>85</v>
+      </c>
+      <c r="F185" t="s">
+        <v>52</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H185" t="s">
+        <v>14</v>
+      </c>
+      <c r="I185" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K185" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>154</v>
+      </c>
+      <c r="B186" t="s">
+        <v>177</v>
+      </c>
+      <c r="D186" t="s">
+        <v>254</v>
+      </c>
+      <c r="E186" t="s">
+        <v>85</v>
+      </c>
+      <c r="F186" t="s">
+        <v>52</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H186" t="s">
+        <v>14</v>
+      </c>
+      <c r="I186" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K186" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>155</v>
+      </c>
+      <c r="B187" t="s">
+        <v>170</v>
+      </c>
+      <c r="D187" t="s">
+        <v>253</v>
+      </c>
+      <c r="E187" t="s">
+        <v>85</v>
+      </c>
+      <c r="F187" t="s">
+        <v>52</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H187" t="s">
+        <v>14</v>
+      </c>
+      <c r="I187" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K187" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>156</v>
+      </c>
+      <c r="B188" t="s">
+        <v>171</v>
+      </c>
+      <c r="D188" t="s">
+        <v>254</v>
+      </c>
+      <c r="E188" t="s">
+        <v>85</v>
+      </c>
+      <c r="F188" t="s">
+        <v>52</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H188" t="s">
+        <v>14</v>
+      </c>
+      <c r="I188" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K188" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>157</v>
+      </c>
+      <c r="B189" t="s">
+        <v>178</v>
+      </c>
+      <c r="D189" t="s">
+        <v>255</v>
+      </c>
+      <c r="E189" t="s">
+        <v>85</v>
+      </c>
+      <c r="F189" t="s">
+        <v>69</v>
+      </c>
+      <c r="G189" t="s">
+        <v>107</v>
+      </c>
+      <c r="H189" t="s">
+        <v>14</v>
+      </c>
+      <c r="I189" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K189" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>158</v>
+      </c>
+      <c r="B190" t="s">
+        <v>179</v>
+      </c>
+      <c r="D190" t="s">
+        <v>256</v>
+      </c>
+      <c r="E190" t="s">
+        <v>85</v>
+      </c>
+      <c r="F190" t="s">
+        <v>13</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H190" t="s">
+        <v>14</v>
+      </c>
+      <c r="I190" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K190" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>159</v>
+      </c>
+      <c r="B191" t="s">
+        <v>180</v>
+      </c>
+      <c r="D191" t="s">
+        <v>257</v>
+      </c>
+      <c r="E191" t="s">
+        <v>85</v>
+      </c>
+      <c r="F191" t="s">
+        <v>20</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H191" t="s">
+        <v>14</v>
+      </c>
+      <c r="I191" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K191" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>160</v>
+      </c>
+      <c r="B192" t="s">
+        <v>181</v>
+      </c>
+      <c r="D192" t="s">
+        <v>258</v>
+      </c>
+      <c r="E192" t="s">
+        <v>85</v>
+      </c>
+      <c r="F192" t="s">
+        <v>13</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H192" t="s">
+        <v>14</v>
+      </c>
+      <c r="I192" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K192" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>231</v>
+      </c>
+      <c r="B193" t="s">
+        <v>82</v>
+      </c>
+      <c r="D193" t="s">
+        <v>259</v>
+      </c>
+      <c r="E193" t="s">
+        <v>85</v>
+      </c>
+      <c r="F193" t="s">
+        <v>84</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H193" t="s">
+        <v>14</v>
+      </c>
+      <c r="I193" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K193" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>233</v>
+      </c>
+      <c r="B194" t="s">
+        <v>236</v>
+      </c>
+      <c r="D194" t="s">
+        <v>260</v>
+      </c>
+      <c r="E194" t="s">
+        <v>85</v>
+      </c>
+      <c r="F194" t="s">
+        <v>84</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H194" t="s">
+        <v>14</v>
+      </c>
+      <c r="I194" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K194" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>232</v>
+      </c>
+      <c r="B195" t="s">
+        <v>237</v>
+      </c>
+      <c r="D195" t="s">
+        <v>261</v>
+      </c>
+      <c r="E195" t="s">
+        <v>85</v>
+      </c>
+      <c r="F195" t="s">
+        <v>84</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="H195" t="s">
+        <v>14</v>
+      </c>
+      <c r="I195" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K195" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>276</v>
+      </c>
+      <c r="B196" t="s">
+        <v>209</v>
+      </c>
+      <c r="C196" t="s">
+        <v>41</v>
+      </c>
+      <c r="D196" t="s">
+        <v>262</v>
+      </c>
+      <c r="E196" t="s">
+        <v>183</v>
+      </c>
+      <c r="F196" t="s">
+        <v>13</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H196" t="s">
+        <v>14</v>
+      </c>
+      <c r="I196" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K196" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>277</v>
+      </c>
+      <c r="B197" t="s">
+        <v>210</v>
+      </c>
+      <c r="C197" t="s">
+        <v>41</v>
+      </c>
+      <c r="D197" t="s">
+        <v>263</v>
+      </c>
+      <c r="E197" t="s">
+        <v>183</v>
+      </c>
+      <c r="F197" t="s">
+        <v>13</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H197" t="s">
+        <v>14</v>
+      </c>
+      <c r="I197" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K197" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>28</v>
+      </c>
+      <c r="B198" t="s">
+        <v>211</v>
+      </c>
+      <c r="C198" t="s">
+        <v>41</v>
+      </c>
+      <c r="D198" t="s">
+        <v>264</v>
+      </c>
+      <c r="E198" t="s">
+        <v>183</v>
+      </c>
+      <c r="F198" t="s">
+        <v>13</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H198" t="s">
+        <v>14</v>
+      </c>
+      <c r="I198" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K198" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>278</v>
+      </c>
+      <c r="B199" t="s">
+        <v>212</v>
+      </c>
+      <c r="C199" t="s">
+        <v>41</v>
+      </c>
+      <c r="D199" t="s">
+        <v>265</v>
+      </c>
+      <c r="E199" t="s">
+        <v>183</v>
+      </c>
+      <c r="F199" t="s">
+        <v>13</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H199" t="s">
+        <v>14</v>
+      </c>
+      <c r="I199" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K199" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>279</v>
+      </c>
+      <c r="B200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C200" t="s">
+        <v>41</v>
+      </c>
+      <c r="D200" t="s">
+        <v>266</v>
+      </c>
+      <c r="E200" t="s">
+        <v>183</v>
+      </c>
+      <c r="F200" t="s">
+        <v>20</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H200" t="s">
+        <v>14</v>
+      </c>
+      <c r="I200" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K200" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>280</v>
+      </c>
+      <c r="B201" t="s">
+        <v>214</v>
+      </c>
+      <c r="C201" t="s">
+        <v>41</v>
+      </c>
+      <c r="D201" t="s">
+        <v>267</v>
+      </c>
+      <c r="E201" t="s">
+        <v>183</v>
+      </c>
+      <c r="F201" t="s">
+        <v>20</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H201" t="s">
+        <v>14</v>
+      </c>
+      <c r="I201" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K201" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>281</v>
+      </c>
+      <c r="B202" t="s">
+        <v>215</v>
+      </c>
+      <c r="C202" t="s">
+        <v>41</v>
+      </c>
+      <c r="D202" t="s">
+        <v>266</v>
+      </c>
+      <c r="E202" t="s">
+        <v>183</v>
+      </c>
+      <c r="F202" t="s">
+        <v>42</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H202" t="s">
+        <v>14</v>
+      </c>
+      <c r="I202" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K202" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>282</v>
+      </c>
+      <c r="B203" t="s">
+        <v>216</v>
+      </c>
+      <c r="C203" t="s">
+        <v>41</v>
+      </c>
+      <c r="D203" t="s">
+        <v>267</v>
+      </c>
+      <c r="E203" t="s">
+        <v>183</v>
+      </c>
+      <c r="F203" t="s">
+        <v>42</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H203" t="s">
+        <v>14</v>
+      </c>
+      <c r="I203" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K203" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>283</v>
+      </c>
+      <c r="B204" t="s">
+        <v>217</v>
+      </c>
+      <c r="C204" t="s">
+        <v>41</v>
+      </c>
+      <c r="D204" t="s">
+        <v>266</v>
+      </c>
+      <c r="E204" t="s">
+        <v>183</v>
+      </c>
+      <c r="F204" t="s">
+        <v>52</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H204" t="s">
+        <v>14</v>
+      </c>
+      <c r="I204" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K204" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>284</v>
+      </c>
+      <c r="B205" t="s">
+        <v>218</v>
+      </c>
+      <c r="C205" t="s">
+        <v>41</v>
+      </c>
+      <c r="D205" t="s">
+        <v>267</v>
+      </c>
+      <c r="E205" t="s">
+        <v>183</v>
+      </c>
+      <c r="F205" t="s">
+        <v>52</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H205" t="s">
+        <v>14</v>
+      </c>
+      <c r="I205" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K205" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>285</v>
+      </c>
+      <c r="B206" t="s">
+        <v>219</v>
+      </c>
+      <c r="C206" t="s">
+        <v>41</v>
+      </c>
+      <c r="D206" t="s">
+        <v>266</v>
+      </c>
+      <c r="E206" t="s">
+        <v>183</v>
+      </c>
+      <c r="F206" t="s">
+        <v>52</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H206" t="s">
+        <v>14</v>
+      </c>
+      <c r="I206" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K206" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>286</v>
+      </c>
+      <c r="B207" t="s">
+        <v>220</v>
+      </c>
+      <c r="C207" t="s">
+        <v>41</v>
+      </c>
+      <c r="D207" t="s">
+        <v>267</v>
+      </c>
+      <c r="E207" t="s">
+        <v>183</v>
+      </c>
+      <c r="F207" t="s">
+        <v>52</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H207" t="s">
+        <v>14</v>
+      </c>
+      <c r="I207" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K207" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>287</v>
+      </c>
+      <c r="B208" t="s">
+        <v>221</v>
+      </c>
+      <c r="D208" t="s">
+        <v>268</v>
+      </c>
+      <c r="E208" t="s">
+        <v>183</v>
+      </c>
+      <c r="F208" t="s">
+        <v>13</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H208" t="s">
+        <v>14</v>
+      </c>
+      <c r="I208" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K208" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>288</v>
+      </c>
+      <c r="B209" t="s">
+        <v>222</v>
+      </c>
+      <c r="D209" t="s">
+        <v>269</v>
+      </c>
+      <c r="E209" t="s">
+        <v>183</v>
+      </c>
+      <c r="F209" t="s">
+        <v>13</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H209" t="s">
+        <v>14</v>
+      </c>
+      <c r="I209" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K209" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>289</v>
+      </c>
+      <c r="B210" t="s">
+        <v>213</v>
+      </c>
+      <c r="D210" t="s">
+        <v>270</v>
+      </c>
+      <c r="E210" t="s">
+        <v>183</v>
+      </c>
+      <c r="F210" t="s">
+        <v>20</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H210" t="s">
+        <v>14</v>
+      </c>
+      <c r="I210" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K210" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>290</v>
+      </c>
+      <c r="B211" t="s">
+        <v>214</v>
+      </c>
+      <c r="D211" t="s">
+        <v>271</v>
+      </c>
+      <c r="E211" t="s">
+        <v>183</v>
+      </c>
+      <c r="F211" t="s">
+        <v>20</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H211" t="s">
+        <v>14</v>
+      </c>
+      <c r="I211" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K211" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>291</v>
+      </c>
+      <c r="B212" t="s">
+        <v>223</v>
+      </c>
+      <c r="D212" t="s">
+        <v>270</v>
+      </c>
+      <c r="E212" t="s">
+        <v>183</v>
+      </c>
+      <c r="F212" t="s">
+        <v>49</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H212" t="s">
+        <v>14</v>
+      </c>
+      <c r="I212" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K212" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>292</v>
+      </c>
+      <c r="B213" t="s">
+        <v>224</v>
+      </c>
+      <c r="D213" t="s">
+        <v>271</v>
+      </c>
+      <c r="E213" t="s">
+        <v>183</v>
+      </c>
+      <c r="F213" t="s">
+        <v>49</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H213" t="s">
+        <v>14</v>
+      </c>
+      <c r="I213" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K213" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>293</v>
+      </c>
+      <c r="B214" t="s">
+        <v>225</v>
+      </c>
+      <c r="D214" t="s">
+        <v>270</v>
+      </c>
+      <c r="E214" t="s">
+        <v>183</v>
+      </c>
+      <c r="F214" t="s">
+        <v>52</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H214" t="s">
+        <v>14</v>
+      </c>
+      <c r="I214" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K214" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>294</v>
+      </c>
+      <c r="B215" t="s">
+        <v>226</v>
+      </c>
+      <c r="D215" t="s">
+        <v>271</v>
+      </c>
+      <c r="E215" t="s">
+        <v>183</v>
+      </c>
+      <c r="F215" t="s">
+        <v>52</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H215" t="s">
+        <v>14</v>
+      </c>
+      <c r="I215" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K215" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>295</v>
+      </c>
+      <c r="B216" t="s">
+        <v>219</v>
+      </c>
+      <c r="D216" t="s">
+        <v>270</v>
+      </c>
+      <c r="E216" t="s">
+        <v>183</v>
+      </c>
+      <c r="F216" t="s">
+        <v>52</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H216" t="s">
+        <v>14</v>
+      </c>
+      <c r="I216" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K216" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>296</v>
+      </c>
+      <c r="B217" t="s">
+        <v>220</v>
+      </c>
+      <c r="D217" t="s">
+        <v>271</v>
+      </c>
+      <c r="E217" t="s">
+        <v>183</v>
+      </c>
+      <c r="F217" t="s">
+        <v>52</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H217" t="s">
+        <v>14</v>
+      </c>
+      <c r="I217" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K217" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>297</v>
+      </c>
+      <c r="B218" t="s">
+        <v>227</v>
+      </c>
+      <c r="D218" t="s">
+        <v>272</v>
+      </c>
+      <c r="E218" t="s">
+        <v>183</v>
+      </c>
+      <c r="F218" t="s">
+        <v>69</v>
+      </c>
+      <c r="G218" t="s">
+        <v>205</v>
+      </c>
+      <c r="H218" t="s">
+        <v>14</v>
+      </c>
+      <c r="I218" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K218" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>298</v>
+      </c>
+      <c r="B219" t="s">
+        <v>228</v>
+      </c>
+      <c r="D219" t="s">
+        <v>273</v>
+      </c>
+      <c r="E219" t="s">
+        <v>183</v>
+      </c>
+      <c r="F219" t="s">
+        <v>13</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H219" t="s">
+        <v>14</v>
+      </c>
+      <c r="I219" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K219" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>299</v>
+      </c>
+      <c r="B220" t="s">
+        <v>229</v>
+      </c>
+      <c r="D220" t="s">
+        <v>274</v>
+      </c>
+      <c r="E220" t="s">
+        <v>183</v>
+      </c>
+      <c r="F220" t="s">
+        <v>20</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H220" t="s">
+        <v>14</v>
+      </c>
+      <c r="I220" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K220" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>300</v>
+      </c>
+      <c r="B221" t="s">
+        <v>230</v>
+      </c>
+      <c r="D221" t="s">
+        <v>275</v>
+      </c>
+      <c r="E221" t="s">
+        <v>183</v>
+      </c>
+      <c r="F221" t="s">
+        <v>13</v>
+      </c>
+      <c r="G221" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H221" t="s">
+        <v>14</v>
+      </c>
+      <c r="I221" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K221" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>341</v>
+      </c>
+      <c r="B222" t="s">
+        <v>366</v>
+      </c>
+      <c r="C222" t="s">
+        <v>41</v>
+      </c>
+      <c r="D222" t="s">
+        <v>301</v>
+      </c>
+      <c r="E222" t="s">
+        <v>302</v>
+      </c>
+      <c r="F222" t="s">
+        <v>13</v>
+      </c>
+      <c r="G222" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="H222" t="s">
+        <v>14</v>
+      </c>
+      <c r="I222" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K222" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>342</v>
+      </c>
+      <c r="B223" t="s">
+        <v>367</v>
+      </c>
+      <c r="C223" t="s">
+        <v>41</v>
+      </c>
+      <c r="D223" t="s">
+        <v>304</v>
+      </c>
+      <c r="E223" t="s">
+        <v>302</v>
+      </c>
+      <c r="F223" t="s">
+        <v>13</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="H223" t="s">
+        <v>14</v>
+      </c>
+      <c r="I223" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K223" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>28</v>
+      </c>
+      <c r="B224" t="s">
+        <v>368</v>
+      </c>
+      <c r="C224" t="s">
+        <v>41</v>
+      </c>
+      <c r="D224" t="s">
+        <v>306</v>
+      </c>
+      <c r="E224" t="s">
+        <v>302</v>
+      </c>
+      <c r="F224" t="s">
+        <v>13</v>
+      </c>
+      <c r="G224" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H224" t="s">
+        <v>14</v>
+      </c>
+      <c r="I224" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K224" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>343</v>
+      </c>
+      <c r="B225" t="s">
+        <v>212</v>
+      </c>
+      <c r="C225" t="s">
+        <v>41</v>
+      </c>
+      <c r="D225" t="s">
+        <v>308</v>
+      </c>
+      <c r="E225" t="s">
+        <v>302</v>
+      </c>
+      <c r="F225" t="s">
+        <v>13</v>
+      </c>
+      <c r="G225" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H225" t="s">
+        <v>14</v>
+      </c>
+      <c r="I225" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K225" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>344</v>
+      </c>
+      <c r="B226" t="s">
+        <v>369</v>
+      </c>
+      <c r="C226" t="s">
+        <v>41</v>
+      </c>
+      <c r="D226" t="s">
+        <v>310</v>
+      </c>
+      <c r="E226" t="s">
+        <v>302</v>
+      </c>
+      <c r="F226" t="s">
+        <v>20</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="H226" t="s">
+        <v>14</v>
+      </c>
+      <c r="I226" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K226" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>345</v>
+      </c>
+      <c r="B227" t="s">
+        <v>370</v>
+      </c>
+      <c r="C227" t="s">
+        <v>41</v>
+      </c>
+      <c r="D227" t="s">
+        <v>312</v>
+      </c>
+      <c r="E227" t="s">
+        <v>302</v>
+      </c>
+      <c r="F227" t="s">
+        <v>20</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H227" t="s">
+        <v>14</v>
+      </c>
+      <c r="I227" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K227" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>346</v>
+      </c>
+      <c r="B228" t="s">
+        <v>371</v>
+      </c>
+      <c r="C228" t="s">
+        <v>41</v>
+      </c>
+      <c r="D228" t="s">
+        <v>310</v>
+      </c>
+      <c r="E228" t="s">
+        <v>302</v>
+      </c>
+      <c r="F228" t="s">
+        <v>42</v>
+      </c>
+      <c r="G228" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="H228" t="s">
+        <v>14</v>
+      </c>
+      <c r="I228" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K228" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>347</v>
+      </c>
+      <c r="B229" t="s">
+        <v>372</v>
+      </c>
+      <c r="C229" t="s">
+        <v>41</v>
+      </c>
+      <c r="D229" t="s">
+        <v>312</v>
+      </c>
+      <c r="E229" t="s">
+        <v>302</v>
+      </c>
+      <c r="F229" t="s">
+        <v>42</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="H229" t="s">
+        <v>14</v>
+      </c>
+      <c r="I229" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K229" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>348</v>
+      </c>
+      <c r="B230" t="s">
+        <v>373</v>
+      </c>
+      <c r="C230" t="s">
+        <v>41</v>
+      </c>
+      <c r="D230" t="s">
+        <v>310</v>
+      </c>
+      <c r="E230" t="s">
+        <v>302</v>
+      </c>
+      <c r="F230" t="s">
+        <v>52</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="H230" t="s">
+        <v>14</v>
+      </c>
+      <c r="I230" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K230" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>349</v>
+      </c>
+      <c r="B231" t="s">
+        <v>374</v>
+      </c>
+      <c r="C231" t="s">
+        <v>41</v>
+      </c>
+      <c r="D231" t="s">
+        <v>312</v>
+      </c>
+      <c r="E231" t="s">
+        <v>302</v>
+      </c>
+      <c r="F231" t="s">
+        <v>52</v>
+      </c>
+      <c r="G231" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H231" t="s">
+        <v>14</v>
+      </c>
+      <c r="I231" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K231" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>350</v>
+      </c>
+      <c r="B232" t="s">
+        <v>375</v>
+      </c>
+      <c r="C232" t="s">
+        <v>41</v>
+      </c>
+      <c r="D232" t="s">
+        <v>310</v>
+      </c>
+      <c r="E232" t="s">
+        <v>302</v>
+      </c>
+      <c r="F232" t="s">
+        <v>52</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="H232" t="s">
+        <v>14</v>
+      </c>
+      <c r="I232" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K232" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>351</v>
+      </c>
+      <c r="B233" t="s">
+        <v>376</v>
+      </c>
+      <c r="C233" t="s">
+        <v>41</v>
+      </c>
+      <c r="D233" t="s">
+        <v>312</v>
+      </c>
+      <c r="E233" t="s">
+        <v>302</v>
+      </c>
+      <c r="F233" t="s">
+        <v>52</v>
+      </c>
+      <c r="G233" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="H233" t="s">
+        <v>14</v>
+      </c>
+      <c r="I233" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K233" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>352</v>
+      </c>
+      <c r="B234" t="s">
+        <v>377</v>
+      </c>
+      <c r="D234" t="s">
+        <v>320</v>
+      </c>
+      <c r="E234" t="s">
+        <v>302</v>
+      </c>
+      <c r="F234" t="s">
+        <v>13</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="H234" t="s">
+        <v>14</v>
+      </c>
+      <c r="I234" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K234" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>353</v>
+      </c>
+      <c r="B235" t="s">
+        <v>378</v>
+      </c>
+      <c r="D235" t="s">
+        <v>322</v>
+      </c>
+      <c r="E235" t="s">
+        <v>302</v>
+      </c>
+      <c r="F235" t="s">
+        <v>13</v>
+      </c>
+      <c r="G235" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="H235" t="s">
+        <v>14</v>
+      </c>
+      <c r="I235" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K235" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>354</v>
+      </c>
+      <c r="B236" t="s">
+        <v>369</v>
+      </c>
+      <c r="D236" t="s">
+        <v>324</v>
+      </c>
+      <c r="E236" t="s">
+        <v>302</v>
+      </c>
+      <c r="F236" t="s">
+        <v>20</v>
+      </c>
+      <c r="G236" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H236" t="s">
+        <v>14</v>
+      </c>
+      <c r="I236" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K236" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>355</v>
+      </c>
+      <c r="B237" t="s">
+        <v>370</v>
+      </c>
+      <c r="D237" t="s">
+        <v>326</v>
+      </c>
+      <c r="E237" t="s">
+        <v>302</v>
+      </c>
+      <c r="F237" t="s">
+        <v>20</v>
+      </c>
+      <c r="G237" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H237" t="s">
+        <v>14</v>
+      </c>
+      <c r="I237" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K237" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>356</v>
+      </c>
+      <c r="B238" t="s">
+        <v>379</v>
+      </c>
+      <c r="D238" t="s">
+        <v>324</v>
+      </c>
+      <c r="E238" t="s">
+        <v>302</v>
+      </c>
+      <c r="F238" t="s">
+        <v>49</v>
+      </c>
+      <c r="G238" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H238" t="s">
+        <v>14</v>
+      </c>
+      <c r="I238" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K238" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>357</v>
+      </c>
+      <c r="B239" t="s">
+        <v>380</v>
+      </c>
+      <c r="D239" t="s">
+        <v>326</v>
+      </c>
+      <c r="E239" t="s">
+        <v>302</v>
+      </c>
+      <c r="F239" t="s">
+        <v>49</v>
+      </c>
+      <c r="G239" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H239" t="s">
+        <v>14</v>
+      </c>
+      <c r="I239" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K239" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>358</v>
+      </c>
+      <c r="B240" t="s">
+        <v>381</v>
+      </c>
+      <c r="D240" t="s">
+        <v>324</v>
+      </c>
+      <c r="E240" t="s">
+        <v>302</v>
+      </c>
+      <c r="F240" t="s">
+        <v>52</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="H240" t="s">
+        <v>14</v>
+      </c>
+      <c r="I240" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K240" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>359</v>
+      </c>
+      <c r="B241" t="s">
+        <v>382</v>
+      </c>
+      <c r="D241" t="s">
+        <v>326</v>
+      </c>
+      <c r="E241" t="s">
+        <v>302</v>
+      </c>
+      <c r="F241" t="s">
+        <v>52</v>
+      </c>
+      <c r="G241" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="H241" t="s">
+        <v>14</v>
+      </c>
+      <c r="I241" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K241" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>360</v>
+      </c>
+      <c r="B242" t="s">
+        <v>375</v>
+      </c>
+      <c r="D242" t="s">
+        <v>324</v>
+      </c>
+      <c r="E242" t="s">
+        <v>302</v>
+      </c>
+      <c r="F242" t="s">
+        <v>52</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H242" t="s">
+        <v>14</v>
+      </c>
+      <c r="I242" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K242" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>361</v>
+      </c>
+      <c r="B243" t="s">
+        <v>376</v>
+      </c>
+      <c r="D243" t="s">
+        <v>326</v>
+      </c>
+      <c r="E243" t="s">
+        <v>302</v>
+      </c>
+      <c r="F243" t="s">
+        <v>52</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="H243" t="s">
+        <v>14</v>
+      </c>
+      <c r="I243" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K243" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>362</v>
+      </c>
+      <c r="B244" t="s">
+        <v>383</v>
+      </c>
+      <c r="D244" t="s">
+        <v>333</v>
+      </c>
+      <c r="E244" t="s">
+        <v>302</v>
+      </c>
+      <c r="F244" t="s">
+        <v>69</v>
+      </c>
+      <c r="G244" t="s">
+        <v>334</v>
+      </c>
+      <c r="H244" t="s">
+        <v>14</v>
+      </c>
+      <c r="I244" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K244" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>363</v>
+      </c>
+      <c r="B245" t="s">
+        <v>384</v>
+      </c>
+      <c r="D245" t="s">
+        <v>335</v>
+      </c>
+      <c r="E245" t="s">
+        <v>302</v>
+      </c>
+      <c r="F245" t="s">
+        <v>13</v>
+      </c>
+      <c r="G245" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="H245" t="s">
+        <v>14</v>
+      </c>
+      <c r="I245" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K245" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>364</v>
+      </c>
+      <c r="B246" t="s">
+        <v>385</v>
+      </c>
+      <c r="D246" t="s">
+        <v>337</v>
+      </c>
+      <c r="E246" t="s">
+        <v>302</v>
+      </c>
+      <c r="F246" t="s">
+        <v>20</v>
+      </c>
+      <c r="G246" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H246" t="s">
+        <v>14</v>
+      </c>
+      <c r="I246" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K246" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>365</v>
+      </c>
+      <c r="B247" t="s">
+        <v>386</v>
+      </c>
+      <c r="D247" t="s">
+        <v>339</v>
+      </c>
+      <c r="E247" t="s">
+        <v>302</v>
+      </c>
+      <c r="F247" t="s">
+        <v>13</v>
+      </c>
+      <c r="G247" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H247" t="s">
+        <v>14</v>
+      </c>
+      <c r="I247" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="K247" s="2" t="s">
+        <v>473</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{3EE8CCD2-69EC-4278-AE21-D65D369CECAD}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{76FCC99B-F1FC-4090-95AB-A31441781683}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{A27A6072-8D0B-4EC8-A0C7-3EA6D6ABD9F4}"/>
+    <hyperlink ref="G14" r:id="rId2" xr:uid="{76FCC99B-F1FC-4090-95AB-A31441781683}"/>
+    <hyperlink ref="G16" r:id="rId3" xr:uid="{A27A6072-8D0B-4EC8-A0C7-3EA6D6ABD9F4}"/>
+    <hyperlink ref="G3" r:id="rId4" xr:uid="{20BB1ED5-C34E-4748-B886-E54795444B6C}"/>
+    <hyperlink ref="G4" r:id="rId5" xr:uid="{8A2CB655-6FA4-4138-A66D-615985F29357}"/>
+    <hyperlink ref="G5" r:id="rId6" xr:uid="{772767B5-33E2-4D24-B078-E9A2234FF557}"/>
+    <hyperlink ref="G6" r:id="rId7" xr:uid="{4F2A1F0E-8500-4439-8996-DFED640B8CEF}"/>
+    <hyperlink ref="G7" r:id="rId8" xr:uid="{DDDBCE71-7051-458D-BC8B-117D26FB6FAC}"/>
+    <hyperlink ref="G15" r:id="rId9" xr:uid="{04FA62B8-3E25-4C00-9C0F-F5316CAB8FDC}"/>
+    <hyperlink ref="G17" r:id="rId10" xr:uid="{A55ED7C5-F99C-44A5-BD48-373730CD2C00}"/>
+    <hyperlink ref="G8" r:id="rId11" xr:uid="{84160D21-704F-4F7A-8D8E-600670AD4090}"/>
+    <hyperlink ref="G9" r:id="rId12" xr:uid="{8A5DB7DD-1F7A-4187-9B49-341CBB921AA9}"/>
+    <hyperlink ref="G18" r:id="rId13" xr:uid="{67BA1531-DB78-46FF-96E8-6B38E7BB9FF8}"/>
+    <hyperlink ref="G19" r:id="rId14" xr:uid="{1A55A5B8-2819-4C18-8DDB-4CBCE5D55CF9}"/>
+    <hyperlink ref="G22" r:id="rId15" xr:uid="{F7684A7C-D334-4458-9AA3-A201101F71EA}"/>
+    <hyperlink ref="G23" r:id="rId16" xr:uid="{A3186681-82A6-4CE1-BFAB-F79916B161B3}"/>
+    <hyperlink ref="G20" r:id="rId17" xr:uid="{D4722470-01FC-46F1-B669-53622505DE2C}"/>
+    <hyperlink ref="G21" r:id="rId18" xr:uid="{88DA17E9-2575-41B2-B486-A0A44398559A}"/>
+    <hyperlink ref="G12" r:id="rId19" xr:uid="{E1AC1FE2-DFF2-4A79-959F-45D1C24D8C92}"/>
+    <hyperlink ref="G13" r:id="rId20" xr:uid="{B18BD72F-C4A6-4045-AE8A-7F719201BA21}"/>
+    <hyperlink ref="G10" r:id="rId21" xr:uid="{1F4594BD-452B-4A83-B2CD-98A0AFF148C7}"/>
+    <hyperlink ref="G11" r:id="rId22" xr:uid="{887A2F45-1D0F-4039-BA8F-FD6DE6BCCE65}"/>
+    <hyperlink ref="G25" r:id="rId23" xr:uid="{75921F28-6B77-45D5-87C5-554D1D35B95C}"/>
+    <hyperlink ref="G26" r:id="rId24" xr:uid="{9241829D-BF69-44C8-A31B-99A25F7AF6C1}"/>
+    <hyperlink ref="G27" r:id="rId25" xr:uid="{D034064B-F6BF-4A86-951C-466D8909946C}"/>
+    <hyperlink ref="G31" r:id="rId26" xr:uid="{A7A9F844-0CF7-43E0-9653-728377EE9088}"/>
+    <hyperlink ref="G43" r:id="rId27" xr:uid="{D72E27C9-378E-45A8-A232-E6F9DFA41DB1}"/>
+    <hyperlink ref="G45" r:id="rId28" xr:uid="{18C0E69F-3BE9-4EF5-BBCC-E507A5405FF2}"/>
+    <hyperlink ref="G32" r:id="rId29" xr:uid="{8ABD1182-1A44-4A3C-AABA-662AD43735C9}"/>
+    <hyperlink ref="G33" r:id="rId30" xr:uid="{5F532BD2-7AE3-4AAC-B171-7D9B66D1CAF2}"/>
+    <hyperlink ref="G34" r:id="rId31" xr:uid="{DA210AF8-76BF-4170-835A-768959CC681B}"/>
+    <hyperlink ref="G35" r:id="rId32" xr:uid="{EF8DF4DC-8577-45B2-9E3D-DED8779F51AF}"/>
+    <hyperlink ref="G36" r:id="rId33" xr:uid="{F98EBDA3-05BC-4A70-BE6D-8359D8132868}"/>
+    <hyperlink ref="G44" r:id="rId34" xr:uid="{BA764B75-BBD7-4944-BE4C-4FFF84F85B4E}"/>
+    <hyperlink ref="G46" r:id="rId35" xr:uid="{50A4A755-F137-4C1A-BFD5-264E350A9587}"/>
+    <hyperlink ref="G37" r:id="rId36" xr:uid="{92E68E5B-94A7-4664-AFBC-3E215203AB4D}"/>
+    <hyperlink ref="G38" r:id="rId37" xr:uid="{5862D0A8-856C-4F2A-BB5A-342564ED4434}"/>
+    <hyperlink ref="G47" r:id="rId38" xr:uid="{D1BAF795-F101-47F5-B8E0-6085D5862D92}"/>
+    <hyperlink ref="G48" r:id="rId39" xr:uid="{0D188133-9969-4BCC-915E-F268FC369981}"/>
+    <hyperlink ref="G51" r:id="rId40" xr:uid="{C3EF5C54-81F6-41F0-90EB-4B262944FBDB}"/>
+    <hyperlink ref="G52" r:id="rId41" xr:uid="{52484E64-8503-44C9-8133-12120ABAC2FA}"/>
+    <hyperlink ref="G49" r:id="rId42" xr:uid="{3221E400-DB1B-4110-8014-E2756F38EE0D}"/>
+    <hyperlink ref="G50" r:id="rId43" xr:uid="{1DFBCFFD-54D5-42AE-AFF6-32954A6D9DA7}"/>
+    <hyperlink ref="G41" r:id="rId44" xr:uid="{8A1D580A-86D4-4FAC-A96A-31A458722E11}"/>
+    <hyperlink ref="G42" r:id="rId45" xr:uid="{C21FDBA7-7415-4E47-A1E1-52DE294A4841}"/>
+    <hyperlink ref="G39" r:id="rId46" xr:uid="{13B27CE7-5730-4B2F-8609-4CA87401B1C7}"/>
+    <hyperlink ref="G40" r:id="rId47" xr:uid="{8FA8908A-BDCF-4A5A-B3ED-2B3230843F47}"/>
+    <hyperlink ref="G54" r:id="rId48" xr:uid="{FECDE756-2E55-448D-A493-AB830E00422F}"/>
+    <hyperlink ref="G55" r:id="rId49" xr:uid="{2605904F-74E2-4140-8422-83AC6F95ACF0}"/>
+    <hyperlink ref="G56" r:id="rId50" xr:uid="{4AAD2757-BD97-4642-943D-36ED00E6418E}"/>
+    <hyperlink ref="G60" r:id="rId51" display="category_var=@variable_map$nut_muac_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_muac_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{DC17D908-1A18-441E-B183-3AC2BCBCF286}"/>
+    <hyperlink ref="G72" r:id="rId52" display="category_var=@variable_map$nut_mfaz_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{DBEF38CD-CFA3-4B7E-9873-820D8C655ABE}"/>
+    <hyperlink ref="G74" r:id="rId53" display="numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name=&quot;MUAC-for-Age Z-Score Boxplot, Overall&quot;,y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{44B07A4B-C2D2-444F-A938-5BB0668259A7}"/>
+    <hyperlink ref="G61" r:id="rId54" display="category_var=@variable_map$nut_muac_cat_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_muac_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{348278FB-E600-4D5C-99EC-2D9DB9E45613}"/>
+    <hyperlink ref="G62" r:id="rId55" display="category_var=@variable_map$gam_muac,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$gam_muac,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{634E6F14-89DF-4B4C-9D88-1F8CAC06F5D8}"/>
+    <hyperlink ref="G63" r:id="rId56" display="category_var=@variable_map$gam_muac_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$gam_muac_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{AFFF0B7C-BFB3-4156-8EF5-58E5BCE5E074}"/>
+    <hyperlink ref="G64" r:id="rId57" display="numeric_var=@variable_map$nut_muac_cm,show_labels=TRUE,y_label=@variable_label$nut_muac_cm,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{226A4FC9-22BE-4FB5-8D98-20A8457DBB05}"/>
+    <hyperlink ref="G65" r:id="rId58" display="numeric_var=@variable_map$nut_muac_cm_noflag,show_labels=TRUE,y_label=@variable_label$nut_muac_cm_noflag,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{B0D949BF-68BA-4C69-8689-359A2F583EF9}"/>
+    <hyperlink ref="G73" r:id="rId59" display="category_var=@variable_map$nut_mfaz_cat_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_mfaz_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{25A9D459-321D-4708-910A-4791E1503DF5}"/>
+    <hyperlink ref="G75" r:id="rId60" display="numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name=&quot;MUAC-for-Age Z-Score Boxplot, Overall&quot;,y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{F422D042-0B0B-4A47-A764-379976C739FC}"/>
+    <hyperlink ref="G66" r:id="rId61" display="data_var=@variable_map$nut_muac_cm,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm,grouping=@variable_map$sex" xr:uid="{E1B50673-322D-40F4-83D8-E19F39BFD7BB}"/>
+    <hyperlink ref="G67" r:id="rId62" display="data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$sex" xr:uid="{09814A23-CE25-4A8F-9B18-0FE76DB8F140}"/>
+    <hyperlink ref="G76" r:id="rId63" display="zscore_var=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,grouping=@variable_map$sex,grouping_label=@variable_label$sex" xr:uid="{4D66F8A6-C082-4133-9349-BED74ECFF6E2}"/>
+    <hyperlink ref="G77" r:id="rId64" display="zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$sex,grouping_label=@variable_label$sex" xr:uid="{6977622A-816F-4BB6-AB61-5E79A374565C}"/>
+    <hyperlink ref="G80" r:id="rId65" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{714B0ED5-5A0F-4D3E-90FD-DF45F8B6646D}"/>
+    <hyperlink ref="G81" r:id="rId66" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{4F790A65-5DFB-4237-B71D-DD38C690E637}"/>
+    <hyperlink ref="G78" r:id="rId67" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{09905EB5-A9C3-45CD-A179-2F0DD9A8DB32}"/>
+    <hyperlink ref="G79" r:id="rId68" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{D9D1D564-66B7-48E6-AB7C-DF35812E70F3}"/>
+    <hyperlink ref="G70" r:id="rId69" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{9C437AB8-175D-49E5-ABFF-D6D535AB14C7}"/>
+    <hyperlink ref="G71" r:id="rId70" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{1F546702-B4E7-404B-9B49-FB06C84FAF75}"/>
+    <hyperlink ref="G68" r:id="rId71" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{6FD76700-34A2-4660-B8BB-0867F9D32A32}"/>
+    <hyperlink ref="G69" r:id="rId72" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{F1D47BB5-C13D-4E62-9164-464C0F4DAC73}"/>
+    <hyperlink ref="G83" r:id="rId73" display="category_var=@variable_map$nut_ecfies_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_ecfies_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{F930CC13-9893-41CC-AB42-833159D9880C}"/>
+    <hyperlink ref="G84" r:id="rId74" display="numeric_var=@variable_map$nut_ecfies_score,show_labels=TRUE,y_label=@variable_label$nut_ecfies_score,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{4A5D9903-0A53-4E44-A04F-976E352F0F6B}"/>
+    <hyperlink ref="G85" r:id="rId75" display="category_var=@variable_map$nut_bf_yesterday,legend_label=@variable_label$nut_bf_yesterday,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{96AE37DE-D165-451C-A4C4-CBF04A624485}"/>
+    <hyperlink ref="G28" r:id="rId76" xr:uid="{D20018F9-DE4C-4A19-B62E-900ED6FC9607}"/>
+    <hyperlink ref="G29" r:id="rId77" xr:uid="{DC0D0395-33A4-4B4C-816E-3ECE93577432}"/>
+    <hyperlink ref="G30" r:id="rId78" xr:uid="{981D25C0-EDD1-4FEE-9E70-02CA3ED6AAFD}"/>
+    <hyperlink ref="G57" r:id="rId79" xr:uid="{3C2A0CAC-66A0-47D4-A0F0-89B19754D18D}"/>
+    <hyperlink ref="G58" r:id="rId80" xr:uid="{9DB72E38-4958-4736-A5E3-D4644ABCF002}"/>
+    <hyperlink ref="G59" r:id="rId81" xr:uid="{85DD2781-1EA6-40D7-908A-7FD48518C729}"/>
+    <hyperlink ref="G86" r:id="rId82" display="category_var=@variable_map$nut_muac_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_muac_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{C50EF722-80D0-458B-AA9E-3D141D7098A0}"/>
+    <hyperlink ref="G98" r:id="rId83" display="category_var=@variable_map$nut_mfaz_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{9763A159-4A0F-4874-937A-E1E068CA8155}"/>
+    <hyperlink ref="G100" r:id="rId84" display="numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name=&quot;MUAC-for-Age Z-Score Boxplot, Overall&quot;,y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{56FB19AC-95A7-4823-B1A9-A911D1116DFF}"/>
+    <hyperlink ref="G87" r:id="rId85" display="category_var=@variable_map$nut_muac_cat_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_muac_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{7646EA6B-3E19-4F84-8DB6-96C0C88719DE}"/>
+    <hyperlink ref="G88" r:id="rId86" display="category_var=@variable_map$gam_muac,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$gam_muac,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{7019747F-FAEA-4D07-891E-E8A3F1512EE1}"/>
+    <hyperlink ref="G89" r:id="rId87" display="category_var=@variable_map$gam_muac_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$gam_muac_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{11408ECD-FCC8-4893-BC47-FD03B5D715AA}"/>
+    <hyperlink ref="G90" r:id="rId88" display="numeric_var=@variable_map$nut_muac_cm,show_labels=TRUE,y_label=@variable_label$nut_muac_cm,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{BE6E3F41-AA39-44B2-8ED3-3FA9AD059846}"/>
+    <hyperlink ref="G91" r:id="rId89" display="numeric_var=@variable_map$nut_muac_cm_noflag,show_labels=TRUE,y_label=@variable_label$nut_muac_cm_noflag,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{41CB1A42-4471-4340-A509-F9EB595AC573}"/>
+    <hyperlink ref="G99" r:id="rId90" display="category_var=@variable_map$nut_mfaz_cat_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_mfaz_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{997EB8EE-0B6E-4A90-B948-D1D003100F77}"/>
+    <hyperlink ref="G101" r:id="rId91" display="numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name=&quot;MUAC-for-Age Z-Score Boxplot, Overall&quot;,y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{DA7F3ADD-8533-4610-9ADC-4949C16D7799}"/>
+    <hyperlink ref="G92" r:id="rId92" display="data_var=@variable_map$nut_muac_cm,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm,grouping=@variable_map$sex" xr:uid="{FE815EC5-4A21-41FF-B787-AE7A5F790A7F}"/>
+    <hyperlink ref="G93" r:id="rId93" display="data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$sex" xr:uid="{5AF5438C-8619-4E02-AA66-8C2D4FEA564C}"/>
+    <hyperlink ref="G102" r:id="rId94" display="zscore_var=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,grouping=@variable_map$sex,grouping_label=@variable_label$sex" xr:uid="{9FC78B1B-64F8-442E-9858-6ECCD58FAB06}"/>
+    <hyperlink ref="G103" r:id="rId95" display="zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$sex,grouping_label=@variable_label$sex" xr:uid="{E67C249C-1DDA-46F9-A190-D074F214BDEC}"/>
+    <hyperlink ref="G106" r:id="rId96" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{8972D3C8-EC88-40AD-AF7A-1E194052D149}"/>
+    <hyperlink ref="G107" r:id="rId97" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{C93146C6-DCA8-4AAE-A653-24CD9BAB841B}"/>
+    <hyperlink ref="G104" r:id="rId98" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{1A96410D-4E11-4B8B-BEFC-5A6F285DEA04}"/>
+    <hyperlink ref="G105" r:id="rId99" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{5CB3AFBE-FB24-4507-8434-F5DEF9BA7831}"/>
+    <hyperlink ref="G96" r:id="rId100" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{37A135D7-BDE6-44F5-B2FB-8F8A09C082C0}"/>
+    <hyperlink ref="G97" r:id="rId101" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{FE46AC5C-A569-471B-A5A1-5D9936A42C98}"/>
+    <hyperlink ref="G94" r:id="rId102" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{93FF3820-B05A-4C34-940D-FD567E877FD9}"/>
+    <hyperlink ref="G95" r:id="rId103" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{22DE9744-63B6-4EED-9ABE-593F752436A7}"/>
+    <hyperlink ref="G109" r:id="rId104" display="category_var=@variable_map$nut_ecfies_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_ecfies_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{FA38F4B0-9760-4763-BBBF-E1261CB55E2B}"/>
+    <hyperlink ref="G110" r:id="rId105" display="numeric_var=@variable_map$nut_ecfies_score,show_labels=TRUE,y_label=@variable_label$nut_ecfies_score,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{C95684AC-9245-4244-80F5-AC6DEB7E7FA9}"/>
+    <hyperlink ref="G111" r:id="rId106" display="category_var=@variable_map$nut_bf_yesterday,legend_label=@variable_label$nut_bf_yesterday,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{2F76FF96-7096-437C-A520-6257FBC6B0A1}"/>
+    <hyperlink ref="G112" r:id="rId107" display="category_var=@variable_map$nut_muac_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_muac_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{636F6005-FBAE-4703-A70E-91D0D3C1F1A2}"/>
+    <hyperlink ref="G124" r:id="rId108" display="category_var=@variable_map$nut_mfaz_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{3CA816A7-35B6-4A62-BAA9-85311EB83607}"/>
+    <hyperlink ref="G126" r:id="rId109" display="numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name=&quot;MUAC-for-Age Z-Score Boxplot, Overall&quot;,y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{22C9C3DB-03BE-4D7B-BB5E-25B85D2E4B58}"/>
+    <hyperlink ref="G113" r:id="rId110" display="category_var=@variable_map$nut_muac_cat_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_muac_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{896FC618-7EF6-4AFA-B1B1-E1E7738F4BD5}"/>
+    <hyperlink ref="G114" r:id="rId111" display="category_var=@variable_map$gam_muac,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$gam_muac,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{9A99E072-F96A-40E2-99EF-7D11E6FA5119}"/>
+    <hyperlink ref="G115" r:id="rId112" display="category_var=@variable_map$gam_muac_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$gam_muac_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{263BA663-1DBF-4D3B-840D-083C33A4FA12}"/>
+    <hyperlink ref="G116" r:id="rId113" display="numeric_var=@variable_map$nut_muac_cm,show_labels=TRUE,y_label=@variable_label$nut_muac_cm,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{64E2F3B8-9814-48CF-B13B-8271980083B6}"/>
+    <hyperlink ref="G117" r:id="rId114" display="numeric_var=@variable_map$nut_muac_cm_noflag,show_labels=TRUE,y_label=@variable_label$nut_muac_cm_noflag,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{2B00E19A-AFB1-432D-A88C-FA544ECDAB48}"/>
+    <hyperlink ref="G125" r:id="rId115" display="category_var=@variable_map$nut_mfaz_cat_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_mfaz_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{86BDB9A4-7D70-4A42-863A-E92ED77A0562}"/>
+    <hyperlink ref="G127" r:id="rId116" display="numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name=&quot;MUAC-for-Age Z-Score Boxplot, Overall&quot;,y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{FD15088C-56A9-46F1-8056-0BF5D2F42394}"/>
+    <hyperlink ref="G118" r:id="rId117" display="data_var=@variable_map$nut_muac_cm,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm,grouping=@variable_map$sex" xr:uid="{EFF22C0A-6B2E-4733-9221-E3BC473A2BC7}"/>
+    <hyperlink ref="G119" r:id="rId118" display="data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$sex" xr:uid="{3B99B92B-5B77-4426-8EA4-756B33FC5707}"/>
+    <hyperlink ref="G128" r:id="rId119" display="zscore_var=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,grouping=@variable_map$sex,grouping_label=@variable_label$sex" xr:uid="{D970E887-5593-4BCB-A7F2-59CF7E1F162B}"/>
+    <hyperlink ref="G129" r:id="rId120" display="zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$sex,grouping_label=@variable_label$sex" xr:uid="{8F99F829-B982-4A5A-839E-88C58C6DC60E}"/>
+    <hyperlink ref="G132" r:id="rId121" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{442A0577-97B8-407A-B007-494516721296}"/>
+    <hyperlink ref="G133" r:id="rId122" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{4BCAB69E-9565-4517-91DB-A171C751F62B}"/>
+    <hyperlink ref="G130" r:id="rId123" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{2774A969-4E2B-479B-BC31-F6CCFB5B7673}"/>
+    <hyperlink ref="G131" r:id="rId124" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{E59A81E4-42DC-41E9-AF9D-1AC59E4BA52B}"/>
+    <hyperlink ref="G122" r:id="rId125" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{598D1A4F-05DB-4CC1-8AA2-438D7A79800F}"/>
+    <hyperlink ref="G123" r:id="rId126" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{C0A93B3B-58BD-4FB8-A7A1-4913E306B8BD}"/>
+    <hyperlink ref="G120" r:id="rId127" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{E66B884B-6966-426F-85E9-67953D083596}"/>
+    <hyperlink ref="G121" r:id="rId128" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{D0ECA029-139E-48D7-AC85-797449981D99}"/>
+    <hyperlink ref="G135" r:id="rId129" display="category_var=@variable_map$nut_ecfies_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_ecfies_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{BF2277BC-B083-4296-A110-2CD1B6F492A7}"/>
+    <hyperlink ref="G136" r:id="rId130" display="numeric_var=@variable_map$nut_ecfies_score,show_labels=TRUE,y_label=@variable_label$nut_ecfies_score,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{F4153854-A8EB-4471-A8D5-D7C44875E3EF}"/>
+    <hyperlink ref="G137" r:id="rId131" display="category_var=@variable_map$nut_bf_yesterday,legend_label=@variable_label$nut_bf_yesterday,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{D9B6625C-A9DB-4D9E-B73B-4B3FB35745A8}"/>
+    <hyperlink ref="G138" r:id="rId132" xr:uid="{E34B6D3F-A3C1-42DE-83B6-ECB56F03A781}"/>
+    <hyperlink ref="G150" r:id="rId133" xr:uid="{E8B96B85-2B4E-4511-A88A-EE037466F054}"/>
+    <hyperlink ref="G152" r:id="rId134" xr:uid="{5116D3C0-3758-49A4-A54A-EA30AAE2BE88}"/>
+    <hyperlink ref="G139" r:id="rId135" xr:uid="{27603B99-E1F6-4B37-B23A-FE9F0A4FBB7E}"/>
+    <hyperlink ref="G140" r:id="rId136" xr:uid="{5D95E88F-5CBB-48D5-8D20-8A1FDEA1AEC8}"/>
+    <hyperlink ref="G141" r:id="rId137" xr:uid="{E88D2A7C-8444-41AD-8A54-60A50B1B9EF7}"/>
+    <hyperlink ref="G142" r:id="rId138" xr:uid="{06908D2E-8BC3-4033-83C0-DE0F458DB6CE}"/>
+    <hyperlink ref="G143" r:id="rId139" xr:uid="{99E3D2F0-1778-40D9-A10C-3B4EC74ACA17}"/>
+    <hyperlink ref="G151" r:id="rId140" xr:uid="{1C6896F5-49CE-4F3A-9DF0-6C8948E2EBB7}"/>
+    <hyperlink ref="G153" r:id="rId141" xr:uid="{DC55522B-B4DF-439C-BD29-815155D9E175}"/>
+    <hyperlink ref="G144" r:id="rId142" xr:uid="{C86A4B4B-1548-45BB-AE32-9AEF28E931B2}"/>
+    <hyperlink ref="G145" r:id="rId143" xr:uid="{B0EBB407-892A-46F9-A433-339EDEFF36CA}"/>
+    <hyperlink ref="G154" r:id="rId144" xr:uid="{4D1D96AB-F6C0-466C-B288-9B7E965D5FA7}"/>
+    <hyperlink ref="G155" r:id="rId145" xr:uid="{FCCA2229-C8F1-4780-900E-9BD3D7455E0F}"/>
+    <hyperlink ref="G158" r:id="rId146" xr:uid="{3838463F-43C1-4A61-AB63-F1C5B2AFDBF0}"/>
+    <hyperlink ref="G159" r:id="rId147" xr:uid="{3E1334CC-6479-4532-A127-DADAA939A866}"/>
+    <hyperlink ref="G156" r:id="rId148" xr:uid="{63F6986D-3A49-475A-8EE9-E174988E8CB7}"/>
+    <hyperlink ref="G157" r:id="rId149" xr:uid="{D3CD784C-2C34-4EBA-B40B-0F5B8E29CE21}"/>
+    <hyperlink ref="G148" r:id="rId150" xr:uid="{691CC4F2-C608-4C29-8A07-50DB4A64E403}"/>
+    <hyperlink ref="G149" r:id="rId151" xr:uid="{B8B234D7-88AD-4343-93DE-3FD89D6FE0F5}"/>
+    <hyperlink ref="G146" r:id="rId152" xr:uid="{8521FFD6-72AD-489F-BE6E-595EC4DF9B07}"/>
+    <hyperlink ref="G147" r:id="rId153" xr:uid="{599E5410-8644-49E7-BBCE-84A60F553247}"/>
+    <hyperlink ref="G161" r:id="rId154" xr:uid="{E017C265-C7EE-4BE2-92AE-3655FA4CE873}"/>
+    <hyperlink ref="G162" r:id="rId155" xr:uid="{65BFE8A3-327C-4903-AEAD-E18A20B5C1C8}"/>
+    <hyperlink ref="G163" r:id="rId156" xr:uid="{3C9639CE-4095-48D6-9BF2-A97D45FFA1F4}"/>
+    <hyperlink ref="G167" r:id="rId157" xr:uid="{54004AB6-214B-4EFC-B71A-C25F4DC183F4}"/>
+    <hyperlink ref="G179" r:id="rId158" xr:uid="{45B95151-09B0-4FB7-8F4B-AD5DE362E9DA}"/>
+    <hyperlink ref="G181" r:id="rId159" xr:uid="{6426975B-8E05-4AEA-A813-A5DB8FC370F9}"/>
+    <hyperlink ref="G168" r:id="rId160" xr:uid="{BE6F28C6-7E7D-4ADC-B454-B8E58B6BD3C7}"/>
+    <hyperlink ref="G169" r:id="rId161" xr:uid="{720F4333-8BB1-4F4B-B381-AEE73ED98447}"/>
+    <hyperlink ref="G170" r:id="rId162" xr:uid="{F20BFE3C-5593-4E89-90D4-7D3CFF1AE796}"/>
+    <hyperlink ref="G171" r:id="rId163" xr:uid="{E0D1EDD7-C142-4897-9DE4-1F23F9ED12F9}"/>
+    <hyperlink ref="G172" r:id="rId164" xr:uid="{CB61591D-FBF4-43D7-A8CD-A5884AF3DBDF}"/>
+    <hyperlink ref="G180" r:id="rId165" xr:uid="{7EA41CED-6804-4108-822C-BD2B13083345}"/>
+    <hyperlink ref="G182" r:id="rId166" xr:uid="{B0FA04CF-488A-46B7-B2ED-405266CF9337}"/>
+    <hyperlink ref="G173" r:id="rId167" xr:uid="{5181F358-3BB7-48A9-AE98-798FD2DFB181}"/>
+    <hyperlink ref="G174" r:id="rId168" xr:uid="{DABA61E2-643B-405A-BFA0-6995A585B64E}"/>
+    <hyperlink ref="G183" r:id="rId169" xr:uid="{4C36E278-D2D3-45FF-8284-293627DA01F3}"/>
+    <hyperlink ref="G184" r:id="rId170" xr:uid="{22A20EAC-1B3D-41A4-8E1D-8938A76B0875}"/>
+    <hyperlink ref="G187" r:id="rId171" xr:uid="{3D966B71-BED3-45F4-BC61-4CB32D5C3717}"/>
+    <hyperlink ref="G188" r:id="rId172" xr:uid="{08F66550-E9A2-4264-89A0-0A33606F8D83}"/>
+    <hyperlink ref="G185" r:id="rId173" xr:uid="{D46FDDA2-F4E3-4274-BAC0-8674649007FA}"/>
+    <hyperlink ref="G186" r:id="rId174" xr:uid="{30AC6C78-C9EA-47C4-B38B-06DCD2BB5339}"/>
+    <hyperlink ref="G177" r:id="rId175" xr:uid="{56E63E90-383E-43BD-BD09-37AD8A3A38ED}"/>
+    <hyperlink ref="G178" r:id="rId176" xr:uid="{EFEEE030-3555-4DCD-A412-DABB3D57490B}"/>
+    <hyperlink ref="G175" r:id="rId177" xr:uid="{7BC043C1-C6A7-4D0D-AEF1-1BCEEFE1B02F}"/>
+    <hyperlink ref="G176" r:id="rId178" xr:uid="{9488B74C-839C-4FEE-A38C-82DB568AA2AE}"/>
+    <hyperlink ref="G190" r:id="rId179" xr:uid="{C8A13D27-B50E-44F7-BFB1-53837A92FACF}"/>
+    <hyperlink ref="G191" r:id="rId180" xr:uid="{BB5E2201-ADD0-483A-AB50-E4136A8F478D}"/>
+    <hyperlink ref="G192" r:id="rId181" xr:uid="{04AA19E6-62F7-4197-A3FE-DB76769A6795}"/>
+    <hyperlink ref="G196" r:id="rId182" display="category_var=@variable_map$nut_muac_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_muac_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{47841B20-1EBD-4E09-8499-479513F12293}"/>
+    <hyperlink ref="G208" r:id="rId183" display="category_var=@variable_map$nut_mfaz_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{2C19BBFD-D553-4099-AA61-A4970DF55E90}"/>
+    <hyperlink ref="G210" r:id="rId184" display="numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name=&quot;MUAC-for-Age Z-Score Boxplot, Overall&quot;,y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{8BC82AC9-E5F1-4F53-8F99-8274C909080A}"/>
+    <hyperlink ref="G197" r:id="rId185" display="category_var=@variable_map$nut_muac_cat_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_muac_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{12D3EDCF-A580-4FA3-B664-EAB9703ADDFA}"/>
+    <hyperlink ref="G198" r:id="rId186" display="category_var=@variable_map$gam_muac,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$gam_muac,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{F3BCD4B4-8325-4BC2-A8F4-434E4418393D}"/>
+    <hyperlink ref="G199" r:id="rId187" display="category_var=@variable_map$gam_muac_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$gam_muac_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{84980C81-AE3A-4B39-9F03-BDA0495FC390}"/>
+    <hyperlink ref="G200" r:id="rId188" display="numeric_var=@variable_map$nut_muac_cm,show_labels=TRUE,y_label=@variable_label$nut_muac_cm,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{6402C7B2-93E3-4659-BA9B-905C140E09B4}"/>
+    <hyperlink ref="G201" r:id="rId189" display="numeric_var=@variable_map$nut_muac_cm_noflag,show_labels=TRUE,y_label=@variable_label$nut_muac_cm_noflag,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{8A6B3012-B0BE-4EF3-979B-EA4238DE80C9}"/>
+    <hyperlink ref="G209" r:id="rId190" display="category_var=@variable_map$nut_mfaz_cat_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_mfaz_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{79D6E006-779E-4055-B3CF-727E402DC65A}"/>
+    <hyperlink ref="G211" r:id="rId191" display="numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name=&quot;MUAC-for-Age Z-Score Boxplot, Overall&quot;,y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{1E3F4224-9858-47A7-8FBF-BC04BFA67ADA}"/>
+    <hyperlink ref="G202" r:id="rId192" display="data_var=@variable_map$nut_muac_cm,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm,grouping=@variable_map$sex" xr:uid="{E3871BDB-60B4-4463-A52A-23D073826531}"/>
+    <hyperlink ref="G203" r:id="rId193" display="data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$sex" xr:uid="{8244B3E6-63E5-4BD4-8EFC-48C6B7B5AECD}"/>
+    <hyperlink ref="G212" r:id="rId194" display="zscore_var=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,grouping=@variable_map$sex,grouping_label=@variable_label$sex" xr:uid="{77BE8FC8-3DD1-4F71-B76F-9B15F8DCE9F9}"/>
+    <hyperlink ref="G213" r:id="rId195" display="zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$sex,grouping_label=@variable_label$sex" xr:uid="{9D2822FE-5D0E-444A-8A42-2126CA6C840D}"/>
+    <hyperlink ref="G216" r:id="rId196" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{D8ADB5FC-0BB4-4E8C-B240-134DAA3E4B5E}"/>
+    <hyperlink ref="G217" r:id="rId197" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{9CD96EAD-63A4-4FC9-BE8B-B010CB136266}"/>
+    <hyperlink ref="G214" r:id="rId198" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{4AFCAE7E-41B4-4A1B-BA70-7FA94705D32A}"/>
+    <hyperlink ref="G215" r:id="rId199" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{ADB45884-4D91-49B4-84C9-A5563F458973}"/>
+    <hyperlink ref="G206" r:id="rId200" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{F4FC486F-B44B-497D-B296-1A81FC36EE03}"/>
+    <hyperlink ref="G207" r:id="rId201" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{136DC131-7483-42CF-A14F-F1E354AEA249}"/>
+    <hyperlink ref="G204" r:id="rId202" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{445B91FD-FABD-46A3-B77A-2F7640A3327E}"/>
+    <hyperlink ref="G205" r:id="rId203" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{BB2326C1-1C38-4751-96CF-A29CAB0C33F6}"/>
+    <hyperlink ref="G219" r:id="rId204" display="category_var=@variable_map$nut_ecfies_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_ecfies_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{01AD821F-0905-4B0C-8839-B0D3228BFD1A}"/>
+    <hyperlink ref="G220" r:id="rId205" display="numeric_var=@variable_map$nut_ecfies_score,show_labels=TRUE,y_label=@variable_label$nut_ecfies_score,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{554265ED-63BA-4082-BF4F-54CEDE8FE21F}"/>
+    <hyperlink ref="G221" r:id="rId206" display="category_var=@variable_map$nut_bf_yesterday,legend_label=@variable_label$nut_bf_yesterday,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{C07E8C20-E3F3-4AC6-A360-8750A5EAD1B9}"/>
+    <hyperlink ref="G164" r:id="rId207" xr:uid="{57A51525-533E-4E48-89E8-6A68D75817D0}"/>
+    <hyperlink ref="G165" r:id="rId208" xr:uid="{DF6F9A0E-400F-448F-A847-C5E5F82DD5DA}"/>
+    <hyperlink ref="G166" r:id="rId209" xr:uid="{5BDE99E4-35FF-4A68-9FC4-8905078E8AAD}"/>
+    <hyperlink ref="G193" r:id="rId210" xr:uid="{FEB310E9-F85E-4F1E-873C-39F33B7A521D}"/>
+    <hyperlink ref="G194" r:id="rId211" xr:uid="{D428D43E-DF7A-429F-B634-CD3667163E33}"/>
+    <hyperlink ref="G195" r:id="rId212" xr:uid="{2AD304A5-7743-4937-804F-7ABB2FC657EE}"/>
+    <hyperlink ref="G222" r:id="rId213" display="category_var=@variable_map$nut_muac_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_muac_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{F29033A1-33F5-47A1-B112-0E2CDD9570C3}"/>
+    <hyperlink ref="G234" r:id="rId214" display="category_var=@variable_map$nut_mfaz_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{67FE9F13-BBD5-4A12-877F-14A92C135429}"/>
+    <hyperlink ref="G236" r:id="rId215" display="numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name=&quot;MUAC-for-Age Z-Score Boxplot, Overall&quot;,y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{E6C00242-F4FF-4AD9-866D-F67CE9F040B0}"/>
+    <hyperlink ref="G223" r:id="rId216" display="category_var=@variable_map$nut_muac_cat_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_muac_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{99873D91-D833-4440-986D-CF94DA5E4ABD}"/>
+    <hyperlink ref="G224" r:id="rId217" display="category_var=@variable_map$gam_muac,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$gam_muac,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{5DE55BF1-94B6-4E83-983C-3F924F351DB9}"/>
+    <hyperlink ref="G225" r:id="rId218" display="category_var=@variable_map$gam_muac_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$gam_muac_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{DC114AE3-2C9D-4E9B-8674-F6B762699A27}"/>
+    <hyperlink ref="G226" r:id="rId219" display="numeric_var=@variable_map$nut_muac_cm,show_labels=TRUE,y_label=@variable_label$nut_muac_cm,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{55513653-F6D7-4904-A563-3C7C357BEE8C}"/>
+    <hyperlink ref="G227" r:id="rId220" display="numeric_var=@variable_map$nut_muac_cm_noflag,show_labels=TRUE,y_label=@variable_label$nut_muac_cm_noflag,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{45BD4031-0E59-4241-91E1-D868E67E8EF6}"/>
+    <hyperlink ref="G235" r:id="rId221" display="category_var=@variable_map$nut_mfaz_cat_noflag,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_mfaz_cat_noflag,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{2C946148-F73D-4958-B922-BE73663FD1C5}"/>
+    <hyperlink ref="G237" r:id="rId222" display="numeric_var=@variable_map$nut_mfaz,show_labels=TRUE,title_name=&quot;MUAC-for-Age Z-Score Boxplot, Overall&quot;,y_label=@variable_label$nut_mfaz,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{E79188EC-D4ED-4B70-B529-3F8E24107229}"/>
+    <hyperlink ref="G228" r:id="rId223" display="data_var=@variable_map$nut_muac_cm,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm,grouping=@variable_map$sex" xr:uid="{9A40F4CE-2A6D-41FC-9F60-EA0705E8CB01}"/>
+    <hyperlink ref="G229" r:id="rId224" display="data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$sex" xr:uid="{811F67E1-4BA6-4C0B-A921-08FAC8061D20}"/>
+    <hyperlink ref="G238" r:id="rId225" display="zscore_var=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,grouping=@variable_map$sex,grouping_label=@variable_label$sex" xr:uid="{4B5F83D5-1C18-4067-892A-010BCE7868CA}"/>
+    <hyperlink ref="G239" r:id="rId226" display="zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$sex,grouping_label=@variable_label$sex" xr:uid="{3D03BFD6-3F30-438C-96D8-2F46650AB26D}"/>
+    <hyperlink ref="G242" r:id="rId227" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{6F144C50-AD6E-43A5-8617-13332733EEF9}"/>
+    <hyperlink ref="G243" r:id="rId228" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{7DE7977C-0D11-4A98-838C-4E5EE4031EA8}"/>
+    <hyperlink ref="G240" r:id="rId229" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{645115A6-3104-41D7-963E-DAF840BBDB27}"/>
+    <hyperlink ref="G241" r:id="rId230" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{111DA234-F46D-4E49-B341-5AC6231F89EF}"/>
+    <hyperlink ref="G232" r:id="rId231" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{5633975A-862F-4BA5-A7D4-1F68168C3410}"/>
+    <hyperlink ref="G233" r:id="rId232" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{030F4B7C-8A98-4EAE-8C6B-FE4C9427D689}"/>
+    <hyperlink ref="G230" r:id="rId233" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{D1688BF1-8E26-4866-A1CF-3431DAAA7D24}"/>
+    <hyperlink ref="G231" r:id="rId234" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{58EB4F2A-4A96-4A62-B56F-292E81A43A7D}"/>
+    <hyperlink ref="G245" r:id="rId235" display="category_var=@variable_map$nut_ecfies_cat,color_palette=&quot;traffic_light&quot;,legend_label=@variable_label$nut_ecfies_cat,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{1191377D-BAC2-4156-A78C-65A2058E1BA0}"/>
+    <hyperlink ref="G246" r:id="rId236" display="numeric_var=@variable_map$nut_ecfies_score,show_labels=TRUE,y_label=@variable_label$nut_ecfies_score,show_mean=TRUE,grouping=@variable_map$sex" xr:uid="{1FFC9B0E-23BF-49F9-88B3-678E4E907924}"/>
+    <hyperlink ref="G247" r:id="rId237" display="category_var=@variable_map$nut_bf_yesterday,legend_label=@variable_label$nut_bf_yesterday,show_labels=TRUE,grouping=@variable_map$sex" xr:uid="{5B3CB120-5335-4357-AF0A-D05042E7CE0E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/outputs_schema_data_analytics_nutrition_template.xlsx
+++ b/resources/outputs_schema_data_analytics_nutrition_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530F235A-CAE7-4F8F-BDF4-8E56128315B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA87A98-687B-49B2-8699-EC82DE3A876B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -139,33 +139,6 @@
     <t>zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag</t>
   </si>
   <si>
-    <t>plot_date_runnner</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean"</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean"</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean"</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean"</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2</t>
-  </si>
-  <si>
     <t>ecfies_s01,ecfies_s02,ecfies_s03,ecfies_s04,ecfies_s05,ecfies_s06,ecfies_s07,ecfies_s08</t>
   </si>
   <si>
@@ -235,18 +208,6 @@
     <t>data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$sex</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$sex</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$sex</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
-  </si>
-  <si>
     <t>category_var=@variable_map$nut_mfaz_cat,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE,grouping=@variable_map$sex</t>
   </si>
   <si>
@@ -262,18 +223,6 @@
     <t>zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$sex,grouping_label=@variable_label$sex</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$sex</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$sex</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
-  </si>
-  <si>
     <t>catecory_vars=c(@variable_map$ecfies_s01,@variable_map$ecfies_s02,@variable_map$ecfies_s03,@variable_map$ecfies_s04,@variable_map$ecfies_s05,@variable_map$ecfies_s06,@variable_map$ecfies_s07,@variable_map$ecfies_s08),category_labels=c(@variable_label$ecfies_s01,@variable_label$ecfies_s02,@variable_label$ecfies_s03,@variable_label$ecfies_s04,@variable_label$ecfies_s05,@variable_label$ecfies_s06,@variable_label$ecfies_s07,@variable_label$ecfies_s08),show_labels=TRUE,grouping=@variable_map$sex</t>
   </si>
   <si>
@@ -313,18 +262,6 @@
     <t>data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$age_months_cat</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$age_months_cat</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$age_months_cat</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
-  </si>
-  <si>
     <t>category_var=@variable_map$nut_mfaz_cat,color_palette="traffic_light",legend_label=@variable_label$nut_mfaz_cat,show_labels=TRUE,grouping=@variable_map$age_months_cat</t>
   </si>
   <si>
@@ -340,18 +277,6 @@
     <t>zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$age_months_cat,grouping_label=@variable_label$age_months_cat</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$age_months_cat</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$age_months_cat</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
-  </si>
-  <si>
     <t>catecory_vars=c(@variable_map$ecfies_s01,@variable_map$ecfies_s02,@variable_map$ecfies_s03,@variable_map$ecfies_s04,@variable_map$ecfies_s05,@variable_map$ecfies_s06,@variable_map$ecfies_s07,@variable_map$ecfies_s08),category_labels=c(@variable_label$ecfies_s01,@variable_label$ecfies_s02,@variable_label$ecfies_s03,@variable_label$ecfies_s04,@variable_label$ecfies_s05,@variable_label$ecfies_s06,@variable_label$ecfies_s07,@variable_label$ecfies_s08),show_labels=TRUE,grouping=@variable_map$age_months_cat</t>
   </si>
   <si>
@@ -538,18 +463,6 @@
     <t>data_var=@variable_map$nut_muac_cm_noflag,vline_intercepts=c(11.5,12.5),variable_label=@variable_label$nut_muac_cm_noflag,grouping=@variable_map$stratum</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$stratum</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$stratum</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
-  </si>
-  <si>
     <t>nut_mfaz_cat,stratum</t>
   </si>
   <si>
@@ -577,18 +490,6 @@
     <t>zscore_var=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,grouping=@variable_map$stratum,grouping_label=@variable_label$stratum</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$stratum</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$stratum</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
-  </si>
-  <si>
     <t>ecfies_s01,ecfies_s02,ecfies_s03,ecfies_s04,ecfies_s05,ecfies_s06,ecfies_s07,ecfies_s08,stratum</t>
   </si>
   <si>
@@ -682,27 +583,15 @@
     <t>muac_cumrunner_mean_enum_id</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$enum_id</t>
-  </si>
-  <si>
     <t>muac_cumrunner_mean_enum_id_noflag</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$enum_id</t>
-  </si>
-  <si>
     <t>mfaz_cumrunner_sd_enum_id</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
-  </si>
-  <si>
     <t>mfaz_cumrunner_sd_enum_id_noflag</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
-  </si>
-  <si>
     <t>mfaz_cat_enum_id</t>
   </si>
   <si>
@@ -745,21 +634,9 @@
     <t>mfaz_cumrunner_mean_enum_id</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$enum_id</t>
-  </si>
-  <si>
     <t>mfaz_cumrunner_mean_enum_id_noflag</t>
   </si>
   <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$enum_id</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
-  </si>
-  <si>
-    <t>date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
-  </si>
-  <si>
     <t>ecfies_vars_stacked_bar_enum_id</t>
   </si>
   <si>
@@ -2069,6 +1946,129 @@
   </si>
   <si>
     <t>bf_yesterday_stratum_svy</t>
+  </si>
+  <si>
+    <t>plot_date_runner</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean"</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean"</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean"</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean"</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$sex</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$age_months_cat</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$stratum</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation="mean",grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation="mean",grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="mean",grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="mean",grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
+  </si>
+  <si>
+    <t>date_col=@variable_map$date_survey,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation="sd",reference_line=1.2,grouping_col=@variable_map$enum_id</t>
   </si>
 </sst>
 </file>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>285</v>
+        <v>244</v>
       </c>
       <c r="B2" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>286</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>315</v>
+        <v>274</v>
       </c>
       <c r="C3" t="s">
         <v>32</v>
@@ -2537,10 +2537,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>287</v>
+        <v>246</v>
       </c>
       <c r="B4" t="s">
-        <v>316</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
         <v>32</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>288</v>
+        <v>247</v>
       </c>
       <c r="B5" t="s">
-        <v>317</v>
+        <v>276</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>289</v>
+        <v>248</v>
       </c>
       <c r="B6" t="s">
-        <v>318</v>
+        <v>277</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
@@ -2610,7 +2610,7 @@
         <v>16</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
         <v>13</v>
@@ -2624,10 +2624,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="B7" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -2639,7 +2639,7 @@
         <v>16</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
         <v>13</v>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>291</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>320</v>
+        <v>279</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
@@ -2682,10 +2682,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="B9" t="s">
-        <v>321</v>
+        <v>280</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
@@ -2711,10 +2711,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>293</v>
+        <v>252</v>
       </c>
       <c r="B10" t="s">
-        <v>322</v>
+        <v>281</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
@@ -2723,10 +2723,10 @@
         <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>44</v>
+        <v>643</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>294</v>
+        <v>253</v>
       </c>
       <c r="B11" t="s">
-        <v>323</v>
+        <v>282</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
@@ -2752,10 +2752,10 @@
         <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>45</v>
+        <v>644</v>
       </c>
       <c r="H11" t="s">
         <v>13</v>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
       <c r="B12" t="s">
-        <v>324</v>
+        <v>283</v>
       </c>
       <c r="C12" t="s">
         <v>32</v>
@@ -2781,10 +2781,10 @@
         <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>46</v>
+        <v>645</v>
       </c>
       <c r="H12" t="s">
         <v>13</v>
@@ -2798,10 +2798,10 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>296</v>
+        <v>255</v>
       </c>
       <c r="B13" t="s">
-        <v>325</v>
+        <v>284</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
@@ -2810,10 +2810,10 @@
         <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>47</v>
+        <v>646</v>
       </c>
       <c r="H13" t="s">
         <v>13</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="B14" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>298</v>
+        <v>257</v>
       </c>
       <c r="B15" t="s">
-        <v>327</v>
+        <v>286</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
@@ -2879,10 +2879,10 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>299</v>
+        <v>258</v>
       </c>
       <c r="B16" t="s">
-        <v>318</v>
+        <v>277</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -2891,7 +2891,7 @@
         <v>16</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H16" t="s">
         <v>13</v>
@@ -2905,10 +2905,10 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>300</v>
+        <v>259</v>
       </c>
       <c r="B17" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="D17" t="s">
         <v>31</v>
@@ -2917,7 +2917,7 @@
         <v>16</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H17" t="s">
         <v>13</v>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>301</v>
+        <v>260</v>
       </c>
       <c r="B18" t="s">
-        <v>328</v>
+        <v>287</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>302</v>
+        <v>261</v>
       </c>
       <c r="B19" t="s">
-        <v>329</v>
+        <v>288</v>
       </c>
       <c r="D19" t="s">
         <v>31</v>
@@ -2983,19 +2983,19 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="B20" t="s">
-        <v>330</v>
+        <v>289</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>43</v>
+        <v>647</v>
       </c>
       <c r="H20" t="s">
         <v>13</v>
@@ -3009,19 +3009,19 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="B21" t="s">
-        <v>331</v>
+        <v>290</v>
       </c>
       <c r="D21" t="s">
         <v>31</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>42</v>
+        <v>648</v>
       </c>
       <c r="H21" t="s">
         <v>13</v>
@@ -3035,19 +3035,19 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>305</v>
+        <v>264</v>
       </c>
       <c r="B22" t="s">
-        <v>324</v>
+        <v>283</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>40</v>
+        <v>649</v>
       </c>
       <c r="H22" t="s">
         <v>13</v>
@@ -3061,19 +3061,19 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="B23" t="s">
-        <v>325</v>
+        <v>284</v>
       </c>
       <c r="D23" t="s">
         <v>31</v>
       </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>41</v>
+        <v>650</v>
       </c>
       <c r="H23" t="s">
         <v>13</v>
@@ -3087,19 +3087,19 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>307</v>
+        <v>266</v>
       </c>
       <c r="B24" t="s">
-        <v>332</v>
+        <v>291</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G24" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="H24" t="s">
         <v>13</v>
@@ -3113,19 +3113,19 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>308</v>
+        <v>267</v>
       </c>
       <c r="B25" t="s">
-        <v>333</v>
+        <v>292</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H25" t="s">
         <v>13</v>
@@ -3139,19 +3139,19 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s">
-        <v>334</v>
+        <v>293</v>
       </c>
       <c r="D26" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="H26" t="s">
         <v>13</v>
@@ -3165,19 +3165,19 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s">
-        <v>335</v>
+        <v>294</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F27" t="s">
         <v>12</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="H27" t="s">
         <v>13</v>
@@ -3191,19 +3191,19 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s">
         <v>13</v>
@@ -3217,19 +3217,19 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="B29" t="s">
-        <v>337</v>
+        <v>296</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
@@ -3243,19 +3243,19 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>313</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s">
-        <v>338</v>
+        <v>297</v>
       </c>
       <c r="D30" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="F30" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="H30" t="s">
         <v>13</v>
@@ -3269,25 +3269,25 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>339</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s">
-        <v>367</v>
+        <v>326</v>
       </c>
       <c r="C31" t="s">
         <v>32</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H31" t="s">
         <v>13</v>
@@ -3301,25 +3301,25 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>340</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s">
-        <v>368</v>
+        <v>327</v>
       </c>
       <c r="C32" t="s">
         <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="E32" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H32" t="s">
         <v>13</v>
@@ -3333,25 +3333,25 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>482</v>
+        <v>441</v>
       </c>
       <c r="B33" t="s">
-        <v>369</v>
+        <v>328</v>
       </c>
       <c r="C33" t="s">
         <v>32</v>
       </c>
       <c r="D33" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="E33" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="H33" t="s">
         <v>13</v>
@@ -3365,25 +3365,25 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s">
-        <v>370</v>
+        <v>329</v>
       </c>
       <c r="C34" t="s">
         <v>32</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="E34" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H34" t="s">
         <v>13</v>
@@ -3397,25 +3397,25 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>342</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s">
-        <v>371</v>
+        <v>330</v>
       </c>
       <c r="C35" t="s">
         <v>32</v>
       </c>
       <c r="D35" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E35" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F35" t="s">
         <v>16</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="H35" t="s">
         <v>13</v>
@@ -3429,25 +3429,25 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>343</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s">
-        <v>372</v>
+        <v>331</v>
       </c>
       <c r="C36" t="s">
         <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F36" t="s">
         <v>16</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H36" t="s">
         <v>13</v>
@@ -3461,25 +3461,25 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>344</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s">
-        <v>373</v>
+        <v>332</v>
       </c>
       <c r="C37" t="s">
         <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F37" t="s">
         <v>33</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H37" t="s">
         <v>13</v>
@@ -3493,25 +3493,25 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>345</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s">
-        <v>374</v>
+        <v>333</v>
       </c>
       <c r="C38" t="s">
         <v>32</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F38" t="s">
         <v>33</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H38" t="s">
         <v>13</v>
@@ -3525,25 +3525,25 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>346</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s">
-        <v>375</v>
+        <v>334</v>
       </c>
       <c r="C39" t="s">
         <v>32</v>
       </c>
       <c r="D39" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E39" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>71</v>
+        <v>651</v>
       </c>
       <c r="H39" t="s">
         <v>13</v>
@@ -3557,25 +3557,25 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s">
-        <v>376</v>
+        <v>335</v>
       </c>
       <c r="C40" t="s">
         <v>32</v>
       </c>
       <c r="D40" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E40" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>72</v>
+        <v>652</v>
       </c>
       <c r="H40" t="s">
         <v>13</v>
@@ -3589,25 +3589,25 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>348</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s">
-        <v>377</v>
+        <v>336</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
       </c>
       <c r="D41" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E41" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F41" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>73</v>
+        <v>653</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
@@ -3621,25 +3621,25 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>349</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s">
-        <v>378</v>
+        <v>337</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E42" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F42" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>74</v>
+        <v>654</v>
       </c>
       <c r="H42" t="s">
         <v>13</v>
@@ -3653,22 +3653,22 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>350</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s">
-        <v>379</v>
+        <v>338</v>
       </c>
       <c r="D43" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E43" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="H43" t="s">
         <v>13</v>
@@ -3682,22 +3682,22 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>351</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s">
-        <v>380</v>
+        <v>339</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F44" t="s">
         <v>12</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H44" t="s">
         <v>13</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>352</v>
+        <v>311</v>
       </c>
       <c r="B45" t="s">
-        <v>371</v>
+        <v>330</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E45" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F45" t="s">
         <v>16</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="H45" t="s">
         <v>13</v>
@@ -3740,22 +3740,22 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>353</v>
+        <v>312</v>
       </c>
       <c r="B46" t="s">
-        <v>372</v>
+        <v>331</v>
       </c>
       <c r="D46" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="E46" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="H46" t="s">
         <v>13</v>
@@ -3769,22 +3769,22 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>354</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s">
-        <v>381</v>
+        <v>340</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E47" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F47" t="s">
         <v>36</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="H47" t="s">
         <v>13</v>
@@ -3798,22 +3798,22 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s">
-        <v>382</v>
+        <v>341</v>
       </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="E48" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F48" t="s">
         <v>36</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="H48" t="s">
         <v>13</v>
@@ -3827,22 +3827,22 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s">
-        <v>383</v>
+        <v>342</v>
       </c>
       <c r="D49" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E49" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F49" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>80</v>
+        <v>655</v>
       </c>
       <c r="H49" t="s">
         <v>13</v>
@@ -3856,22 +3856,22 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="D50" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="E50" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F50" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>81</v>
+        <v>656</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
@@ -3885,22 +3885,22 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s">
-        <v>377</v>
+        <v>336</v>
       </c>
       <c r="D51" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E51" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>82</v>
+        <v>657</v>
       </c>
       <c r="H51" t="s">
         <v>13</v>
@@ -3914,22 +3914,22 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>359</v>
+        <v>318</v>
       </c>
       <c r="B52" t="s">
-        <v>378</v>
+        <v>337</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="E52" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>83</v>
+        <v>658</v>
       </c>
       <c r="H52" t="s">
         <v>13</v>
@@ -3943,22 +3943,22 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
       <c r="B53" t="s">
-        <v>385</v>
+        <v>344</v>
       </c>
       <c r="D53" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="E53" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F53" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G53" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="H53" t="s">
         <v>13</v>
@@ -3972,22 +3972,22 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>361</v>
+        <v>320</v>
       </c>
       <c r="B54" t="s">
-        <v>386</v>
+        <v>345</v>
       </c>
       <c r="D54" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="E54" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="H54" t="s">
         <v>13</v>
@@ -4001,22 +4001,22 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>362</v>
+        <v>321</v>
       </c>
       <c r="B55" t="s">
-        <v>387</v>
+        <v>346</v>
       </c>
       <c r="D55" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="E55" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="H55" t="s">
         <v>13</v>
@@ -4030,22 +4030,22 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="B56" t="s">
-        <v>388</v>
+        <v>347</v>
       </c>
       <c r="D56" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="E56" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F56" t="s">
         <v>12</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="H56" t="s">
         <v>13</v>
@@ -4059,22 +4059,22 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D57" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="E57" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F57" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="H57" t="s">
         <v>13</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="B58" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="D58" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="E58" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F58" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="H58" t="s">
         <v>13</v>
@@ -4117,22 +4117,22 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>366</v>
+        <v>325</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D59" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="E59" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F59" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H59" t="s">
         <v>13</v>
@@ -4146,25 +4146,25 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="B60" t="s">
-        <v>414</v>
+        <v>373</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
       </c>
       <c r="D60" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F60" t="s">
         <v>12</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="H60" t="s">
         <v>13</v>
@@ -4178,25 +4178,25 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>390</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s">
-        <v>415</v>
+        <v>374</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
       </c>
       <c r="D61" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="E61" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F61" t="s">
         <v>12</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="H61" t="s">
         <v>13</v>
@@ -4210,25 +4210,25 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>483</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s">
-        <v>416</v>
+        <v>375</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
       </c>
       <c r="D62" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="H62" t="s">
         <v>13</v>
@@ -4242,25 +4242,25 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>391</v>
+        <v>350</v>
       </c>
       <c r="B63" t="s">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
       </c>
       <c r="D63" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="E63" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="H63" t="s">
         <v>13</v>
@@ -4274,25 +4274,25 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="B64" t="s">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="C64" t="s">
         <v>32</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E64" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F64" t="s">
         <v>16</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H64" t="s">
         <v>13</v>
@@ -4306,25 +4306,25 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>393</v>
+        <v>352</v>
       </c>
       <c r="B65" t="s">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="C65" t="s">
         <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E65" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F65" t="s">
         <v>16</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="H65" t="s">
         <v>13</v>
@@ -4338,25 +4338,25 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>394</v>
+        <v>353</v>
       </c>
       <c r="B66" t="s">
-        <v>420</v>
+        <v>379</v>
       </c>
       <c r="C66" t="s">
         <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E66" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F66" t="s">
         <v>33</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="H66" t="s">
         <v>13</v>
@@ -4370,25 +4370,25 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>395</v>
+        <v>354</v>
       </c>
       <c r="B67" t="s">
-        <v>421</v>
+        <v>380</v>
       </c>
       <c r="C67" t="s">
         <v>32</v>
       </c>
       <c r="D67" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E67" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F67" t="s">
         <v>33</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s">
         <v>13</v>
@@ -4402,25 +4402,25 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>396</v>
+        <v>355</v>
       </c>
       <c r="B68" t="s">
-        <v>422</v>
+        <v>381</v>
       </c>
       <c r="C68" t="s">
         <v>32</v>
       </c>
       <c r="D68" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E68" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F68" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>97</v>
+        <v>659</v>
       </c>
       <c r="H68" t="s">
         <v>13</v>
@@ -4434,25 +4434,25 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>397</v>
+        <v>356</v>
       </c>
       <c r="B69" t="s">
-        <v>423</v>
+        <v>382</v>
       </c>
       <c r="C69" t="s">
         <v>32</v>
       </c>
       <c r="D69" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E69" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F69" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>98</v>
+        <v>660</v>
       </c>
       <c r="H69" t="s">
         <v>13</v>
@@ -4466,25 +4466,25 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>398</v>
+        <v>357</v>
       </c>
       <c r="B70" t="s">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="C70" t="s">
         <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E70" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F70" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>99</v>
+        <v>661</v>
       </c>
       <c r="H70" t="s">
         <v>13</v>
@@ -4498,25 +4498,25 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>399</v>
+        <v>358</v>
       </c>
       <c r="B71" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="C71" t="s">
         <v>32</v>
       </c>
       <c r="D71" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E71" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F71" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>100</v>
+        <v>662</v>
       </c>
       <c r="H71" t="s">
         <v>13</v>
@@ -4530,22 +4530,22 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>400</v>
+        <v>359</v>
       </c>
       <c r="B72" t="s">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="D72" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="E72" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F72" t="s">
         <v>12</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s">
         <v>13</v>
@@ -4559,22 +4559,22 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>401</v>
+        <v>360</v>
       </c>
       <c r="B73" t="s">
-        <v>427</v>
+        <v>386</v>
       </c>
       <c r="D73" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E73" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F73" t="s">
         <v>12</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s">
         <v>13</v>
@@ -4588,22 +4588,22 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>402</v>
+        <v>361</v>
       </c>
       <c r="B74" t="s">
-        <v>418</v>
+        <v>377</v>
       </c>
       <c r="D74" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E74" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s">
         <v>13</v>
@@ -4617,22 +4617,22 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>403</v>
+        <v>362</v>
       </c>
       <c r="B75" t="s">
-        <v>419</v>
+        <v>378</v>
       </c>
       <c r="D75" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E75" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F75" t="s">
         <v>16</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="H75" t="s">
         <v>13</v>
@@ -4646,22 +4646,22 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>404</v>
+        <v>363</v>
       </c>
       <c r="B76" t="s">
-        <v>428</v>
+        <v>387</v>
       </c>
       <c r="D76" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E76" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F76" t="s">
         <v>36</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="H76" t="s">
         <v>13</v>
@@ -4675,22 +4675,22 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>405</v>
+        <v>364</v>
       </c>
       <c r="B77" t="s">
-        <v>429</v>
+        <v>388</v>
       </c>
       <c r="D77" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E77" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F77" t="s">
         <v>36</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="H77" t="s">
         <v>13</v>
@@ -4704,22 +4704,22 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>406</v>
+        <v>365</v>
       </c>
       <c r="B78" t="s">
-        <v>430</v>
+        <v>389</v>
       </c>
       <c r="D78" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E78" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F78" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>106</v>
+        <v>663</v>
       </c>
       <c r="H78" t="s">
         <v>13</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>407</v>
+        <v>366</v>
       </c>
       <c r="B79" t="s">
-        <v>431</v>
+        <v>390</v>
       </c>
       <c r="D79" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E79" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F79" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>107</v>
+        <v>664</v>
       </c>
       <c r="H79" t="s">
         <v>13</v>
@@ -4762,22 +4762,22 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>408</v>
+        <v>367</v>
       </c>
       <c r="B80" t="s">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="D80" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E80" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F80" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>108</v>
+        <v>665</v>
       </c>
       <c r="H80" t="s">
         <v>13</v>
@@ -4791,22 +4791,22 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>409</v>
+        <v>368</v>
       </c>
       <c r="B81" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="D81" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E81" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F81" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>109</v>
+        <v>666</v>
       </c>
       <c r="H81" t="s">
         <v>13</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>410</v>
+        <v>369</v>
       </c>
       <c r="B82" t="s">
-        <v>432</v>
+        <v>391</v>
       </c>
       <c r="D82" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="E82" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F82" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G82" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="H82" t="s">
         <v>13</v>
@@ -4849,22 +4849,22 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>411</v>
+        <v>370</v>
       </c>
       <c r="B83" t="s">
-        <v>433</v>
+        <v>392</v>
       </c>
       <c r="D83" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="E83" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F83" t="s">
         <v>12</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="H83" t="s">
         <v>13</v>
@@ -4878,22 +4878,22 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>412</v>
+        <v>371</v>
       </c>
       <c r="B84" t="s">
-        <v>434</v>
+        <v>393</v>
       </c>
       <c r="D84" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="E84" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F84" t="s">
         <v>16</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="H84" t="s">
         <v>13</v>
@@ -4907,22 +4907,22 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="B85" t="s">
-        <v>435</v>
+        <v>394</v>
       </c>
       <c r="D85" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="E85" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F85" t="s">
         <v>12</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s">
         <v>13</v>
@@ -4936,25 +4936,25 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="B86" t="s">
-        <v>461</v>
+        <v>420</v>
       </c>
       <c r="C86" t="s">
         <v>32</v>
       </c>
       <c r="D86" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="E86" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F86" t="s">
         <v>12</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="H86" t="s">
         <v>13</v>
@@ -4968,25 +4968,25 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>437</v>
+        <v>396</v>
       </c>
       <c r="B87" t="s">
-        <v>462</v>
+        <v>421</v>
       </c>
       <c r="C87" t="s">
         <v>32</v>
       </c>
       <c r="D87" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E87" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F87" t="s">
         <v>12</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="H87" t="s">
         <v>13</v>
@@ -5003,22 +5003,22 @@
         <v>21</v>
       </c>
       <c r="B88" t="s">
-        <v>463</v>
+        <v>422</v>
       </c>
       <c r="C88" t="s">
         <v>32</v>
       </c>
       <c r="D88" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="E88" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F88" t="s">
         <v>12</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="H88" t="s">
         <v>13</v>
@@ -5032,25 +5032,25 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>438</v>
+        <v>397</v>
       </c>
       <c r="B89" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C89" t="s">
         <v>32</v>
       </c>
       <c r="D89" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="E89" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F89" t="s">
         <v>12</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="H89" t="s">
         <v>13</v>
@@ -5064,25 +5064,25 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>439</v>
+        <v>398</v>
       </c>
       <c r="B90" t="s">
-        <v>464</v>
+        <v>423</v>
       </c>
       <c r="C90" t="s">
         <v>32</v>
       </c>
       <c r="D90" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="E90" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F90" t="s">
         <v>16</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="H90" t="s">
         <v>13</v>
@@ -5096,25 +5096,25 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>440</v>
+        <v>399</v>
       </c>
       <c r="B91" t="s">
-        <v>465</v>
+        <v>424</v>
       </c>
       <c r="C91" t="s">
         <v>32</v>
       </c>
       <c r="D91" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="E91" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F91" t="s">
         <v>16</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="H91" t="s">
         <v>13</v>
@@ -5128,25 +5128,25 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>441</v>
+        <v>400</v>
       </c>
       <c r="B92" t="s">
-        <v>466</v>
+        <v>425</v>
       </c>
       <c r="C92" t="s">
         <v>32</v>
       </c>
       <c r="D92" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="E92" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F92" t="s">
         <v>33</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="H92" t="s">
         <v>13</v>
@@ -5160,25 +5160,25 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>442</v>
+        <v>401</v>
       </c>
       <c r="B93" t="s">
-        <v>467</v>
+        <v>426</v>
       </c>
       <c r="C93" t="s">
         <v>32</v>
       </c>
       <c r="D93" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="E93" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F93" t="s">
         <v>33</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="H93" t="s">
         <v>13</v>
@@ -5192,25 +5192,25 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>443</v>
+        <v>402</v>
       </c>
       <c r="B94" t="s">
-        <v>468</v>
+        <v>427</v>
       </c>
       <c r="C94" t="s">
         <v>32</v>
       </c>
       <c r="D94" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="E94" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F94" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>172</v>
+        <v>667</v>
       </c>
       <c r="H94" t="s">
         <v>13</v>
@@ -5224,25 +5224,25 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>444</v>
+        <v>403</v>
       </c>
       <c r="B95" t="s">
-        <v>469</v>
+        <v>428</v>
       </c>
       <c r="C95" t="s">
         <v>32</v>
       </c>
       <c r="D95" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="E95" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F95" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>173</v>
+        <v>668</v>
       </c>
       <c r="H95" t="s">
         <v>13</v>
@@ -5256,25 +5256,25 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>445</v>
+        <v>404</v>
       </c>
       <c r="B96" t="s">
-        <v>470</v>
+        <v>429</v>
       </c>
       <c r="C96" t="s">
         <v>32</v>
       </c>
       <c r="D96" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="E96" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F96" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>174</v>
+        <v>669</v>
       </c>
       <c r="H96" t="s">
         <v>13</v>
@@ -5288,25 +5288,25 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>446</v>
+        <v>405</v>
       </c>
       <c r="B97" t="s">
-        <v>471</v>
+        <v>430</v>
       </c>
       <c r="C97" t="s">
         <v>32</v>
       </c>
       <c r="D97" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="E97" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F97" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>175</v>
+        <v>670</v>
       </c>
       <c r="H97" t="s">
         <v>13</v>
@@ -5320,22 +5320,22 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="B98" t="s">
-        <v>472</v>
+        <v>431</v>
       </c>
       <c r="D98" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="E98" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F98" t="s">
         <v>12</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="H98" t="s">
         <v>13</v>
@@ -5349,22 +5349,22 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>448</v>
+        <v>407</v>
       </c>
       <c r="B99" t="s">
-        <v>473</v>
+        <v>432</v>
       </c>
       <c r="D99" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="E99" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F99" t="s">
         <v>12</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="H99" t="s">
         <v>13</v>
@@ -5378,22 +5378,22 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>449</v>
+        <v>408</v>
       </c>
       <c r="B100" t="s">
-        <v>464</v>
+        <v>423</v>
       </c>
       <c r="D100" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="E100" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F100" t="s">
         <v>16</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="H100" t="s">
         <v>13</v>
@@ -5407,22 +5407,22 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>450</v>
+        <v>409</v>
       </c>
       <c r="B101" t="s">
-        <v>465</v>
+        <v>424</v>
       </c>
       <c r="D101" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E101" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F101" t="s">
         <v>16</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="H101" t="s">
         <v>13</v>
@@ -5436,22 +5436,22 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>451</v>
+        <v>410</v>
       </c>
       <c r="B102" t="s">
-        <v>474</v>
+        <v>433</v>
       </c>
       <c r="D102" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="E102" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F102" t="s">
         <v>36</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="H102" t="s">
         <v>13</v>
@@ -5465,22 +5465,22 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>452</v>
+        <v>411</v>
       </c>
       <c r="B103" t="s">
-        <v>475</v>
+        <v>434</v>
       </c>
       <c r="D103" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E103" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F103" t="s">
         <v>36</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="H103" t="s">
         <v>13</v>
@@ -5494,22 +5494,22 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>453</v>
+        <v>412</v>
       </c>
       <c r="B104" t="s">
-        <v>476</v>
+        <v>435</v>
       </c>
       <c r="D104" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="E104" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F104" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>185</v>
+        <v>671</v>
       </c>
       <c r="H104" t="s">
         <v>13</v>
@@ -5523,22 +5523,22 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>454</v>
+        <v>413</v>
       </c>
       <c r="B105" t="s">
-        <v>477</v>
+        <v>436</v>
       </c>
       <c r="D105" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E105" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F105" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>186</v>
+        <v>672</v>
       </c>
       <c r="H105" t="s">
         <v>13</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>455</v>
+        <v>414</v>
       </c>
       <c r="B106" t="s">
-        <v>470</v>
+        <v>429</v>
       </c>
       <c r="D106" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="E106" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F106" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>187</v>
+        <v>673</v>
       </c>
       <c r="H106" t="s">
         <v>13</v>
@@ -5581,22 +5581,22 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>456</v>
+        <v>415</v>
       </c>
       <c r="B107" t="s">
-        <v>471</v>
+        <v>430</v>
       </c>
       <c r="D107" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E107" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F107" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>188</v>
+        <v>674</v>
       </c>
       <c r="H107" t="s">
         <v>13</v>
@@ -5610,22 +5610,22 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>457</v>
+        <v>416</v>
       </c>
       <c r="B108" t="s">
-        <v>478</v>
+        <v>437</v>
       </c>
       <c r="D108" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="E108" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F108" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G108" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="H108" t="s">
         <v>13</v>
@@ -5639,22 +5639,22 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>458</v>
+        <v>417</v>
       </c>
       <c r="B109" t="s">
-        <v>479</v>
+        <v>438</v>
       </c>
       <c r="D109" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="E109" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F109" t="s">
         <v>12</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="H109" t="s">
         <v>13</v>
@@ -5668,22 +5668,22 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="B110" t="s">
-        <v>480</v>
+        <v>439</v>
       </c>
       <c r="D110" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="E110" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F110" t="s">
         <v>16</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="H110" t="s">
         <v>13</v>
@@ -5697,22 +5697,22 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>460</v>
+        <v>419</v>
       </c>
       <c r="B111" t="s">
-        <v>481</v>
+        <v>440</v>
       </c>
       <c r="D111" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="E111" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F111" t="s">
         <v>12</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="H111" t="s">
         <v>13</v>
@@ -5726,31 +5726,31 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>258</v>
+        <v>217</v>
       </c>
       <c r="B112" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="C112" t="s">
         <v>32</v>
       </c>
       <c r="D112" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="E112" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F112" t="s">
         <v>12</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="H112" t="s">
         <v>13</v>
       </c>
       <c r="I112" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>14</v>
@@ -5758,31 +5758,31 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="B113" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="C113" t="s">
         <v>32</v>
       </c>
       <c r="D113" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="E113" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F113" t="s">
         <v>12</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>203</v>
+        <v>170</v>
       </c>
       <c r="H113" t="s">
         <v>13</v>
       </c>
       <c r="I113" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>14</v>
@@ -5793,28 +5793,28 @@
         <v>21</v>
       </c>
       <c r="B114" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="C114" t="s">
         <v>32</v>
       </c>
       <c r="D114" t="s">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="E114" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F114" t="s">
         <v>12</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="H114" t="s">
         <v>13</v>
       </c>
       <c r="I114" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K114" s="2" t="s">
         <v>14</v>
@@ -5822,31 +5822,31 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C115" t="s">
         <v>32</v>
       </c>
       <c r="D115" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="E115" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F115" t="s">
         <v>12</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>208</v>
+        <v>175</v>
       </c>
       <c r="H115" t="s">
         <v>13</v>
       </c>
       <c r="I115" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>14</v>
@@ -5854,31 +5854,31 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="B116" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="C116" t="s">
         <v>32</v>
       </c>
       <c r="D116" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E116" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F116" t="s">
         <v>16</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="H116" t="s">
         <v>13</v>
       </c>
       <c r="I116" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K116" s="2" t="s">
         <v>14</v>
@@ -5886,31 +5886,31 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="B117" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="C117" t="s">
         <v>32</v>
       </c>
       <c r="D117" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="E117" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F117" t="s">
         <v>16</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="H117" t="s">
         <v>13</v>
       </c>
       <c r="I117" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>14</v>
@@ -5918,31 +5918,31 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>263</v>
+        <v>222</v>
       </c>
       <c r="B118" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="C118" t="s">
         <v>32</v>
       </c>
       <c r="D118" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E118" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F118" t="s">
         <v>33</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="H118" t="s">
         <v>13</v>
       </c>
       <c r="I118" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>14</v>
@@ -5950,31 +5950,31 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>264</v>
+        <v>223</v>
       </c>
       <c r="B119" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="C119" t="s">
         <v>32</v>
       </c>
       <c r="D119" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="E119" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F119" t="s">
         <v>33</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="H119" t="s">
         <v>13</v>
       </c>
       <c r="I119" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>14</v>
@@ -5982,31 +5982,31 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="B120" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="C120" t="s">
         <v>32</v>
       </c>
       <c r="D120" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E120" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F120" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>220</v>
+        <v>675</v>
       </c>
       <c r="H120" t="s">
         <v>13</v>
       </c>
       <c r="I120" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>14</v>
@@ -6014,31 +6014,31 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="B121" t="s">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="C121" t="s">
         <v>32</v>
       </c>
       <c r="D121" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="E121" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F121" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>222</v>
+        <v>676</v>
       </c>
       <c r="H121" t="s">
         <v>13</v>
       </c>
       <c r="I121" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>14</v>
@@ -6046,31 +6046,31 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>267</v>
+        <v>226</v>
       </c>
       <c r="B122" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="C122" t="s">
         <v>32</v>
       </c>
       <c r="D122" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="E122" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F122" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>224</v>
+        <v>677</v>
       </c>
       <c r="H122" t="s">
         <v>13</v>
       </c>
       <c r="I122" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>14</v>
@@ -6078,31 +6078,31 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>268</v>
+        <v>227</v>
       </c>
       <c r="B123" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="C123" t="s">
         <v>32</v>
       </c>
       <c r="D123" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="E123" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F123" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>226</v>
+        <v>678</v>
       </c>
       <c r="H123" t="s">
         <v>13</v>
       </c>
       <c r="I123" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>14</v>
@@ -6110,28 +6110,28 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>269</v>
+        <v>228</v>
       </c>
       <c r="B124" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="D124" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="E124" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F124" t="s">
         <v>12</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="H124" t="s">
         <v>13</v>
       </c>
       <c r="I124" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>14</v>
@@ -6139,28 +6139,28 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>270</v>
+        <v>229</v>
       </c>
       <c r="B125" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="D125" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="E125" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F125" t="s">
         <v>12</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="H125" t="s">
         <v>13</v>
       </c>
       <c r="I125" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K125" s="2" t="s">
         <v>14</v>
@@ -6168,28 +6168,28 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>271</v>
+        <v>230</v>
       </c>
       <c r="B126" t="s">
-        <v>209</v>
+        <v>176</v>
       </c>
       <c r="D126" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="E126" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F126" t="s">
         <v>16</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="H126" t="s">
         <v>13</v>
       </c>
       <c r="I126" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>14</v>
@@ -6197,28 +6197,28 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>272</v>
+        <v>231</v>
       </c>
       <c r="B127" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="D127" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="E127" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F127" t="s">
         <v>16</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="H127" t="s">
         <v>13</v>
       </c>
       <c r="I127" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K127" s="2" t="s">
         <v>14</v>
@@ -6226,28 +6226,28 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>273</v>
+        <v>232</v>
       </c>
       <c r="B128" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="D128" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="E128" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F128" t="s">
         <v>36</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="H128" t="s">
         <v>13</v>
       </c>
       <c r="I128" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>14</v>
@@ -6255,28 +6255,28 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>274</v>
+        <v>233</v>
       </c>
       <c r="B129" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="D129" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="E129" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F129" t="s">
         <v>36</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="H129" t="s">
         <v>13</v>
       </c>
       <c r="I129" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>14</v>
@@ -6284,28 +6284,28 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="B130" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="D130" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="E130" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F130" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>241</v>
+        <v>679</v>
       </c>
       <c r="H130" t="s">
         <v>13</v>
       </c>
       <c r="I130" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>14</v>
@@ -6313,28 +6313,28 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>276</v>
+        <v>235</v>
       </c>
       <c r="B131" t="s">
-        <v>242</v>
+        <v>204</v>
       </c>
       <c r="D131" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="E131" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F131" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G131" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="H131" t="s">
+        <v>13</v>
+      </c>
+      <c r="I131" t="s">
         <v>243</v>
-      </c>
-      <c r="H131" t="s">
-        <v>13</v>
-      </c>
-      <c r="I131" t="s">
-        <v>284</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>14</v>
@@ -6342,28 +6342,28 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>277</v>
+        <v>236</v>
       </c>
       <c r="B132" t="s">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="D132" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="E132" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F132" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>244</v>
+        <v>681</v>
       </c>
       <c r="H132" t="s">
         <v>13</v>
       </c>
       <c r="I132" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>14</v>
@@ -6371,28 +6371,28 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>278</v>
+        <v>237</v>
       </c>
       <c r="B133" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D133" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="E133" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F133" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>245</v>
+        <v>682</v>
       </c>
       <c r="H133" t="s">
         <v>13</v>
       </c>
       <c r="I133" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>14</v>
@@ -6400,28 +6400,28 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>279</v>
+        <v>238</v>
       </c>
       <c r="B134" t="s">
-        <v>246</v>
+        <v>205</v>
       </c>
       <c r="D134" t="s">
-        <v>247</v>
+        <v>206</v>
       </c>
       <c r="E134" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F134" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G134" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="H134" t="s">
         <v>13</v>
       </c>
       <c r="I134" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>14</v>
@@ -6429,28 +6429,28 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>280</v>
+        <v>239</v>
       </c>
       <c r="B135" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="D135" t="s">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="E135" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F135" t="s">
         <v>12</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="H135" t="s">
         <v>13</v>
       </c>
       <c r="I135" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K135" s="2" t="s">
         <v>14</v>
@@ -6458,28 +6458,28 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>281</v>
+        <v>240</v>
       </c>
       <c r="B136" t="s">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="D136" t="s">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="E136" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F136" t="s">
         <v>16</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>254</v>
+        <v>213</v>
       </c>
       <c r="H136" t="s">
         <v>13</v>
       </c>
       <c r="I136" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>14</v>
@@ -6487,28 +6487,28 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>282</v>
+        <v>241</v>
       </c>
       <c r="B137" t="s">
-        <v>255</v>
+        <v>214</v>
       </c>
       <c r="D137" t="s">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="E137" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="F137" t="s">
         <v>12</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="H137" t="s">
         <v>13</v>
       </c>
       <c r="I137" t="s">
-        <v>284</v>
+        <v>243</v>
       </c>
       <c r="K137" s="2" t="s">
         <v>14</v>
@@ -6516,10 +6516,10 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>484</v>
+        <v>443</v>
       </c>
       <c r="B138" t="s">
-        <v>513</v>
+        <v>472</v>
       </c>
       <c r="C138" t="s">
         <v>32</v>
@@ -6537,18 +6537,18 @@
         <v>13</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>485</v>
+        <v>444</v>
       </c>
       <c r="B139" t="s">
-        <v>514</v>
+        <v>473</v>
       </c>
       <c r="C139" t="s">
         <v>32</v>
@@ -6566,18 +6566,18 @@
         <v>13</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K139" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>486</v>
+        <v>445</v>
       </c>
       <c r="B140" t="s">
-        <v>515</v>
+        <v>474</v>
       </c>
       <c r="C140" t="s">
         <v>32</v>
@@ -6595,18 +6595,18 @@
         <v>13</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>487</v>
+        <v>446</v>
       </c>
       <c r="B141" t="s">
-        <v>516</v>
+        <v>475</v>
       </c>
       <c r="C141" t="s">
         <v>32</v>
@@ -6624,18 +6624,18 @@
         <v>13</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K141" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>488</v>
+        <v>447</v>
       </c>
       <c r="B142" t="s">
-        <v>517</v>
+        <v>476</v>
       </c>
       <c r="C142" t="s">
         <v>32</v>
@@ -6647,24 +6647,24 @@
         <v>16</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H142" t="s">
         <v>13</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>489</v>
+        <v>448</v>
       </c>
       <c r="B143" t="s">
-        <v>518</v>
+        <v>477</v>
       </c>
       <c r="C143" t="s">
         <v>32</v>
@@ -6676,24 +6676,24 @@
         <v>16</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H143" t="s">
         <v>13</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>490</v>
+        <v>449</v>
       </c>
       <c r="B144" t="s">
-        <v>519</v>
+        <v>478</v>
       </c>
       <c r="C144" t="s">
         <v>32</v>
@@ -6711,18 +6711,18 @@
         <v>13</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K144" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>491</v>
+        <v>450</v>
       </c>
       <c r="B145" t="s">
-        <v>520</v>
+        <v>479</v>
       </c>
       <c r="C145" t="s">
         <v>32</v>
@@ -6740,18 +6740,18 @@
         <v>13</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K145" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>492</v>
+        <v>451</v>
       </c>
       <c r="B146" t="s">
-        <v>521</v>
+        <v>480</v>
       </c>
       <c r="C146" t="s">
         <v>32</v>
@@ -6760,27 +6760,27 @@
         <v>27</v>
       </c>
       <c r="F146" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>44</v>
+        <v>643</v>
       </c>
       <c r="H146" t="s">
         <v>13</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="B147" t="s">
-        <v>522</v>
+        <v>481</v>
       </c>
       <c r="C147" t="s">
         <v>32</v>
@@ -6789,27 +6789,27 @@
         <v>28</v>
       </c>
       <c r="F147" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>45</v>
+        <v>644</v>
       </c>
       <c r="H147" t="s">
         <v>13</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K147" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>494</v>
+        <v>453</v>
       </c>
       <c r="B148" t="s">
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="C148" t="s">
         <v>32</v>
@@ -6818,27 +6818,27 @@
         <v>27</v>
       </c>
       <c r="F148" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>46</v>
+        <v>645</v>
       </c>
       <c r="H148" t="s">
         <v>13</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K148" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>495</v>
+        <v>454</v>
       </c>
       <c r="B149" t="s">
-        <v>524</v>
+        <v>483</v>
       </c>
       <c r="C149" t="s">
         <v>32</v>
@@ -6847,27 +6847,27 @@
         <v>28</v>
       </c>
       <c r="F149" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>47</v>
+        <v>646</v>
       </c>
       <c r="H149" t="s">
         <v>13</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K149" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>496</v>
+        <v>455</v>
       </c>
       <c r="B150" t="s">
-        <v>525</v>
+        <v>484</v>
       </c>
       <c r="D150" t="s">
         <v>15</v>
@@ -6882,18 +6882,18 @@
         <v>13</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K150" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>497</v>
+        <v>456</v>
       </c>
       <c r="B151" t="s">
-        <v>526</v>
+        <v>485</v>
       </c>
       <c r="D151" t="s">
         <v>29</v>
@@ -6908,18 +6908,18 @@
         <v>13</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K151" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>498</v>
+        <v>457</v>
       </c>
       <c r="B152" t="s">
-        <v>517</v>
+        <v>476</v>
       </c>
       <c r="D152" t="s">
         <v>17</v>
@@ -6928,24 +6928,24 @@
         <v>16</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H152" t="s">
         <v>13</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K152" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>499</v>
+        <v>458</v>
       </c>
       <c r="B153" t="s">
-        <v>518</v>
+        <v>477</v>
       </c>
       <c r="D153" t="s">
         <v>31</v>
@@ -6954,24 +6954,24 @@
         <v>16</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H153" t="s">
         <v>13</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>500</v>
+        <v>459</v>
       </c>
       <c r="B154" t="s">
-        <v>527</v>
+        <v>486</v>
       </c>
       <c r="D154" t="s">
         <v>17</v>
@@ -6986,18 +6986,18 @@
         <v>13</v>
       </c>
       <c r="I154" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K154" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>501</v>
+        <v>460</v>
       </c>
       <c r="B155" t="s">
-        <v>528</v>
+        <v>487</v>
       </c>
       <c r="D155" t="s">
         <v>31</v>
@@ -7012,2027 +7012,2027 @@
         <v>13</v>
       </c>
       <c r="I155" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>502</v>
+        <v>461</v>
       </c>
       <c r="B156" t="s">
-        <v>529</v>
+        <v>488</v>
       </c>
       <c r="D156" t="s">
         <v>17</v>
       </c>
       <c r="F156" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>43</v>
+        <v>647</v>
       </c>
       <c r="H156" t="s">
         <v>13</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K156" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>503</v>
+        <v>462</v>
       </c>
       <c r="B157" t="s">
-        <v>530</v>
+        <v>489</v>
       </c>
       <c r="D157" t="s">
         <v>31</v>
       </c>
       <c r="F157" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>42</v>
+        <v>648</v>
       </c>
       <c r="H157" t="s">
         <v>13</v>
       </c>
       <c r="I157" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>504</v>
+        <v>463</v>
       </c>
       <c r="B158" t="s">
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="D158" t="s">
         <v>17</v>
       </c>
       <c r="F158" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>40</v>
+        <v>649</v>
       </c>
       <c r="H158" t="s">
         <v>13</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K158" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>505</v>
+        <v>464</v>
       </c>
       <c r="B159" t="s">
-        <v>524</v>
+        <v>483</v>
       </c>
       <c r="D159" t="s">
         <v>31</v>
       </c>
       <c r="F159" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>41</v>
+        <v>650</v>
       </c>
       <c r="H159" t="s">
         <v>13</v>
       </c>
       <c r="I159" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>506</v>
+        <v>465</v>
       </c>
       <c r="B160" t="s">
-        <v>531</v>
+        <v>490</v>
       </c>
       <c r="D160" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F160" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G160" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="H160" t="s">
         <v>13</v>
       </c>
       <c r="I160" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>507</v>
+        <v>466</v>
       </c>
       <c r="B161" t="s">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="D161" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F161" t="s">
         <v>12</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H161" t="s">
         <v>13</v>
       </c>
       <c r="I161" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K161" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>508</v>
+        <v>467</v>
       </c>
       <c r="B162" t="s">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="D162" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F162" t="s">
         <v>16</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="H162" t="s">
         <v>13</v>
       </c>
       <c r="I162" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>509</v>
+        <v>468</v>
       </c>
       <c r="B163" t="s">
-        <v>534</v>
+        <v>493</v>
       </c>
       <c r="D163" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F163" t="s">
         <v>12</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="H163" t="s">
         <v>13</v>
       </c>
       <c r="I163" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K163" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>510</v>
+        <v>469</v>
       </c>
       <c r="B164" t="s">
-        <v>535</v>
+        <v>494</v>
       </c>
       <c r="D164" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F164" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
       <c r="H164" t="s">
         <v>13</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>511</v>
+        <v>470</v>
       </c>
       <c r="B165" t="s">
-        <v>536</v>
+        <v>495</v>
       </c>
       <c r="D165" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="F165" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="H165" t="s">
         <v>13</v>
       </c>
       <c r="I165" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K165" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>512</v>
+        <v>471</v>
       </c>
       <c r="B166" t="s">
-        <v>537</v>
+        <v>496</v>
       </c>
       <c r="D166" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="F166" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="H166" t="s">
         <v>13</v>
       </c>
       <c r="I166" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K166" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>538</v>
+        <v>497</v>
       </c>
       <c r="B167" t="s">
-        <v>567</v>
+        <v>526</v>
       </c>
       <c r="C167" t="s">
         <v>32</v>
       </c>
       <c r="D167" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="E167" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F167" t="s">
         <v>12</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H167" t="s">
         <v>13</v>
       </c>
       <c r="I167" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K167" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>539</v>
+        <v>498</v>
       </c>
       <c r="B168" t="s">
-        <v>568</v>
+        <v>527</v>
       </c>
       <c r="C168" t="s">
         <v>32</v>
       </c>
       <c r="D168" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="E168" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F168" t="s">
         <v>12</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="H168" t="s">
         <v>13</v>
       </c>
       <c r="I168" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>566</v>
+        <v>525</v>
       </c>
       <c r="B169" t="s">
-        <v>569</v>
+        <v>528</v>
       </c>
       <c r="C169" t="s">
         <v>32</v>
       </c>
       <c r="D169" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="E169" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F169" t="s">
         <v>12</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="H169" t="s">
         <v>13</v>
       </c>
       <c r="I169" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K169" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>540</v>
+        <v>499</v>
       </c>
       <c r="B170" t="s">
-        <v>570</v>
+        <v>529</v>
       </c>
       <c r="C170" t="s">
         <v>32</v>
       </c>
       <c r="D170" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="E170" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F170" t="s">
         <v>12</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H170" t="s">
         <v>13</v>
       </c>
       <c r="I170" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K170" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>541</v>
+        <v>500</v>
       </c>
       <c r="B171" t="s">
-        <v>571</v>
+        <v>530</v>
       </c>
       <c r="C171" t="s">
         <v>32</v>
       </c>
       <c r="D171" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E171" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F171" t="s">
         <v>16</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="H171" t="s">
         <v>13</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K171" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>542</v>
+        <v>501</v>
       </c>
       <c r="B172" t="s">
-        <v>572</v>
+        <v>531</v>
       </c>
       <c r="C172" t="s">
         <v>32</v>
       </c>
       <c r="D172" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E172" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F172" t="s">
         <v>16</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="H172" t="s">
         <v>13</v>
       </c>
       <c r="I172" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K172" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="B173" t="s">
-        <v>573</v>
+        <v>532</v>
       </c>
       <c r="C173" t="s">
         <v>32</v>
       </c>
       <c r="D173" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E173" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F173" t="s">
         <v>33</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H173" t="s">
         <v>13</v>
       </c>
       <c r="I173" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>544</v>
+        <v>503</v>
       </c>
       <c r="B174" t="s">
-        <v>574</v>
+        <v>533</v>
       </c>
       <c r="C174" t="s">
         <v>32</v>
       </c>
       <c r="D174" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E174" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F174" t="s">
         <v>33</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H174" t="s">
         <v>13</v>
       </c>
       <c r="I174" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>545</v>
+        <v>504</v>
       </c>
       <c r="B175" t="s">
-        <v>575</v>
+        <v>534</v>
       </c>
       <c r="C175" t="s">
         <v>32</v>
       </c>
       <c r="D175" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E175" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F175" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>71</v>
+        <v>651</v>
       </c>
       <c r="H175" t="s">
         <v>13</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>546</v>
+        <v>505</v>
       </c>
       <c r="B176" t="s">
-        <v>576</v>
+        <v>535</v>
       </c>
       <c r="C176" t="s">
         <v>32</v>
       </c>
       <c r="D176" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E176" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F176" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>72</v>
+        <v>652</v>
       </c>
       <c r="H176" t="s">
         <v>13</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>547</v>
+        <v>506</v>
       </c>
       <c r="B177" t="s">
-        <v>577</v>
+        <v>536</v>
       </c>
       <c r="C177" t="s">
         <v>32</v>
       </c>
       <c r="D177" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E177" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F177" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>73</v>
+        <v>653</v>
       </c>
       <c r="H177" t="s">
         <v>13</v>
       </c>
       <c r="I177" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>548</v>
+        <v>507</v>
       </c>
       <c r="B178" t="s">
-        <v>578</v>
+        <v>537</v>
       </c>
       <c r="C178" t="s">
         <v>32</v>
       </c>
       <c r="D178" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E178" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F178" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>74</v>
+        <v>654</v>
       </c>
       <c r="H178" t="s">
         <v>13</v>
       </c>
       <c r="I178" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>549</v>
+        <v>508</v>
       </c>
       <c r="B179" t="s">
-        <v>579</v>
+        <v>538</v>
       </c>
       <c r="D179" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="E179" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F179" t="s">
         <v>12</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="H179" t="s">
         <v>13</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>550</v>
+        <v>509</v>
       </c>
       <c r="B180" t="s">
-        <v>580</v>
+        <v>539</v>
       </c>
       <c r="D180" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="E180" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F180" t="s">
         <v>12</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H180" t="s">
         <v>13</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>551</v>
+        <v>510</v>
       </c>
       <c r="B181" t="s">
-        <v>571</v>
+        <v>530</v>
       </c>
       <c r="D181" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E181" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F181" t="s">
         <v>16</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="H181" t="s">
         <v>13</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>552</v>
+        <v>511</v>
       </c>
       <c r="B182" t="s">
-        <v>572</v>
+        <v>531</v>
       </c>
       <c r="D182" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="E182" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F182" t="s">
         <v>16</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="H182" t="s">
         <v>13</v>
       </c>
       <c r="I182" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K182" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>553</v>
+        <v>512</v>
       </c>
       <c r="B183" t="s">
-        <v>581</v>
+        <v>540</v>
       </c>
       <c r="D183" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E183" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F183" t="s">
         <v>36</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="H183" t="s">
         <v>13</v>
       </c>
       <c r="I183" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>554</v>
+        <v>513</v>
       </c>
       <c r="B184" t="s">
-        <v>582</v>
+        <v>541</v>
       </c>
       <c r="D184" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="E184" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F184" t="s">
         <v>36</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="H184" t="s">
         <v>13</v>
       </c>
       <c r="I184" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K184" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>555</v>
+        <v>514</v>
       </c>
       <c r="B185" t="s">
-        <v>583</v>
+        <v>542</v>
       </c>
       <c r="D185" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E185" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F185" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>80</v>
+        <v>655</v>
       </c>
       <c r="H185" t="s">
         <v>13</v>
       </c>
       <c r="I185" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K185" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>556</v>
+        <v>515</v>
       </c>
       <c r="B186" t="s">
-        <v>584</v>
+        <v>543</v>
       </c>
       <c r="D186" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="E186" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F186" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>81</v>
+        <v>656</v>
       </c>
       <c r="H186" t="s">
         <v>13</v>
       </c>
       <c r="I186" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K186" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>557</v>
+        <v>516</v>
       </c>
       <c r="B187" t="s">
-        <v>577</v>
+        <v>536</v>
       </c>
       <c r="D187" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E187" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F187" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>82</v>
+        <v>657</v>
       </c>
       <c r="H187" t="s">
         <v>13</v>
       </c>
       <c r="I187" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>558</v>
+        <v>517</v>
       </c>
       <c r="B188" t="s">
-        <v>578</v>
+        <v>537</v>
       </c>
       <c r="D188" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="E188" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F188" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>83</v>
+        <v>658</v>
       </c>
       <c r="H188" t="s">
         <v>13</v>
       </c>
       <c r="I188" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K188" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>559</v>
+        <v>518</v>
       </c>
       <c r="B189" t="s">
-        <v>585</v>
+        <v>544</v>
       </c>
       <c r="D189" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="E189" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F189" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G189" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="H189" t="s">
         <v>13</v>
       </c>
       <c r="I189" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K189" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>560</v>
+        <v>519</v>
       </c>
       <c r="B190" t="s">
-        <v>586</v>
+        <v>545</v>
       </c>
       <c r="D190" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="E190" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F190" t="s">
         <v>12</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="H190" t="s">
         <v>13</v>
       </c>
       <c r="I190" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K190" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>561</v>
+        <v>520</v>
       </c>
       <c r="B191" t="s">
-        <v>587</v>
+        <v>546</v>
       </c>
       <c r="D191" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="E191" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F191" t="s">
         <v>16</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="H191" t="s">
         <v>13</v>
       </c>
       <c r="I191" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K191" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>562</v>
+        <v>521</v>
       </c>
       <c r="B192" t="s">
-        <v>588</v>
+        <v>547</v>
       </c>
       <c r="D192" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="E192" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F192" t="s">
         <v>12</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="H192" t="s">
         <v>13</v>
       </c>
       <c r="I192" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K192" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>563</v>
+        <v>522</v>
       </c>
       <c r="B193" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D193" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="E193" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F193" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="H193" t="s">
         <v>13</v>
       </c>
       <c r="I193" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K193" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>564</v>
+        <v>523</v>
       </c>
       <c r="B194" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="D194" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="E194" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F194" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="H194" t="s">
         <v>13</v>
       </c>
       <c r="I194" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K194" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>565</v>
+        <v>524</v>
       </c>
       <c r="B195" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="D195" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="E195" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F195" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="H195" t="s">
         <v>13</v>
       </c>
       <c r="I195" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K195" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>611</v>
+        <v>570</v>
       </c>
       <c r="B196" t="s">
-        <v>589</v>
+        <v>548</v>
       </c>
       <c r="C196" t="s">
         <v>32</v>
       </c>
       <c r="D196" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="E196" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F196" t="s">
         <v>12</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="H196" t="s">
         <v>13</v>
       </c>
       <c r="I196" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>612</v>
+        <v>571</v>
       </c>
       <c r="B197" t="s">
-        <v>590</v>
+        <v>549</v>
       </c>
       <c r="C197" t="s">
         <v>32</v>
       </c>
       <c r="D197" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="E197" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F197" t="s">
         <v>12</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="H197" t="s">
         <v>13</v>
       </c>
       <c r="I197" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K197" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>636</v>
+        <v>595</v>
       </c>
       <c r="B198" t="s">
-        <v>591</v>
+        <v>550</v>
       </c>
       <c r="C198" t="s">
         <v>32</v>
       </c>
       <c r="D198" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="E198" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F198" t="s">
         <v>12</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="H198" t="s">
         <v>13</v>
       </c>
       <c r="I198" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K198" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>613</v>
+        <v>572</v>
       </c>
       <c r="B199" t="s">
-        <v>592</v>
+        <v>551</v>
       </c>
       <c r="C199" t="s">
         <v>32</v>
       </c>
       <c r="D199" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="E199" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F199" t="s">
         <v>12</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="H199" t="s">
         <v>13</v>
       </c>
       <c r="I199" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K199" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>614</v>
+        <v>573</v>
       </c>
       <c r="B200" t="s">
-        <v>593</v>
+        <v>552</v>
       </c>
       <c r="C200" t="s">
         <v>32</v>
       </c>
       <c r="D200" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E200" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F200" t="s">
         <v>16</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H200" t="s">
         <v>13</v>
       </c>
       <c r="I200" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K200" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>615</v>
+        <v>574</v>
       </c>
       <c r="B201" t="s">
-        <v>594</v>
+        <v>553</v>
       </c>
       <c r="C201" t="s">
         <v>32</v>
       </c>
       <c r="D201" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E201" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F201" t="s">
         <v>16</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="H201" t="s">
         <v>13</v>
       </c>
       <c r="I201" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K201" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>616</v>
+        <v>575</v>
       </c>
       <c r="B202" t="s">
-        <v>595</v>
+        <v>554</v>
       </c>
       <c r="C202" t="s">
         <v>32</v>
       </c>
       <c r="D202" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E202" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F202" t="s">
         <v>33</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="H202" t="s">
         <v>13</v>
       </c>
       <c r="I202" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K202" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>617</v>
+        <v>576</v>
       </c>
       <c r="B203" t="s">
-        <v>596</v>
+        <v>555</v>
       </c>
       <c r="C203" t="s">
         <v>32</v>
       </c>
       <c r="D203" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E203" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F203" t="s">
         <v>33</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="H203" t="s">
         <v>13</v>
       </c>
       <c r="I203" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K203" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>618</v>
+        <v>577</v>
       </c>
       <c r="B204" t="s">
-        <v>597</v>
+        <v>556</v>
       </c>
       <c r="C204" t="s">
         <v>32</v>
       </c>
       <c r="D204" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E204" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F204" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>97</v>
+        <v>659</v>
       </c>
       <c r="H204" t="s">
         <v>13</v>
       </c>
       <c r="I204" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K204" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>619</v>
+        <v>578</v>
       </c>
       <c r="B205" t="s">
-        <v>598</v>
+        <v>557</v>
       </c>
       <c r="C205" t="s">
         <v>32</v>
       </c>
       <c r="D205" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E205" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F205" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>98</v>
+        <v>660</v>
       </c>
       <c r="H205" t="s">
         <v>13</v>
       </c>
       <c r="I205" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K205" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>620</v>
+        <v>579</v>
       </c>
       <c r="B206" t="s">
-        <v>599</v>
+        <v>558</v>
       </c>
       <c r="C206" t="s">
         <v>32</v>
       </c>
       <c r="D206" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E206" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F206" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>99</v>
+        <v>661</v>
       </c>
       <c r="H206" t="s">
         <v>13</v>
       </c>
       <c r="I206" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K206" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>621</v>
+        <v>580</v>
       </c>
       <c r="B207" t="s">
-        <v>600</v>
+        <v>559</v>
       </c>
       <c r="C207" t="s">
         <v>32</v>
       </c>
       <c r="D207" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E207" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F207" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>100</v>
+        <v>662</v>
       </c>
       <c r="H207" t="s">
         <v>13</v>
       </c>
       <c r="I207" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K207" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>622</v>
+        <v>581</v>
       </c>
       <c r="B208" t="s">
-        <v>601</v>
+        <v>560</v>
       </c>
       <c r="D208" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="E208" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F208" t="s">
         <v>12</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="H208" t="s">
         <v>13</v>
       </c>
       <c r="I208" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K208" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>623</v>
+        <v>582</v>
       </c>
       <c r="B209" t="s">
-        <v>602</v>
+        <v>561</v>
       </c>
       <c r="D209" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E209" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F209" t="s">
         <v>12</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="H209" t="s">
         <v>13</v>
       </c>
       <c r="I209" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K209" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>624</v>
+        <v>583</v>
       </c>
       <c r="B210" t="s">
-        <v>593</v>
+        <v>552</v>
       </c>
       <c r="D210" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E210" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F210" t="s">
         <v>16</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="H210" t="s">
         <v>13</v>
       </c>
       <c r="I210" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K210" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>625</v>
+        <v>584</v>
       </c>
       <c r="B211" t="s">
-        <v>594</v>
+        <v>553</v>
       </c>
       <c r="D211" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E211" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F211" t="s">
         <v>16</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="H211" t="s">
         <v>13</v>
       </c>
       <c r="I211" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K211" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>626</v>
+        <v>585</v>
       </c>
       <c r="B212" t="s">
-        <v>603</v>
+        <v>562</v>
       </c>
       <c r="D212" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E212" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F212" t="s">
         <v>36</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="H212" t="s">
         <v>13</v>
       </c>
       <c r="I212" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K212" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>627</v>
+        <v>586</v>
       </c>
       <c r="B213" t="s">
-        <v>604</v>
+        <v>563</v>
       </c>
       <c r="D213" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E213" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F213" t="s">
         <v>36</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="H213" t="s">
         <v>13</v>
       </c>
       <c r="I213" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K213" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>628</v>
+        <v>587</v>
       </c>
       <c r="B214" t="s">
-        <v>605</v>
+        <v>564</v>
       </c>
       <c r="D214" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E214" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F214" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>106</v>
+        <v>663</v>
       </c>
       <c r="H214" t="s">
         <v>13</v>
       </c>
       <c r="I214" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K214" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>629</v>
+        <v>588</v>
       </c>
       <c r="B215" t="s">
-        <v>606</v>
+        <v>565</v>
       </c>
       <c r="D215" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E215" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F215" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>107</v>
+        <v>664</v>
       </c>
       <c r="H215" t="s">
         <v>13</v>
       </c>
       <c r="I215" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>630</v>
+        <v>589</v>
       </c>
       <c r="B216" t="s">
-        <v>599</v>
+        <v>558</v>
       </c>
       <c r="D216" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="E216" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F216" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>108</v>
+        <v>665</v>
       </c>
       <c r="H216" t="s">
         <v>13</v>
       </c>
       <c r="I216" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K216" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>631</v>
+        <v>590</v>
       </c>
       <c r="B217" t="s">
-        <v>600</v>
+        <v>559</v>
       </c>
       <c r="D217" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="E217" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F217" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>109</v>
+        <v>666</v>
       </c>
       <c r="H217" t="s">
         <v>13</v>
       </c>
       <c r="I217" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K217" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>632</v>
+        <v>591</v>
       </c>
       <c r="B218" t="s">
-        <v>607</v>
+        <v>566</v>
       </c>
       <c r="D218" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="E218" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F218" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G218" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="H218" t="s">
         <v>13</v>
       </c>
       <c r="I218" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K218" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>633</v>
+        <v>592</v>
       </c>
       <c r="B219" t="s">
-        <v>608</v>
+        <v>567</v>
       </c>
       <c r="D219" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="E219" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F219" t="s">
         <v>12</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="H219" t="s">
         <v>13</v>
       </c>
       <c r="I219" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K219" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>634</v>
+        <v>593</v>
       </c>
       <c r="B220" t="s">
-        <v>609</v>
+        <v>568</v>
       </c>
       <c r="D220" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="E220" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F220" t="s">
         <v>16</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="H220" t="s">
         <v>13</v>
       </c>
       <c r="I220" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K220" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>635</v>
+        <v>594</v>
       </c>
       <c r="B221" t="s">
-        <v>610</v>
+        <v>569</v>
       </c>
       <c r="D221" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="E221" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F221" t="s">
         <v>12</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="H221" t="s">
         <v>13</v>
       </c>
       <c r="I221" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K221" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>637</v>
+        <v>596</v>
       </c>
       <c r="B222" t="s">
-        <v>662</v>
+        <v>621</v>
       </c>
       <c r="C222" t="s">
         <v>32</v>
       </c>
       <c r="D222" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="E222" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F222" t="s">
         <v>12</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="H222" t="s">
         <v>13</v>
       </c>
       <c r="I222" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K222" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>638</v>
+        <v>597</v>
       </c>
       <c r="B223" t="s">
-        <v>663</v>
+        <v>622</v>
       </c>
       <c r="C223" t="s">
         <v>32</v>
       </c>
       <c r="D223" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E223" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F223" t="s">
         <v>12</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="H223" t="s">
         <v>13</v>
       </c>
       <c r="I223" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K223" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -9040,725 +9040,725 @@
         <v>21</v>
       </c>
       <c r="B224" t="s">
-        <v>664</v>
+        <v>623</v>
       </c>
       <c r="C224" t="s">
         <v>32</v>
       </c>
       <c r="D224" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="E224" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F224" t="s">
         <v>12</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="H224" t="s">
         <v>13</v>
       </c>
       <c r="I224" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K224" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>639</v>
+        <v>598</v>
       </c>
       <c r="B225" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C225" t="s">
         <v>32</v>
       </c>
       <c r="D225" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="E225" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F225" t="s">
         <v>12</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="H225" t="s">
         <v>13</v>
       </c>
       <c r="I225" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K225" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>640</v>
+        <v>599</v>
       </c>
       <c r="B226" t="s">
-        <v>665</v>
+        <v>624</v>
       </c>
       <c r="C226" t="s">
         <v>32</v>
       </c>
       <c r="D226" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="E226" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F226" t="s">
         <v>16</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="H226" t="s">
         <v>13</v>
       </c>
       <c r="I226" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K226" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>641</v>
+        <v>600</v>
       </c>
       <c r="B227" t="s">
-        <v>666</v>
+        <v>625</v>
       </c>
       <c r="C227" t="s">
         <v>32</v>
       </c>
       <c r="D227" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="E227" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F227" t="s">
         <v>16</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="H227" t="s">
         <v>13</v>
       </c>
       <c r="I227" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K227" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>642</v>
+        <v>601</v>
       </c>
       <c r="B228" t="s">
-        <v>667</v>
+        <v>626</v>
       </c>
       <c r="C228" t="s">
         <v>32</v>
       </c>
       <c r="D228" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="E228" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F228" t="s">
         <v>33</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="H228" t="s">
         <v>13</v>
       </c>
       <c r="I228" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K228" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>643</v>
+        <v>602</v>
       </c>
       <c r="B229" t="s">
-        <v>668</v>
+        <v>627</v>
       </c>
       <c r="C229" t="s">
         <v>32</v>
       </c>
       <c r="D229" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="E229" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F229" t="s">
         <v>33</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="H229" t="s">
         <v>13</v>
       </c>
       <c r="I229" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K229" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>644</v>
+        <v>603</v>
       </c>
       <c r="B230" t="s">
-        <v>669</v>
+        <v>628</v>
       </c>
       <c r="C230" t="s">
         <v>32</v>
       </c>
       <c r="D230" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="E230" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F230" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>172</v>
+        <v>667</v>
       </c>
       <c r="H230" t="s">
         <v>13</v>
       </c>
       <c r="I230" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K230" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>645</v>
+        <v>604</v>
       </c>
       <c r="B231" t="s">
-        <v>670</v>
+        <v>629</v>
       </c>
       <c r="C231" t="s">
         <v>32</v>
       </c>
       <c r="D231" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="E231" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F231" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>173</v>
+        <v>668</v>
       </c>
       <c r="H231" t="s">
         <v>13</v>
       </c>
       <c r="I231" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K231" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>646</v>
+        <v>605</v>
       </c>
       <c r="B232" t="s">
-        <v>671</v>
+        <v>630</v>
       </c>
       <c r="C232" t="s">
         <v>32</v>
       </c>
       <c r="D232" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="E232" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F232" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>174</v>
+        <v>669</v>
       </c>
       <c r="H232" t="s">
         <v>13</v>
       </c>
       <c r="I232" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K232" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>647</v>
+        <v>606</v>
       </c>
       <c r="B233" t="s">
-        <v>672</v>
+        <v>631</v>
       </c>
       <c r="C233" t="s">
         <v>32</v>
       </c>
       <c r="D233" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="E233" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F233" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>175</v>
+        <v>670</v>
       </c>
       <c r="H233" t="s">
         <v>13</v>
       </c>
       <c r="I233" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K233" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>648</v>
+        <v>607</v>
       </c>
       <c r="B234" t="s">
-        <v>673</v>
+        <v>632</v>
       </c>
       <c r="D234" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="E234" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F234" t="s">
         <v>12</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="H234" t="s">
         <v>13</v>
       </c>
       <c r="I234" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K234" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>649</v>
+        <v>608</v>
       </c>
       <c r="B235" t="s">
-        <v>674</v>
+        <v>633</v>
       </c>
       <c r="D235" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="E235" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F235" t="s">
         <v>12</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="H235" t="s">
         <v>13</v>
       </c>
       <c r="I235" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K235" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>650</v>
+        <v>609</v>
       </c>
       <c r="B236" t="s">
-        <v>665</v>
+        <v>624</v>
       </c>
       <c r="D236" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="E236" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F236" t="s">
         <v>16</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="H236" t="s">
         <v>13</v>
       </c>
       <c r="I236" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K236" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>651</v>
+        <v>610</v>
       </c>
       <c r="B237" t="s">
-        <v>666</v>
+        <v>625</v>
       </c>
       <c r="D237" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E237" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F237" t="s">
         <v>16</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="H237" t="s">
         <v>13</v>
       </c>
       <c r="I237" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K237" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>652</v>
+        <v>611</v>
       </c>
       <c r="B238" t="s">
-        <v>675</v>
+        <v>634</v>
       </c>
       <c r="D238" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="E238" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F238" t="s">
         <v>36</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="H238" t="s">
         <v>13</v>
       </c>
       <c r="I238" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K238" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>653</v>
+        <v>612</v>
       </c>
       <c r="B239" t="s">
-        <v>676</v>
+        <v>635</v>
       </c>
       <c r="D239" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E239" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F239" t="s">
         <v>36</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="H239" t="s">
         <v>13</v>
       </c>
       <c r="I239" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K239" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>654</v>
+        <v>613</v>
       </c>
       <c r="B240" t="s">
-        <v>677</v>
+        <v>636</v>
       </c>
       <c r="D240" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="E240" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F240" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>185</v>
+        <v>671</v>
       </c>
       <c r="H240" t="s">
         <v>13</v>
       </c>
       <c r="I240" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K240" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>655</v>
+        <v>614</v>
       </c>
       <c r="B241" t="s">
-        <v>678</v>
+        <v>637</v>
       </c>
       <c r="D241" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E241" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F241" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>186</v>
+        <v>672</v>
       </c>
       <c r="H241" t="s">
         <v>13</v>
       </c>
       <c r="I241" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K241" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>656</v>
+        <v>615</v>
       </c>
       <c r="B242" t="s">
-        <v>671</v>
+        <v>630</v>
       </c>
       <c r="D242" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="E242" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F242" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>187</v>
+        <v>673</v>
       </c>
       <c r="H242" t="s">
         <v>13</v>
       </c>
       <c r="I242" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K242" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>657</v>
+        <v>616</v>
       </c>
       <c r="B243" t="s">
-        <v>672</v>
+        <v>631</v>
       </c>
       <c r="D243" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="E243" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F243" t="s">
-        <v>39</v>
+        <v>642</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>188</v>
+        <v>674</v>
       </c>
       <c r="H243" t="s">
         <v>13</v>
       </c>
       <c r="I243" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K243" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>658</v>
+        <v>617</v>
       </c>
       <c r="B244" t="s">
-        <v>679</v>
+        <v>638</v>
       </c>
       <c r="D244" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="E244" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F244" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G244" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="H244" t="s">
         <v>13</v>
       </c>
       <c r="I244" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K244" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>659</v>
+        <v>618</v>
       </c>
       <c r="B245" t="s">
-        <v>680</v>
+        <v>639</v>
       </c>
       <c r="D245" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="E245" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F245" t="s">
         <v>12</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="H245" t="s">
         <v>13</v>
       </c>
       <c r="I245" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K245" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>660</v>
+        <v>619</v>
       </c>
       <c r="B246" t="s">
-        <v>681</v>
+        <v>640</v>
       </c>
       <c r="D246" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="E246" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F246" t="s">
         <v>16</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="H246" t="s">
         <v>13</v>
       </c>
       <c r="I246" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K246" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>661</v>
+        <v>620</v>
       </c>
       <c r="B247" t="s">
-        <v>682</v>
+        <v>641</v>
       </c>
       <c r="D247" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="E247" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="F247" t="s">
         <v>12</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="H247" t="s">
         <v>13</v>
       </c>
       <c r="I247" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
       <c r="K247" s="2" t="s">
-        <v>283</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -9777,14 +9777,14 @@
     <hyperlink ref="G9" r:id="rId12" xr:uid="{8A5DB7DD-1F7A-4187-9B49-341CBB921AA9}"/>
     <hyperlink ref="G18" r:id="rId13" xr:uid="{67BA1531-DB78-46FF-96E8-6B38E7BB9FF8}"/>
     <hyperlink ref="G19" r:id="rId14" xr:uid="{1A55A5B8-2819-4C18-8DDB-4CBCE5D55CF9}"/>
-    <hyperlink ref="G22" r:id="rId15" xr:uid="{F7684A7C-D334-4458-9AA3-A201101F71EA}"/>
-    <hyperlink ref="G23" r:id="rId16" xr:uid="{A3186681-82A6-4CE1-BFAB-F79916B161B3}"/>
-    <hyperlink ref="G20" r:id="rId17" xr:uid="{D4722470-01FC-46F1-B669-53622505DE2C}"/>
-    <hyperlink ref="G21" r:id="rId18" xr:uid="{88DA17E9-2575-41B2-B486-A0A44398559A}"/>
-    <hyperlink ref="G12" r:id="rId19" xr:uid="{E1AC1FE2-DFF2-4A79-959F-45D1C24D8C92}"/>
-    <hyperlink ref="G13" r:id="rId20" xr:uid="{B18BD72F-C4A6-4045-AE8A-7F719201BA21}"/>
-    <hyperlink ref="G10" r:id="rId21" xr:uid="{1F4594BD-452B-4A83-B2CD-98A0AFF148C7}"/>
-    <hyperlink ref="G11" r:id="rId22" xr:uid="{887A2F45-1D0F-4039-BA8F-FD6DE6BCCE65}"/>
+    <hyperlink ref="G22" r:id="rId15" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;sd&quot;,reference_line=1.2" xr:uid="{F7684A7C-D334-4458-9AA3-A201101F71EA}"/>
+    <hyperlink ref="G23" r:id="rId16" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;sd&quot;,reference_line=1.2" xr:uid="{A3186681-82A6-4CE1-BFAB-F79916B161B3}"/>
+    <hyperlink ref="G20" r:id="rId17" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;mean&quot;" xr:uid="{D4722470-01FC-46F1-B669-53622505DE2C}"/>
+    <hyperlink ref="G21" r:id="rId18" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;mean&quot;" xr:uid="{88DA17E9-2575-41B2-B486-A0A44398559A}"/>
+    <hyperlink ref="G12" r:id="rId19" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation=&quot;sd&quot;,reference_line=1.2" xr:uid="{E1AC1FE2-DFF2-4A79-959F-45D1C24D8C92}"/>
+    <hyperlink ref="G13" r:id="rId20" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation=&quot;sd&quot;,reference_line=1.2" xr:uid="{B18BD72F-C4A6-4045-AE8A-7F719201BA21}"/>
+    <hyperlink ref="G10" r:id="rId21" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation=&quot;mean&quot;" xr:uid="{1F4594BD-452B-4A83-B2CD-98A0AFF148C7}"/>
+    <hyperlink ref="G11" r:id="rId22" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation=&quot;mean&quot;" xr:uid="{887A2F45-1D0F-4039-BA8F-FD6DE6BCCE65}"/>
     <hyperlink ref="G25" r:id="rId23" xr:uid="{75921F28-6B77-45D5-87C5-554D1D35B95C}"/>
     <hyperlink ref="G26" r:id="rId24" xr:uid="{9241829D-BF69-44C8-A31B-99A25F7AF6C1}"/>
     <hyperlink ref="G27" r:id="rId25" xr:uid="{D034064B-F6BF-4A86-951C-466D8909946C}"/>
@@ -9802,14 +9802,14 @@
     <hyperlink ref="G38" r:id="rId37" xr:uid="{5862D0A8-856C-4F2A-BB5A-342564ED4434}"/>
     <hyperlink ref="G47" r:id="rId38" xr:uid="{D1BAF795-F101-47F5-B8E0-6085D5862D92}"/>
     <hyperlink ref="G48" r:id="rId39" xr:uid="{0D188133-9969-4BCC-915E-F268FC369981}"/>
-    <hyperlink ref="G51" r:id="rId40" xr:uid="{C3EF5C54-81F6-41F0-90EB-4B262944FBDB}"/>
-    <hyperlink ref="G52" r:id="rId41" xr:uid="{52484E64-8503-44C9-8133-12120ABAC2FA}"/>
-    <hyperlink ref="G49" r:id="rId42" xr:uid="{3221E400-DB1B-4110-8014-E2756F38EE0D}"/>
-    <hyperlink ref="G50" r:id="rId43" xr:uid="{1DFBCFFD-54D5-42AE-AFF6-32954A6D9DA7}"/>
-    <hyperlink ref="G41" r:id="rId44" xr:uid="{8A1D580A-86D4-4FAC-A96A-31A458722E11}"/>
-    <hyperlink ref="G42" r:id="rId45" xr:uid="{C21FDBA7-7415-4E47-A1E1-52DE294A4841}"/>
-    <hyperlink ref="G39" r:id="rId46" xr:uid="{13B27CE7-5730-4B2F-8609-4CA87401B1C7}"/>
-    <hyperlink ref="G40" r:id="rId47" xr:uid="{8FA8908A-BDCF-4A5A-B3ED-2B3230843F47}"/>
+    <hyperlink ref="G51" r:id="rId40" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{C3EF5C54-81F6-41F0-90EB-4B262944FBDB}"/>
+    <hyperlink ref="G52" r:id="rId41" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{52484E64-8503-44C9-8133-12120ABAC2FA}"/>
+    <hyperlink ref="G49" r:id="rId42" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{3221E400-DB1B-4110-8014-E2756F38EE0D}"/>
+    <hyperlink ref="G50" r:id="rId43" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{1DFBCFFD-54D5-42AE-AFF6-32954A6D9DA7}"/>
+    <hyperlink ref="G41" r:id="rId44" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{8A1D580A-86D4-4FAC-A96A-31A458722E11}"/>
+    <hyperlink ref="G42" r:id="rId45" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{C21FDBA7-7415-4E47-A1E1-52DE294A4841}"/>
+    <hyperlink ref="G39" r:id="rId46" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{13B27CE7-5730-4B2F-8609-4CA87401B1C7}"/>
+    <hyperlink ref="G40" r:id="rId47" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{8FA8908A-BDCF-4A5A-B3ED-2B3230843F47}"/>
     <hyperlink ref="G54" r:id="rId48" xr:uid="{FECDE756-2E55-448D-A493-AB830E00422F}"/>
     <hyperlink ref="G55" r:id="rId49" xr:uid="{2605904F-74E2-4140-8422-83AC6F95ACF0}"/>
     <hyperlink ref="G56" r:id="rId50" xr:uid="{4AAD2757-BD97-4642-943D-36ED00E6418E}"/>
@@ -9908,14 +9908,14 @@
     <hyperlink ref="G145" r:id="rId143" xr:uid="{B0EBB407-892A-46F9-A433-339EDEFF36CA}"/>
     <hyperlink ref="G154" r:id="rId144" xr:uid="{4D1D96AB-F6C0-466C-B288-9B7E965D5FA7}"/>
     <hyperlink ref="G155" r:id="rId145" xr:uid="{FCCA2229-C8F1-4780-900E-9BD3D7455E0F}"/>
-    <hyperlink ref="G158" r:id="rId146" xr:uid="{3838463F-43C1-4A61-AB63-F1C5B2AFDBF0}"/>
-    <hyperlink ref="G159" r:id="rId147" xr:uid="{3E1334CC-6479-4532-A127-DADAA939A866}"/>
-    <hyperlink ref="G156" r:id="rId148" xr:uid="{63F6986D-3A49-475A-8EE9-E174988E8CB7}"/>
-    <hyperlink ref="G157" r:id="rId149" xr:uid="{D3CD784C-2C34-4EBA-B40B-0F5B8E29CE21}"/>
-    <hyperlink ref="G148" r:id="rId150" xr:uid="{691CC4F2-C608-4C29-8A07-50DB4A64E403}"/>
-    <hyperlink ref="G149" r:id="rId151" xr:uid="{B8B234D7-88AD-4343-93DE-3FD89D6FE0F5}"/>
-    <hyperlink ref="G146" r:id="rId152" xr:uid="{8521FFD6-72AD-489F-BE6E-595EC4DF9B07}"/>
-    <hyperlink ref="G147" r:id="rId153" xr:uid="{599E5410-8644-49E7-BBCE-84A60F553247}"/>
+    <hyperlink ref="G158" r:id="rId146" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;sd&quot;,reference_line=1.2" xr:uid="{3838463F-43C1-4A61-AB63-F1C5B2AFDBF0}"/>
+    <hyperlink ref="G159" r:id="rId147" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;sd&quot;,reference_line=1.2" xr:uid="{3E1334CC-6479-4532-A127-DADAA939A866}"/>
+    <hyperlink ref="G156" r:id="rId148" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;mean&quot;" xr:uid="{63F6986D-3A49-475A-8EE9-E174988E8CB7}"/>
+    <hyperlink ref="G157" r:id="rId149" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;mean&quot;" xr:uid="{D3CD784C-2C34-4EBA-B40B-0F5B8E29CE21}"/>
+    <hyperlink ref="G148" r:id="rId150" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation=&quot;sd&quot;,reference_line=1.2" xr:uid="{691CC4F2-C608-4C29-8A07-50DB4A64E403}"/>
+    <hyperlink ref="G149" r:id="rId151" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation=&quot;sd&quot;,reference_line=1.2" xr:uid="{B8B234D7-88AD-4343-93DE-3FD89D6FE0F5}"/>
+    <hyperlink ref="G146" r:id="rId152" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation=&quot;mean&quot;" xr:uid="{8521FFD6-72AD-489F-BE6E-595EC4DF9B07}"/>
+    <hyperlink ref="G147" r:id="rId153" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation=&quot;mean&quot;" xr:uid="{599E5410-8644-49E7-BBCE-84A60F553247}"/>
     <hyperlink ref="G161" r:id="rId154" xr:uid="{E017C265-C7EE-4BE2-92AE-3655FA4CE873}"/>
     <hyperlink ref="G162" r:id="rId155" xr:uid="{65BFE8A3-327C-4903-AEAD-E18A20B5C1C8}"/>
     <hyperlink ref="G163" r:id="rId156" xr:uid="{3C9639CE-4095-48D6-9BF2-A97D45FFA1F4}"/>
@@ -9933,14 +9933,14 @@
     <hyperlink ref="G174" r:id="rId168" xr:uid="{DABA61E2-643B-405A-BFA0-6995A585B64E}"/>
     <hyperlink ref="G183" r:id="rId169" xr:uid="{4C36E278-D2D3-45FF-8284-293627DA01F3}"/>
     <hyperlink ref="G184" r:id="rId170" xr:uid="{22A20EAC-1B3D-41A4-8E1D-8938A76B0875}"/>
-    <hyperlink ref="G187" r:id="rId171" xr:uid="{3D966B71-BED3-45F4-BC61-4CB32D5C3717}"/>
-    <hyperlink ref="G188" r:id="rId172" xr:uid="{08F66550-E9A2-4264-89A0-0A33606F8D83}"/>
-    <hyperlink ref="G185" r:id="rId173" xr:uid="{D46FDDA2-F4E3-4274-BAC0-8674649007FA}"/>
-    <hyperlink ref="G186" r:id="rId174" xr:uid="{30AC6C78-C9EA-47C4-B38B-06DCD2BB5339}"/>
-    <hyperlink ref="G177" r:id="rId175" xr:uid="{56E63E90-383E-43BD-BD09-37AD8A3A38ED}"/>
-    <hyperlink ref="G178" r:id="rId176" xr:uid="{EFEEE030-3555-4DCD-A412-DABB3D57490B}"/>
-    <hyperlink ref="G175" r:id="rId177" xr:uid="{7BC043C1-C6A7-4D0D-AEF1-1BCEEFE1B02F}"/>
-    <hyperlink ref="G176" r:id="rId178" xr:uid="{9488B74C-839C-4FEE-A38C-82DB568AA2AE}"/>
+    <hyperlink ref="G187" r:id="rId171" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{3D966B71-BED3-45F4-BC61-4CB32D5C3717}"/>
+    <hyperlink ref="G188" r:id="rId172" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{08F66550-E9A2-4264-89A0-0A33606F8D83}"/>
+    <hyperlink ref="G185" r:id="rId173" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz,variable_label=@variable_label$nut_mfaz,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{D46FDDA2-F4E3-4274-BAC0-8674649007FA}"/>
+    <hyperlink ref="G186" r:id="rId174" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_mfaz_noflag,variable_label=@variable_label$nut_mfaz_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{30AC6C78-C9EA-47C4-B38B-06DCD2BB5339}"/>
+    <hyperlink ref="G177" r:id="rId175" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac,variable_label=@variable_label$nut_muac,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{56E63E90-383E-43BD-BD09-37AD8A3A38ED}"/>
+    <hyperlink ref="G178" r:id="rId176" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_noflag,variable_label=@variable_label$nut_muac_noflag,operation=&quot;sd&quot;,reference_line=1.2,grouping_col=@variable_map$sex" xr:uid="{EFEEE030-3555-4DCD-A412-DABB3D57490B}"/>
+    <hyperlink ref="G175" r:id="rId177" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm,variable_label=@variable_label$nut_muac_cm,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{7BC043C1-C6A7-4D0D-AEF1-1BCEEFE1B02F}"/>
+    <hyperlink ref="G176" r:id="rId178" display="date_col=@variable_map$survey_date,numeric_col=@variable_map$nut_muac_cm_noflag,variable_label=@variable_label$nut_muac_cm_noflag,operation=&quot;mean&quot;,grouping_col=@variable_map$sex" xr:uid="{9488B74C-839C-4FEE-A38C-82DB568AA2AE}"/>
     <hyperlink ref="G190" r:id="rId179" xr:uid="{C8A13D27-B50E-44F7-BFB1-53837A92FACF}"/>
     <hyperlink ref="G191" r:id="rId180" xr:uid="{BB5E2201-ADD0-483A-AB50-E4136A8F478D}"/>
     <hyperlink ref="G192" r:id="rId181" xr:uid="{04AA19E6-62F7-4197-A3FE-DB76769A6795}"/>
